--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45020</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>45754</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45826</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45867</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45881</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45224</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>45205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>46161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>45568</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45103</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>45194</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45078</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45086</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>45357</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45978</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45236</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45996</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>45152</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45212</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45126</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>46196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>46198</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45111</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>44610</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>46272</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45078</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45042</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>45013</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45427</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45054</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>45483</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>45510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45561</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>45012</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>45617</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45805</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>44908</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45937</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44985</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44645</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46006</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44928</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45079</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>45961</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45205</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>45686</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45672</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>45012</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45282</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>46195</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>46106</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45334</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>45005</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45527</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>46204</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45555</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45061</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45372</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45020</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45749</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>46266</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>46280</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45833</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45869</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>44894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45274</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44461</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45875</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45611</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>44616</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45335</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>44978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44672</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44869</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45772</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>46146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>46168</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>46202</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>46206</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>46211</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>46279</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44715</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44571</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44568</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44853</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44622</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44508</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44459</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>44510</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>44809</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44607</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44721</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44510</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>44818</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44848</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44635</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44510</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44503</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44587</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44592</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>44742</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>44623</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44650</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44714</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44847</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44847</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44749</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44460</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44460</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44474</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44880</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44837</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44861</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44482</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44476</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44476</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44461</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>44459</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>44502</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44495</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>44476</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44576</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>44888</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>44825</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44460</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>44565</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44760</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44732</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44469</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44469</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44550</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44536</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44810</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44810</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44588</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44845</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44862</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44764</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44739</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>44742</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44515</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>44517</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44595</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>44592</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44879</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44831</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44882</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44817</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44537</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>44806</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44810</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44530</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44882</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44712</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44806</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44809</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>44606</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44610</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>44715</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>44497</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44495</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45748</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45097</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45614</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45187</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44850</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45068</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44825</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44928</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45082</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45065</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45551</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45103</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45218</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45735</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45684</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>44874</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45714</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>44617</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45602</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>45188</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45345</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44883</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45617</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45111</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45110</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44764</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45279</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45643</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>44823</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44634</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45719</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45099</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45593</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44858</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44959</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45441</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44634</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45226</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45181</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45672</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>44852</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45223</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44923</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44882</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45730</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45700</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44851</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>44706</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45279</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45103</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45461</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45163</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>45278</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44817</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45272</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45106</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45183</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45446</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45246</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45216</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>45260</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45686</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45281</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45202</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45126</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45350</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>45350</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>45546</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>44582</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44928</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45215</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>45305</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45317</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44886</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45264</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>44810</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>44908</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>45412</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45097</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45148</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>44809</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>45684</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45757</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>44603</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44603</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44603</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>44945</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45646</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44993</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>44942</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45510</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45629</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45301</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>45527</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45212</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45525</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44810</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45280</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45225</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45225</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45257</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45099</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45119</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45162</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45339</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>45645</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45646</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>45632</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>44894</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45328</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>45197</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45748</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>44923</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45700</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>46139</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>45749</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45775</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>44487</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45112</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45679</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45604</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45260</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45280</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>45475</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44903</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45845</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45679</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>45243</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44670</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45483</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45137</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45715</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45764</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45733</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45784</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>45567</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>46139</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45167</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44740</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45440</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>45275</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45727</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45888</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         <v>45207</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45715</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45888</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>45077</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>45069</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45567</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45837</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>44656</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>45838</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45085</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45895</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45895</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45355</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45895</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45818</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45645</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45895</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45895</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45895</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>44991</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>45742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45897</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45162</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45798</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>44896</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45826</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>45370</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>45215</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45644</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45758</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>45546</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45755</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>45734</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>45275</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>44585</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45811</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45902</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>45905</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45905</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>44999</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45476</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45916</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45635</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45733</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45842</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>46140</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45845</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>44991</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44991</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45908</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45910</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45707</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45366</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45876</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>46140</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>46140</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>45069</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45911</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45911</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45748</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45914</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45195</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45917</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45916</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45916</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44634</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45917</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45917</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>44991</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>44991</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>44959</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>44959</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45187</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45176</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45181</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45714</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>44523</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45168</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45224</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45097</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>44573</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45463</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45923</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45923</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45924</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45923</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>46057</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>46059</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45925</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45925</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45925</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45925</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45925</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44820</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45476</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45111</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>44846</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>44848</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46146</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45089</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44565</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>44565</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45730</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45068</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>46146</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45315</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45734</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45672</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45938</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45940</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45470</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45602</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45339</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45940</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45169</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45614</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>45945</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45945</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>45595</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44867</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45427</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>45946</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45950</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45950</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45950</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45225</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45116</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45116</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45911</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>45950</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>45610</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45156</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45218</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>44971</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45714</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45754</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>45349</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45957</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45957</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>44466</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45957</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>44937</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45957</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45629</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45610</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>44620</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>46150</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>46150</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45888</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45628</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45603</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>45959</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45961</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>45961</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>45324</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>45964</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45964</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>46154</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45533</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45510</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>46155</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45811</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45845</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45749</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>46155</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45764</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45181</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>45097</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45356</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>46155</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45973</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45264</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>44895</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44895</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>44895</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45630</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45546</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45048</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45977</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45978</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>46154</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>45874</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45978</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45981</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>45754</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>45981</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45639</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45980</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>46155</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45980</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45985</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45281</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44886</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45265</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45179</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45756</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>46059</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45561</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>46079</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45988</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45401</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45989</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45992</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45610</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45992</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45992</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>44900</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>46160</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>44508</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48050,7 +48050,7 @@
         <v>44946</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45239</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>46161</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>44742</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45995</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>44974</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45994</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>45993</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>44587</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45315</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>44959</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>44959</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45036</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45593</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>46006</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45483</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>46006</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>46006</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>45628</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>46006</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>46006</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49593,7 +49593,7 @@
         <v>45181</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>46008</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>46008</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>46008</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>45390</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>44551</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45267</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>44971</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>44750</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>45084</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>46014</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>45121</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>45188</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45056</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45621</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         <v>46020</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>46104</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>46170</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>46024</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45604</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>44802</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>45240</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45993</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51345,7 +51345,7 @@
         <v>46170</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45993</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>45441</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>46170</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>46170</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>46030</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>44825</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45769</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51929,7 +51929,7 @@
         <v>45119</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>46174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>46174</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>45273</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         <v>45081</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45162</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         <v>45463</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>45055</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45349</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52596,7 +52596,7 @@
         <v>45775</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>46045</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         <v>46045</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52815,7 +52815,7 @@
         <v>46045</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52888,7 +52888,7 @@
         <v>44915</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52961,7 +52961,7 @@
         <v>46045</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>46045</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53107,7 +53107,7 @@
         <v>45610</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>46171</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53253,7 +53253,7 @@
         <v>45183</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53326,7 +53326,7 @@
         <v>46176</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53399,7 +53399,7 @@
         <v>45509</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45726</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53550,7 +53550,7 @@
         <v>46176</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>45168</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>46050</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>46050</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>45614</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53920,7 +53920,7 @@
         <v>45614</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>46054</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>46054</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>46054</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54217,7 +54217,7 @@
         <v>45092</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>45146</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>44551</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54436,7 +54436,7 @@
         <v>45620</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45236</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54582,7 +54582,7 @@
         <v>46059</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>44960</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54728,7 +54728,7 @@
         <v>46059</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>46059</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>46062</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>45188</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>46063</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>46063</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>46063</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>46063</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>44938</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55390,7 +55390,7 @@
         <v>44908</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>44946</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55541,7 +55541,7 @@
         <v>45357</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55614,7 +55614,7 @@
         <v>44712</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55687,7 +55687,7 @@
         <v>46069</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45217</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>46182</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>46182</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>45618</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>46182</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56130,7 +56130,7 @@
         <v>45562</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45509</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56286,7 +56286,7 @@
         <v>46078</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56359,7 +56359,7 @@
         <v>44908</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>46076</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>46077</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56583,7 +56583,7 @@
         <v>45677</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>46184</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56729,7 +56729,7 @@
         <v>46184</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>46079</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45742</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56948,7 +56948,7 @@
         <v>45735</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         <v>45568</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>44978</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>46084</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>46087</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45735</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>45702</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>45126</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>46091</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>46091</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>46094</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45084</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45722</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57897,7 +57897,7 @@
         <v>46094</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>46097</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58043,7 +58043,7 @@
         <v>46097</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>46097</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>46097</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>46097</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>46097</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45754</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>44806</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58554,7 +58554,7 @@
         <v>46097</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>46098</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>46097</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>46191</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58846,7 +58846,7 @@
         <v>45131</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58919,7 +58919,7 @@
         <v>46195</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58992,7 +58992,7 @@
         <v>46104</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>45372</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>46106</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59211,7 +59211,7 @@
         <v>46104</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>45121</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>46197</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59430,7 +59430,7 @@
         <v>46107</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59503,7 +59503,7 @@
         <v>44743</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59576,7 +59576,7 @@
         <v>46198</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>44991</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59722,7 +59722,7 @@
         <v>46107</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>46107</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59868,7 +59868,7 @@
         <v>45035</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59941,7 +59941,7 @@
         <v>45614</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60014,7 +60014,7 @@
         <v>46107</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60087,7 +60087,7 @@
         <v>44851</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>46111</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60238,7 +60238,7 @@
         <v>46198</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>46111</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60384,7 +60384,7 @@
         <v>44988</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>45705</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>46112</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>46113</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60676,7 +60676,7 @@
         <v>46113</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60749,7 +60749,7 @@
         <v>45089</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60822,7 +60822,7 @@
         <v>46113</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>45356</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>46113</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>46113</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         <v>46113</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61187,7 +61187,7 @@
         <v>46120</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61260,7 +61260,7 @@
         <v>46119</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61338,7 +61338,7 @@
         <v>46119</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61416,7 +61416,7 @@
         <v>45908</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61489,7 +61489,7 @@
         <v>46119</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
         <v>45323</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61640,7 +61640,7 @@
         <v>45373</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61713,7 +61713,7 @@
         <v>46119</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>46244</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>44924</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61937,7 +61937,7 @@
         <v>46128</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>46244</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62083,7 +62083,7 @@
         <v>45621</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>46204</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45126</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62302,7 +62302,7 @@
         <v>45253</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         <v>44810</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>44923</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45187</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>46246</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45076</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62740,7 +62740,7 @@
         <v>45524</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62813,7 +62813,7 @@
         <v>46134</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62886,7 +62886,7 @@
         <v>46134</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45099</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63032,7 +63032,7 @@
         <v>44628</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63105,7 +63105,7 @@
         <v>45119</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63178,7 +63178,7 @@
         <v>46134</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63251,7 +63251,7 @@
         <v>44988</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         <v>44809</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63397,7 +63397,7 @@
         <v>44809</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63470,7 +63470,7 @@
         <v>45880</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63543,7 +63543,7 @@
         <v>45903</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63616,7 +63616,7 @@
         <v>44887</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63689,7 +63689,7 @@
         <v>45908</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         <v>45005</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>44868</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45831</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>45126</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64054,7 +64054,7 @@
         <v>44565</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>45742</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45188</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64273,7 +64273,7 @@
         <v>45546</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64346,7 +64346,7 @@
         <v>44651</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>46205</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64492,7 +64492,7 @@
         <v>46246</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64565,7 +64565,7 @@
         <v>46206</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64638,7 +64638,7 @@
         <v>45323</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64716,7 +64716,7 @@
         <v>46206</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64789,7 +64789,7 @@
         <v>45012</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64862,7 +64862,7 @@
         <v>46251</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64935,7 +64935,7 @@
         <v>45181</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65008,7 +65008,7 @@
         <v>44812</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65081,7 +65081,7 @@
         <v>45205</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65154,7 +65154,7 @@
         <v>44980</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65227,7 +65227,7 @@
         <v>44810</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65300,7 +65300,7 @@
         <v>46206</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65373,7 +65373,7 @@
         <v>46206</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>46206</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65519,7 +65519,7 @@
         <v>45231</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65592,7 +65592,7 @@
         <v>45035</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>45077</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65738,7 +65738,7 @@
         <v>44945</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65811,7 +65811,7 @@
         <v>45594</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65884,7 +65884,7 @@
         <v>46252</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65957,7 +65957,7 @@
         <v>44721</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66030,7 +66030,7 @@
         <v>45300</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66103,7 +66103,7 @@
         <v>45210</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66176,7 +66176,7 @@
         <v>45614</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66254,7 +66254,7 @@
         <v>44903</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66327,7 +66327,7 @@
         <v>45065</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66400,7 +66400,7 @@
         <v>46253</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66473,7 +66473,7 @@
         <v>45224</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66546,7 +66546,7 @@
         <v>45607</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>45075</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66692,7 +66692,7 @@
         <v>46254</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66765,7 +66765,7 @@
         <v>45615</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66838,7 +66838,7 @@
         <v>45223</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66911,7 +66911,7 @@
         <v>45223</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66984,7 +66984,7 @@
         <v>46211</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67057,7 +67057,7 @@
         <v>45071</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67130,7 +67130,7 @@
         <v>45071</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67203,7 +67203,7 @@
         <v>46211</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67276,7 +67276,7 @@
         <v>44642</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67349,7 +67349,7 @@
         <v>45301</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67422,7 +67422,7 @@
         <v>44712</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67495,7 +67495,7 @@
         <v>46216</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67568,7 +67568,7 @@
         <v>45195</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67641,7 +67641,7 @@
         <v>45071</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67714,7 +67714,7 @@
         <v>45071</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67787,7 +67787,7 @@
         <v>45705</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45701</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67933,7 +67933,7 @@
         <v>45628</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68006,7 +68006,7 @@
         <v>45581</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68079,7 +68079,7 @@
         <v>45372</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68152,7 +68152,7 @@
         <v>46259</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68225,7 +68225,7 @@
         <v>45250</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68298,7 +68298,7 @@
         <v>46063</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68371,7 +68371,7 @@
         <v>44819</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68444,7 +68444,7 @@
         <v>45152</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68517,7 +68517,7 @@
         <v>45097</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68590,7 +68590,7 @@
         <v>45131</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68663,7 +68663,7 @@
         <v>45441</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68736,7 +68736,7 @@
         <v>46184</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68809,7 +68809,7 @@
         <v>45131</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68882,7 +68882,7 @@
         <v>45615</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68955,7 +68955,7 @@
         <v>45033</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69028,7 +69028,7 @@
         <v>45307</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69101,7 +69101,7 @@
         <v>45764</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>44886</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>45226</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69320,7 +69320,7 @@
         <v>45306</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69393,7 +69393,7 @@
         <v>45548</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69466,7 +69466,7 @@
         <v>44985</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69539,7 +69539,7 @@
         <v>44985</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69612,7 +69612,7 @@
         <v>44995</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69685,7 +69685,7 @@
         <v>45562</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69758,7 +69758,7 @@
         <v>45594</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69831,7 +69831,7 @@
         <v>46265</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69904,7 +69904,7 @@
         <v>45170</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69977,7 +69977,7 @@
         <v>46266</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70055,7 +70055,7 @@
         <v>45272</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70128,7 +70128,7 @@
         <v>45272</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70201,7 +70201,7 @@
         <v>44924</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70274,7 +70274,7 @@
         <v>45628</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70347,7 +70347,7 @@
         <v>44657</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70420,7 +70420,7 @@
         <v>46224</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70493,7 +70493,7 @@
         <v>44999</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70566,7 +70566,7 @@
         <v>46268</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70639,7 +70639,7 @@
         <v>45637</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70712,7 +70712,7 @@
         <v>45164</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70785,7 +70785,7 @@
         <v>45629</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70858,7 +70858,7 @@
         <v>46273</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70931,7 +70931,7 @@
         <v>45534</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -71004,7 +71004,7 @@
         <v>46009</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71077,7 +71077,7 @@
         <v>45708</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71150,7 +71150,7 @@
         <v>44959</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71228,7 +71228,7 @@
         <v>45783</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71301,7 +71301,7 @@
         <v>45783</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>45783</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71447,7 +71447,7 @@
         <v>45021</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71520,7 +71520,7 @@
         <v>45783</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71593,7 +71593,7 @@
         <v>45783</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71666,7 +71666,7 @@
         <v>45783</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71739,7 +71739,7 @@
         <v>46273</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71812,7 +71812,7 @@
         <v>45708</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71885,7 +71885,7 @@
         <v>46274</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71958,7 +71958,7 @@
         <v>46274</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72031,7 +72031,7 @@
         <v>46277</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72104,7 +72104,7 @@
         <v>45628</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72177,7 +72177,7 @@
         <v>45161</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72250,7 +72250,7 @@
         <v>45734</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72323,7 +72323,7 @@
         <v>45372</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72396,7 +72396,7 @@
         <v>46279</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72469,7 +72469,7 @@
         <v>45166</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72542,7 +72542,7 @@
         <v>45756</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72615,7 +72615,7 @@
         <v>45510</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72688,7 +72688,7 @@
         <v>45681</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72761,7 +72761,7 @@
         <v>45510</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72834,7 +72834,7 @@
         <v>45628</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72907,7 +72907,7 @@
         <v>45792</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72980,7 +72980,7 @@
         <v>45793</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73053,7 +73053,7 @@
         <v>45596</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73126,7 +73126,7 @@
         <v>44927</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73199,7 +73199,7 @@
         <v>45796</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73277,7 +73277,7 @@
         <v>45796</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73355,7 +73355,7 @@
         <v>45796</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73433,7 +73433,7 @@
         <v>46239</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73506,7 +73506,7 @@
         <v>46241</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73584,7 +73584,7 @@
         <v>45596</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73657,7 +73657,7 @@
         <v>45796</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73735,7 +73735,7 @@
         <v>46240</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73813,7 +73813,7 @@
         <v>45562</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73886,7 +73886,7 @@
         <v>45156</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73959,7 +73959,7 @@
         <v>45253</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -74037,7 +74037,7 @@
         <v>45645</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74110,7 +74110,7 @@
         <v>45811</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74183,7 +74183,7 @@
         <v>45811</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74256,7 +74256,7 @@
         <v>45811</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74329,7 +74329,7 @@
         <v>45371</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74402,7 +74402,7 @@
         <v>45812</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74475,7 +74475,7 @@
         <v>45686</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74548,7 +74548,7 @@
         <v>45817</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74621,7 +74621,7 @@
         <v>45762</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74694,7 +74694,7 @@
         <v>45518</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74767,7 +74767,7 @@
         <v>45818</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74840,7 +74840,7 @@
         <v>45617</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74913,7 +74913,7 @@
         <v>45825</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74986,7 +74986,7 @@
         <v>45824</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -75059,7 +75059,7 @@
         <v>45793</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75132,7 +75132,7 @@
         <v>45826</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75205,7 +75205,7 @@
         <v>45831</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75278,7 +75278,7 @@
         <v>45831</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75351,7 +75351,7 @@
         <v>45831</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75424,7 +75424,7 @@
         <v>45831</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75497,7 +75497,7 @@
         <v>45831</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75570,7 +75570,7 @@
         <v>45831</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75643,7 +75643,7 @@
         <v>45833</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75716,7 +75716,7 @@
         <v>45835</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75789,7 +75789,7 @@
         <v>45835</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75862,7 +75862,7 @@
         <v>45837</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75935,7 +75935,7 @@
         <v>45840</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -76008,7 +76008,7 @@
         <v>45840</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76081,7 +76081,7 @@
         <v>45842</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76154,7 +76154,7 @@
         <v>45723</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76227,7 +76227,7 @@
         <v>45775</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76300,7 +76300,7 @@
         <v>45730</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76373,7 +76373,7 @@
         <v>45848</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76446,7 +76446,7 @@
         <v>45848</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76519,7 +76519,7 @@
         <v>45811</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76592,7 +76592,7 @@
         <v>45852</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76665,7 +76665,7 @@
         <v>45667</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76738,7 +76738,7 @@
         <v>45109</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76811,7 +76811,7 @@
         <v>45530</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76884,7 +76884,7 @@
         <v>45811</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76957,7 +76957,7 @@
         <v>45860</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -77030,7 +77030,7 @@
         <v>45274</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77103,7 +77103,7 @@
         <v>45396</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77176,7 +77176,7 @@
         <v>45145</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77249,7 +77249,7 @@
         <v>44881</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77322,7 +77322,7 @@
         <v>45869</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77400,7 +77400,7 @@
         <v>45701</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77473,7 +77473,7 @@
         <v>45847</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77546,7 +77546,7 @@
         <v>45739</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77619,7 +77619,7 @@
         <v>45783</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77692,7 +77692,7 @@
         <v>45005</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77765,7 +77765,7 @@
         <v>44917</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77838,7 +77838,7 @@
         <v>45701</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77911,7 +77911,7 @@
         <v>45425</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77984,7 +77984,7 @@
         <v>45099</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -78057,7 +78057,7 @@
         <v>44621</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78130,7 +78130,7 @@
         <v>45079</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78203,7 +78203,7 @@
         <v>44538</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78276,7 +78276,7 @@
         <v>45394</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78349,7 +78349,7 @@
         <v>45869</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78427,7 +78427,7 @@
         <v>45271</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78500,7 +78500,7 @@
         <v>44847</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78573,7 +78573,7 @@
         <v>45026</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78646,7 +78646,7 @@
         <v>45301</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78719,7 +78719,7 @@
         <v>45647</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78792,7 +78792,7 @@
         <v>44881</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78865,7 +78865,7 @@
         <v>45211</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78938,7 +78938,7 @@
         <v>45247</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -79011,7 +79011,7 @@
         <v>44461</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79084,7 +79084,7 @@
         <v>44461</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79157,7 +79157,7 @@
         <v>45145</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79230,7 +79230,7 @@
         <v>45394</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79303,7 +79303,7 @@
         <v>44715</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79376,7 +79376,7 @@
         <v>45301</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79449,7 +79449,7 @@
         <v>45481</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79522,7 +79522,7 @@
         <v>44515</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79595,7 +79595,7 @@
         <v>44515</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79668,7 +79668,7 @@
         <v>45831</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79741,7 +79741,7 @@
         <v>45211</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79814,7 +79814,7 @@
         <v>45750</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79887,7 +79887,7 @@
         <v>45869</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79965,7 +79965,7 @@
         <v>45824</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -80038,7 +80038,7 @@
         <v>45301</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80111,7 +80111,7 @@
         <v>44860</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80184,7 +80184,7 @@
         <v>45676</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80257,7 +80257,7 @@
         <v>45875</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80330,7 +80330,7 @@
         <v>45875</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80403,7 +80403,7 @@
         <v>45881</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80476,7 +80476,7 @@
         <v>45880</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80549,7 +80549,7 @@
         <v>45880</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80622,7 +80622,7 @@
         <v>45881</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80695,7 +80695,7 @@
         <v>45110</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80768,7 +80768,7 @@
         <v>44820</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80841,7 +80841,7 @@
         <v>45537</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80914,7 +80914,7 @@
         <v>45226</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80987,7 +80987,7 @@
         <v>45527</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -81060,7 +81060,7 @@
         <v>45593</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81133,7 +81133,7 @@
         <v>44638</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81206,7 +81206,7 @@
         <v>45000</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81279,7 +81279,7 @@
         <v>44644</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81352,7 +81352,7 @@
         <v>44820</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81425,7 +81425,7 @@
         <v>44643</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81498,7 +81498,7 @@
         <v>45412</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81571,7 +81571,7 @@
         <v>45272</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81644,7 +81644,7 @@
         <v>45168</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81717,7 +81717,7 @@
         <v>45378</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81790,7 +81790,7 @@
         <v>44643</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81863,7 +81863,7 @@
         <v>44655</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81936,7 +81936,7 @@
         <v>45554</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -82009,7 +82009,7 @@
         <v>44484</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82082,7 +82082,7 @@
         <v>45574</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82155,7 +82155,7 @@
         <v>45615</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82228,7 +82228,7 @@
         <v>45526</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82301,7 +82301,7 @@
         <v>45597</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82374,7 +82374,7 @@
         <v>45033</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82447,7 +82447,7 @@
         <v>45553</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82520,7 +82520,7 @@
         <v>45357</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82593,7 +82593,7 @@
         <v>45427</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82666,7 +82666,7 @@
         <v>44642</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82739,7 +82739,7 @@
         <v>45447</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82812,7 +82812,7 @@
         <v>45294</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82885,7 +82885,7 @@
         <v>44831</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82958,7 +82958,7 @@
         <v>45000</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -83031,7 +83031,7 @@
         <v>45168</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83104,7 +83104,7 @@
         <v>45044</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83177,7 +83177,7 @@
         <v>45267</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83250,7 +83250,7 @@
         <v>45442</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83323,7 +83323,7 @@
         <v>44960</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83396,7 +83396,7 @@
         <v>44973</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83469,7 +83469,7 @@
         <v>45560</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83542,7 +83542,7 @@
         <v>45357</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83615,7 +83615,7 @@
         <v>44882</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83688,7 +83688,7 @@
         <v>45110</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83761,7 +83761,7 @@
         <v>45755</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83834,7 +83834,7 @@
         <v>45637</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83907,7 +83907,7 @@
         <v>45645</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83980,7 +83980,7 @@
         <v>45713</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -84053,7 +84053,7 @@
         <v>45742</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84126,7 +84126,7 @@
         <v>45720</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84199,7 +84199,7 @@
         <v>45632</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84272,7 +84272,7 @@
         <v>45631</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84345,7 +84345,7 @@
         <v>45713</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84418,7 +84418,7 @@
         <v>45789</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84491,7 +84491,7 @@
         <v>45818</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84564,7 +84564,7 @@
         <v>45831</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84637,7 +84637,7 @@
         <v>45831</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84710,7 +84710,7 @@
         <v>45895</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84783,7 +84783,7 @@
         <v>45895</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84856,7 +84856,7 @@
         <v>45894</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84929,7 +84929,7 @@
         <v>46027</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -85002,7 +85002,7 @@
         <v>46024</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -85075,7 +85075,7 @@
         <v>46024</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -85148,7 +85148,7 @@
         <v>46029</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85226,7 +85226,7 @@
         <v>46063</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -85299,7 +85299,7 @@
         <v>46062</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -85372,7 +85372,7 @@
         <v>46064</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -85445,7 +85445,7 @@
         <v>46150</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -85518,7 +85518,7 @@
         <v>46150</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -85591,7 +85591,7 @@
         <v>46156</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -85664,7 +85664,7 @@
         <v>46161</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -85737,7 +85737,7 @@
         <v>46161</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -85810,7 +85810,7 @@
         <v>46209</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -85888,7 +85888,7 @@
         <v>46266</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -85961,7 +85961,7 @@
         <v>46279</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -86039,7 +86039,7 @@
         <v>46279</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45224</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45568</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>46161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>45211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>45533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45236</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>45357</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45978</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45152</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46150</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45086</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>45126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45819</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>46196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>46198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>44610</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>45642</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45103</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45194</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>46272</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45042</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45013</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45372</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45061</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45266</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45594</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44985</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45555</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45510</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44645</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46106</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45020</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45012</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45937</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45805</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45483</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>45832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45054</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45833</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45686</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45961</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45672</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45869</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45274</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45561</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44894</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45527</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45079</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45334</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45875</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>46204</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45246</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>46266</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>46280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45282</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45012</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45162</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>45005</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45749</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45558</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44616</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44672</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45611</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44869</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45772</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>46146</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46168</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>46202</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46206</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46211</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46279</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44467</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>44715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44568</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44853</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44622</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>44508</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>44818</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44848</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>44635</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44510</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>44592</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44742</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44623</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>44714</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44749</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44474</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>44880</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>44837</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44861</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44482</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>44476</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>44476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44502</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44495</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44476</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44576</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44825</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44760</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44732</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>44469</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44469</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>44550</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>44536</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44810</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>44588</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44810</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44845</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>44862</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44764</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>44739</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44742</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44515</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>44592</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44517</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44595</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>44879</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44831</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44882</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>44537</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>44806</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>44810</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44530</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44882</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44806</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44809</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>44606</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>44610</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44715</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>44497</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44495</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44991</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44991</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44809</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44819</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45684</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44764</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45048</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45272</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45187</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45187</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>44900</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44867</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45069</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44825</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45085</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45324</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45440</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45089</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45764</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44928</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45300</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44810</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45441</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45239</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44810</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45373</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>44895</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44895</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44895</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45197</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>45126</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>44551</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>45119</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44946</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45461</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45317</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45702</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45112</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44823</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45119</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45323</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45280</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45796</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45796</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45097</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>46014</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45275</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45596</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45278</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>46020</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44894</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>46024</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45993</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45260</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44886</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>44850</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45339</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>46030</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45793</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45796</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45483</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45509</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45796</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45596</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44927</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>44945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45476</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45715</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>44817</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45748</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45672</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45749</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45888</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45758</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45715</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>45775</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44523</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45837</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>45156</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45645</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44656</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45826</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>45895</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45895</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>44908</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45895</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45895</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45895</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44915</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45897</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45562</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>46045</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>46045</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>46045</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>46045</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46045</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45902</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45357</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45137</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>46050</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>46050</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44874</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45908</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45905</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45646</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>45905</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45910</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>46054</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>46054</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>46054</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45707</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45911</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45911</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45876</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45916</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45215</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>46059</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45217</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45914</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>46059</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45916</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>46062</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>46059</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45525</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45917</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45562</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46063</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>44886</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>46063</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>46063</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45917</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>46063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45350</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45350</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46069</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45923</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45923</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45923</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>45253</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45925</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45925</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45925</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45924</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45925</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45925</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>44942</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46076</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46077</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45126</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>46078</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45735</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45742</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45372</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>44670</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45246</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45371</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>45110</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>46084</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45167</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45735</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45614</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>46087</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>46091</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46091</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45734</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45071</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>45071</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45938</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>44573</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46094</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46097</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>45940</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46097</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46097</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46097</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>46097</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>45441</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>46094</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46097</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46097</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46097</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45705</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>46098</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45945</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45945</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45946</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45205</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45205</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>44945</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45950</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45243</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45950</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44740</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45272</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45226</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>46104</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>46104</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45950</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45950</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>46107</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>46107</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44946</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>46107</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>46107</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45811</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36555,7 +36555,7 @@
         <v>45811</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45811</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>45911</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>46111</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>46111</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45084</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>46113</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>46113</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45957</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45957</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>46113</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>44634</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>46113</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>46113</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45888</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>46112</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45957</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44959</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44923</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>44923</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45957</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45614</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46113</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>44959</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>46119</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>45301</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>46119</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45959</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>45628</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45961</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>46120</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45964</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45964</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45961</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>45621</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45618</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45610</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>44634</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>44928</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45684</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45602</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>45686</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45617</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45973</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>45323</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45977</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45978</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45152</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45131</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45978</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45645</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>46128</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45980</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45980</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>46134</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46134</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>46134</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45509</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45981</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>44999</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45981</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>44802</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>45645</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44743</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45985</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45845</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45784</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45733</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45630</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45988</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45831</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45903</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>45989</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>45992</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45838</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>45762</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45483</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>45992</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45992</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45817</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45727</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45204</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45994</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>44809</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45880</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45995</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45993</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>44980</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45679</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>46057</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45764</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45224</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45916</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45518</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45742</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>46140</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45510</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45818</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>46140</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45908</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>46006</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>45224</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45679</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>46006</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45811</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>46006</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45646</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>46008</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>46008</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>45475</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45035</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45705</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45005</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44834,7 +44834,7 @@
         <v>44820</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>46006</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>46139</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>45628</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>46006</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>46139</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>46008</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>44712</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45033</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45798</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45567</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45168</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45845</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45714</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45742</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>45012</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>44991</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46075,7 +46075,7 @@
         <v>45824</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45111</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45621</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45267</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45643</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46440,7 +46440,7 @@
         <v>44991</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>44991</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45761</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46659,7 +46659,7 @@
         <v>45818</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>46140</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45476</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>45644</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45055</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45826</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45236</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45735</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45825</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>44565</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44565</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>45169</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44809</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>44810</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45714</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>46059</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45071</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45071</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45733</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45730</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>44903</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>45842</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45793</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45076</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>45077</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45831</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45068</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>45764</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>46146</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44565</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45036</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>44886</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>45831</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>44585</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>45620</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45831</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45831</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>45831</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>44551</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45594</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45366</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>46146</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49730,7 +49730,7 @@
         <v>45546</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45546</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>45831</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49959,7 +49959,7 @@
         <v>46150</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>46150</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45510</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>45833</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45629</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45202</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>44923</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>44846</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>44896</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>46154</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>46155</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50762,7 +50762,7 @@
         <v>45845</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45874</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>46155</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>46154</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>46059</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45811</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>45835</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>46155</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>46155</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45749</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>46079</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>45099</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>46160</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45092</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51789,7 +51789,7 @@
         <v>45837</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>45835</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45840</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>45103</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>45840</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45595</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>45307</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>45065</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>46161</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>44974</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>44924</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45842</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45775</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>45723</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45035</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>45272</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45848</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45848</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45126</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>45730</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45811</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45852</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45183</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45223</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45223</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45614</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45667</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>45811</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>45109</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45530</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45860</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>46170</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>46104</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>46170</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>46170</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>46171</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>45470</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45097</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45463</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>45775</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54792,7 +54792,7 @@
         <v>46174</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         <v>46174</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>45372</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45306</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>46176</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>46176</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45869</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55308,7 +55308,7 @@
         <v>45869</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>45869</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45567</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45099</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45754</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>45481</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>45783</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>44848</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>45026</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>44847</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>44881</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>44860</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>44917</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45099</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>45831</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45396</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45701</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>45425</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>46182</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46182</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>44515</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56851,7 +56851,7 @@
         <v>44515</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45162</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>44538</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>46182</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>44881</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57216,7 +57216,7 @@
         <v>45617</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>45181</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>45824</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>45390</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57508,7 +57508,7 @@
         <v>45394</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>45701</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45148</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57727,7 +57727,7 @@
         <v>46184</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>46184</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45271</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45301</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>45211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>45301</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>45168</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45188</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58311,7 +58311,7 @@
         <v>44985</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58384,7 +58384,7 @@
         <v>44985</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45847</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58530,7 +58530,7 @@
         <v>45116</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>45116</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58676,7 +58676,7 @@
         <v>45370</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58749,7 +58749,7 @@
         <v>44937</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58822,7 +58822,7 @@
         <v>44621</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>44715</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45273</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>45739</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>45394</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>45533</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45145</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59338,7 +59338,7 @@
         <v>45676</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45750</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59484,7 +59484,7 @@
         <v>45593</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45079</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>45005</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>45274</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59781,7 +59781,7 @@
         <v>45145</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59854,7 +59854,7 @@
         <v>45247</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59927,7 +59927,7 @@
         <v>44995</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60000,7 +60000,7 @@
         <v>45647</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45301</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60146,7 +60146,7 @@
         <v>45211</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
         <v>45754</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60292,7 +60292,7 @@
         <v>45524</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60365,7 +60365,7 @@
         <v>45527</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45349</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60511,7 +60511,7 @@
         <v>46191</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60584,7 +60584,7 @@
         <v>46195</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45131</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>45875</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45875</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>45089</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60949,7 +60949,7 @@
         <v>44999</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61022,7 +61022,7 @@
         <v>45629</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61095,7 +61095,7 @@
         <v>45056</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61168,7 +61168,7 @@
         <v>45188</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>46197</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61314,7 +61314,7 @@
         <v>45610</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45637</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>45880</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61533,7 +61533,7 @@
         <v>45719</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>45084</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>45614</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61757,7 +61757,7 @@
         <v>45216</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61830,7 +61830,7 @@
         <v>46198</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>45908</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61976,7 +61976,7 @@
         <v>44603</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>44603</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62122,7 +62122,7 @@
         <v>44603</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>45345</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62268,7 +62268,7 @@
         <v>46198</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62341,7 +62341,7 @@
         <v>45880</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62414,7 +62414,7 @@
         <v>44582</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62487,7 +62487,7 @@
         <v>45881</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62560,7 +62560,7 @@
         <v>45881</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62633,7 +62633,7 @@
         <v>45275</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>44988</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62784,7 +62784,7 @@
         <v>46204</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62857,7 +62857,7 @@
         <v>46205</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>45427</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>45176</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63081,7 +63081,7 @@
         <v>45183</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45082</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63227,7 +63227,7 @@
         <v>46206</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63300,7 +63300,7 @@
         <v>46206</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63373,7 +63373,7 @@
         <v>46206</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63446,7 +63446,7 @@
         <v>46251</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>45769</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>44642</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>46206</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>45628</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63811,7 +63811,7 @@
         <v>44634</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>46206</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63957,7 +63957,7 @@
         <v>45615</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>46252</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64103,7 +64103,7 @@
         <v>45628</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64176,7 +64176,7 @@
         <v>45614</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64254,7 +64254,7 @@
         <v>46254</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64327,7 +64327,7 @@
         <v>45069</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64400,7 +64400,7 @@
         <v>46211</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64473,7 +64473,7 @@
         <v>46211</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64546,7 +64546,7 @@
         <v>46253</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64619,7 +64619,7 @@
         <v>44617</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>45677</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45240</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64843,7 +64843,7 @@
         <v>45615</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64916,7 +64916,7 @@
         <v>45179</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64989,7 +64989,7 @@
         <v>44721</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65062,7 +65062,7 @@
         <v>44851</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65140,7 +65140,7 @@
         <v>45686</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65213,7 +65213,7 @@
         <v>45701</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65286,7 +65286,7 @@
         <v>45700</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65359,7 +65359,7 @@
         <v>44628</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65432,7 +65432,7 @@
         <v>46184</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65505,7 +65505,7 @@
         <v>46259</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65578,7 +65578,7 @@
         <v>45446</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65651,7 +65651,7 @@
         <v>46216</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>45181</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
         <v>44851</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65875,7 +65875,7 @@
         <v>45195</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65948,7 +65948,7 @@
         <v>46063</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66021,7 +66021,7 @@
         <v>45163</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66094,7 +66094,7 @@
         <v>44706</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66167,7 +66167,7 @@
         <v>45126</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66240,7 +66240,7 @@
         <v>45187</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>44750</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45581</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66459,7 +66459,7 @@
         <v>45225</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66532,7 +66532,7 @@
         <v>45131</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66605,7 +66605,7 @@
         <v>45207</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66678,7 +66678,7 @@
         <v>45756</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66751,7 +66751,7 @@
         <v>45231</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66824,7 +66824,7 @@
         <v>45264</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66897,7 +66897,7 @@
         <v>45748</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66970,7 +66970,7 @@
         <v>44825</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67043,7 +67043,7 @@
         <v>46265</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67116,7 +67116,7 @@
         <v>45315</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67189,7 +67189,7 @@
         <v>46266</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67267,7 +67267,7 @@
         <v>45215</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67340,7 +67340,7 @@
         <v>45328</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67413,7 +67413,7 @@
         <v>46268</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67486,7 +67486,7 @@
         <v>45225</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67559,7 +67559,7 @@
         <v>45257</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67632,7 +67632,7 @@
         <v>45162</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67705,7 +67705,7 @@
         <v>44988</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67778,7 +67778,7 @@
         <v>46009</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>46273</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67924,7 +67924,7 @@
         <v>45356</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>45218</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68070,7 +68070,7 @@
         <v>45195</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68143,7 +68143,7 @@
         <v>44908</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68221,7 +68221,7 @@
         <v>44858</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68294,7 +68294,7 @@
         <v>46273</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68367,7 +68367,7 @@
         <v>46274</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>46274</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68513,7 +68513,7 @@
         <v>44852</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68586,7 +68586,7 @@
         <v>45280</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68659,7 +68659,7 @@
         <v>45279</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68732,7 +68732,7 @@
         <v>45264</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68805,7 +68805,7 @@
         <v>45099</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68878,7 +68878,7 @@
         <v>46277</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68951,7 +68951,7 @@
         <v>46279</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69024,7 +69024,7 @@
         <v>46239</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69097,7 +69097,7 @@
         <v>45225</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69170,7 +69170,7 @@
         <v>46240</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69248,7 +69248,7 @@
         <v>45604</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69321,7 +69321,7 @@
         <v>45734</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69394,7 +69394,7 @@
         <v>44651</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69467,7 +69467,7 @@
         <v>46241</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69545,7 +69545,7 @@
         <v>44620</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69618,7 +69618,7 @@
         <v>46287</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69691,7 +69691,7 @@
         <v>45812</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69764,7 +69764,7 @@
         <v>44887</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69837,7 +69837,7 @@
         <v>44938</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69910,7 +69910,7 @@
         <v>44974</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69983,7 +69983,7 @@
         <v>44959</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70061,7 +70061,7 @@
         <v>44959</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70134,7 +70134,7 @@
         <v>44959</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70207,7 +70207,7 @@
         <v>46244</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70280,7 +70280,7 @@
         <v>44812</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70353,7 +70353,7 @@
         <v>44810</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70426,7 +70426,7 @@
         <v>46287</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70499,7 +70499,7 @@
         <v>46244</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70572,7 +70572,7 @@
         <v>46246</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70645,7 +70645,7 @@
         <v>46224</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70718,7 +70718,7 @@
         <v>46119</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70796,7 +70796,7 @@
         <v>46286</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70869,7 +70869,7 @@
         <v>46286</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70942,7 +70942,7 @@
         <v>45188</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71015,7 +71015,7 @@
         <v>45162</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71093,7 +71093,7 @@
         <v>44924</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71166,7 +71166,7 @@
         <v>46246</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71239,7 +71239,7 @@
         <v>44657</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71312,7 +71312,7 @@
         <v>46289</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71385,7 +71385,7 @@
         <v>45218</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71458,7 +71458,7 @@
         <v>45260</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71531,7 +71531,7 @@
         <v>44806</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71604,7 +71604,7 @@
         <v>44742</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71677,7 +71677,7 @@
         <v>45356</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71750,7 +71750,7 @@
         <v>44487</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71823,7 +71823,7 @@
         <v>45562</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71901,7 +71901,7 @@
         <v>45546</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71979,7 +71979,7 @@
         <v>45604</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72052,7 +72052,7 @@
         <v>45940</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72125,7 +72125,7 @@
         <v>45593</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72203,7 +72203,7 @@
         <v>45226</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72276,7 +72276,7 @@
         <v>45568</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72349,7 +72349,7 @@
         <v>45097</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72422,7 +72422,7 @@
         <v>45097</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72495,7 +72495,7 @@
         <v>45081</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72568,7 +72568,7 @@
         <v>45093</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72641,7 +72641,7 @@
         <v>45305</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72714,7 +72714,7 @@
         <v>45607</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72787,7 +72787,7 @@
         <v>45097</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72860,7 +72860,7 @@
         <v>45121</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72933,7 +72933,7 @@
         <v>44985</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73006,7 +73006,7 @@
         <v>45757</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73079,7 +73079,7 @@
         <v>45349</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73152,7 +73152,7 @@
         <v>44978</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73225,7 +73225,7 @@
         <v>44960</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73298,7 +73298,7 @@
         <v>44712</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73371,7 +73371,7 @@
         <v>44929</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73444,7 +73444,7 @@
         <v>45281</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73517,7 +73517,7 @@
         <v>45253</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73590,7 +73590,7 @@
         <v>45754</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73663,7 +73663,7 @@
         <v>44991</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73736,7 +73736,7 @@
         <v>44971</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73809,7 +73809,7 @@
         <v>45111</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73882,7 +73882,7 @@
         <v>45181</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73955,7 +73955,7 @@
         <v>45119</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74028,7 +74028,7 @@
         <v>44868</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74101,7 +74101,7 @@
         <v>44882</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74174,7 +74174,7 @@
         <v>45188</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74247,7 +74247,7 @@
         <v>45463</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74320,7 +74320,7 @@
         <v>45602</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74393,7 +74393,7 @@
         <v>45672</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74466,7 +74466,7 @@
         <v>45551</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74544,7 +74544,7 @@
         <v>44883</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74617,7 +74617,7 @@
         <v>45614</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74695,7 +74695,7 @@
         <v>45068</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74768,7 +74768,7 @@
         <v>45401</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74841,7 +74841,7 @@
         <v>45103</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74914,7 +74914,7 @@
         <v>45301</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>45700</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75060,7 +75060,7 @@
         <v>45065</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75133,7 +75133,7 @@
         <v>45121</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75206,7 +75206,7 @@
         <v>45146</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75279,7 +75279,7 @@
         <v>45632</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75352,7 +75352,7 @@
         <v>45210</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75425,7 +75425,7 @@
         <v>45603</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75503,7 +75503,7 @@
         <v>45748</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75576,7 +75576,7 @@
         <v>45181</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75649,7 +75649,7 @@
         <v>45412</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75722,7 +75722,7 @@
         <v>45561</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75795,7 +75795,7 @@
         <v>45755</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75868,7 +75868,7 @@
         <v>44993</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75941,7 +75941,7 @@
         <v>45097</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76014,7 +76014,7 @@
         <v>45223</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76087,7 +76087,7 @@
         <v>45250</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76160,7 +76160,7 @@
         <v>44903</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76233,7 +76233,7 @@
         <v>45106</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76306,7 +76306,7 @@
         <v>45546</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76379,7 +76379,7 @@
         <v>45355</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76452,7 +76452,7 @@
         <v>45315</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76525,7 +76525,7 @@
         <v>45339</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76598,7 +76598,7 @@
         <v>44466</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76671,7 +76671,7 @@
         <v>44971</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76744,7 +76744,7 @@
         <v>45726</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76817,7 +76817,7 @@
         <v>45610</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76890,7 +76890,7 @@
         <v>45281</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76963,7 +76963,7 @@
         <v>44587</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77036,7 +77036,7 @@
         <v>45279</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77114,7 +77114,7 @@
         <v>45548</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77187,7 +77187,7 @@
         <v>45610</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77260,7 +77260,7 @@
         <v>45594</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77333,7 +77333,7 @@
         <v>45077</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77406,7 +77406,7 @@
         <v>45714</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77479,7 +77479,7 @@
         <v>45075</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77552,7 +77552,7 @@
         <v>45635</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77625,7 +77625,7 @@
         <v>45722</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77698,7 +77698,7 @@
         <v>45639</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77771,7 +77771,7 @@
         <v>45156</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77844,7 +77844,7 @@
         <v>45164</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77917,7 +77917,7 @@
         <v>44508</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77990,7 +77990,7 @@
         <v>45730</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78063,7 +78063,7 @@
         <v>45441</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78136,7 +78136,7 @@
         <v>45181</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78209,7 +78209,7 @@
         <v>45629</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78282,7 +78282,7 @@
         <v>45534</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78355,7 +78355,7 @@
         <v>45708</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78428,7 +78428,7 @@
         <v>44959</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78506,7 +78506,7 @@
         <v>45783</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78579,7 +78579,7 @@
         <v>45783</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78652,7 +78652,7 @@
         <v>45783</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78725,7 +78725,7 @@
         <v>45783</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78798,7 +78798,7 @@
         <v>45783</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78871,7 +78871,7 @@
         <v>45161</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78944,7 +78944,7 @@
         <v>45021</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79017,7 +79017,7 @@
         <v>45783</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79090,7 +79090,7 @@
         <v>45708</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79163,7 +79163,7 @@
         <v>45681</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79236,7 +79236,7 @@
         <v>45628</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79309,7 +79309,7 @@
         <v>45372</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79382,7 +79382,7 @@
         <v>45734</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79455,7 +79455,7 @@
         <v>45510</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79528,7 +79528,7 @@
         <v>45756</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79601,7 +79601,7 @@
         <v>45166</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79674,7 +79674,7 @@
         <v>45628</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79747,7 +79747,7 @@
         <v>45792</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79820,7 +79820,7 @@
         <v>45510</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79893,7 +79893,7 @@
         <v>44638</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79966,7 +79966,7 @@
         <v>44644</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80039,7 +80039,7 @@
         <v>44643</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80112,7 +80112,7 @@
         <v>44643</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80185,7 +80185,7 @@
         <v>44655</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80258,7 +80258,7 @@
         <v>44642</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80331,7 +80331,7 @@
         <v>45110</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80404,7 +80404,7 @@
         <v>44820</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80477,7 +80477,7 @@
         <v>45537</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80550,7 +80550,7 @@
         <v>45226</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80623,7 +80623,7 @@
         <v>45527</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80696,7 +80696,7 @@
         <v>45593</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80769,7 +80769,7 @@
         <v>45000</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80842,7 +80842,7 @@
         <v>44820</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80915,7 +80915,7 @@
         <v>45412</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80988,7 +80988,7 @@
         <v>45272</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81061,7 +81061,7 @@
         <v>45168</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81134,7 +81134,7 @@
         <v>45378</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81207,7 +81207,7 @@
         <v>45554</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81280,7 +81280,7 @@
         <v>44484</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81353,7 +81353,7 @@
         <v>45574</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81426,7 +81426,7 @@
         <v>45615</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81499,7 +81499,7 @@
         <v>45526</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81572,7 +81572,7 @@
         <v>45597</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81645,7 +81645,7 @@
         <v>45033</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81718,7 +81718,7 @@
         <v>45553</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81791,7 +81791,7 @@
         <v>45357</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81864,7 +81864,7 @@
         <v>45427</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81937,7 +81937,7 @@
         <v>45447</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82010,7 +82010,7 @@
         <v>45294</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82083,7 +82083,7 @@
         <v>44831</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82156,7 +82156,7 @@
         <v>45000</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82229,7 +82229,7 @@
         <v>45168</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82302,7 +82302,7 @@
         <v>45044</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82375,7 +82375,7 @@
         <v>45267</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82448,7 +82448,7 @@
         <v>45442</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82521,7 +82521,7 @@
         <v>44960</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82594,7 +82594,7 @@
         <v>44973</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82667,7 +82667,7 @@
         <v>45560</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82740,7 +82740,7 @@
         <v>45357</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82813,7 +82813,7 @@
         <v>44882</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82886,7 +82886,7 @@
         <v>45110</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82959,7 +82959,7 @@
         <v>45755</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83032,7 +83032,7 @@
         <v>45637</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83105,7 +83105,7 @@
         <v>45645</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83178,7 +83178,7 @@
         <v>45713</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83251,7 +83251,7 @@
         <v>45742</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83324,7 +83324,7 @@
         <v>45720</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83397,7 +83397,7 @@
         <v>45632</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83470,7 +83470,7 @@
         <v>45631</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83543,7 +83543,7 @@
         <v>45713</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83616,7 +83616,7 @@
         <v>45789</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83689,7 +83689,7 @@
         <v>45818</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83762,7 +83762,7 @@
         <v>45831</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83835,7 +83835,7 @@
         <v>45831</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83908,7 +83908,7 @@
         <v>45895</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83981,7 +83981,7 @@
         <v>45895</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84054,7 +84054,7 @@
         <v>45894</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84127,7 +84127,7 @@
         <v>46024</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84200,7 +84200,7 @@
         <v>46024</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84273,7 +84273,7 @@
         <v>46027</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84346,7 +84346,7 @@
         <v>46029</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84424,7 +84424,7 @@
         <v>46062</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84497,7 +84497,7 @@
         <v>46063</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84570,7 +84570,7 @@
         <v>46064</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84643,7 +84643,7 @@
         <v>46150</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84716,7 +84716,7 @@
         <v>46150</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84789,7 +84789,7 @@
         <v>46156</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84862,7 +84862,7 @@
         <v>46161</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84935,7 +84935,7 @@
         <v>46161</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -85008,7 +85008,7 @@
         <v>46209</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -85086,7 +85086,7 @@
         <v>46266</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85159,7 +85159,7 @@
         <v>46279</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -85237,7 +85237,7 @@
         <v>46279</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45224</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45568</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>46161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>45211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>45533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45236</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>45476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>45357</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45978</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45152</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>45111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46150</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45086</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>45126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45819</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>46196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>46198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>44610</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>45642</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45103</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45194</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>46272</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45042</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45013</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45372</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45061</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45266</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45594</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44985</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45555</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45510</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44645</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46106</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45020</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45012</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45937</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45805</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45483</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44852</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>45832</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45054</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45833</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45686</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45961</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45672</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45869</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45274</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45561</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44894</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45527</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45079</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45334</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45875</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>46204</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45246</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>46266</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>46280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45282</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45012</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45162</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>45005</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45749</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45558</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44616</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44672</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45611</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44869</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45772</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>46146</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46168</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>46202</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46206</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46211</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46279</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44467</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>44715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44568</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44853</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44622</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>44508</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>44818</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44848</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>44635</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44510</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>44592</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44742</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44623</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>44714</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44749</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44474</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>44880</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>44837</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44861</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44482</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>44476</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>44476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>44502</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44495</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44476</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44576</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44825</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44760</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44732</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>44469</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44469</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>44550</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>44536</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44810</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>44588</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44810</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44845</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>44862</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44764</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>44739</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44742</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44515</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>44592</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44517</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44595</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>44879</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44831</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44882</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>44537</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>44806</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>44810</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44530</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44882</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44806</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44809</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>44606</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>44610</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44715</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>44497</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44495</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44991</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44991</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44809</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44819</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45684</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44764</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45048</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45272</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45187</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45187</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>44900</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44867</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45069</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44825</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45085</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45324</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45440</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45089</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45764</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>44928</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45300</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44810</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45441</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45239</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44810</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45373</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>44895</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44895</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44895</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45197</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>45126</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>44551</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>45119</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44946</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45461</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45317</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45702</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45112</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44823</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45119</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45323</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45280</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45796</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45796</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45097</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>46014</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45275</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45596</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45278</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>46020</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44894</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>46024</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45993</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45260</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44886</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>44850</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45339</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>46030</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45793</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45796</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45483</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45509</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45796</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45596</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44927</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>44945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45476</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45715</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>44817</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45748</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45672</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45749</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45888</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45758</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45715</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>45775</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44523</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45837</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>45156</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45645</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44656</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45826</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>45895</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45895</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>44908</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45895</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45895</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45895</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44915</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45897</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45562</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>46045</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>46045</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>46045</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>46045</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46045</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45902</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45357</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45137</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>46050</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>46050</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44874</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45908</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45905</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45646</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>45905</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45910</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>46054</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>46054</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>46054</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45707</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45911</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45911</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45876</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45916</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45215</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>46059</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45217</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45914</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>46059</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45916</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>46062</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>46059</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45525</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45917</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45562</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46063</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>44886</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>46063</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>46063</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45917</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>46063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45350</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45350</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46069</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45923</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45923</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45923</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>45253</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45925</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45925</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45925</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45924</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45925</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45925</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>44942</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46076</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46077</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45126</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>46078</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45735</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45742</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45372</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>44670</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45246</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45371</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>45110</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>46084</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45167</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45735</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45614</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>46087</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>46091</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46091</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45734</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45071</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>45071</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45938</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>44573</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46094</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46097</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>45940</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46097</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46097</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46097</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>46097</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>45441</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>46094</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46097</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46097</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46097</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45705</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>46098</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45945</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45945</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45946</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45205</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45205</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>44945</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45950</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45243</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45950</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44740</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45272</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45226</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>46104</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>46104</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45950</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45950</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>46107</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>46107</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44946</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>46107</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>46107</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45811</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36555,7 +36555,7 @@
         <v>45811</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45811</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>45911</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>46111</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>46111</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45084</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>46113</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>46113</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45957</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45957</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>46113</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>44634</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>46113</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>46113</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45888</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>46112</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45957</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44959</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44923</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>44923</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45957</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45614</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46113</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>44959</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>46119</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>45301</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>46119</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45959</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>45628</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45961</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>46120</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45964</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45964</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45961</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>45621</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45618</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45610</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>44634</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>44928</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45684</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45602</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>45686</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45617</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45973</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>45323</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45977</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45978</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45152</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45131</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45978</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45645</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>46128</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45980</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45980</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>46134</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46134</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>46134</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45509</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45981</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>44999</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45981</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>44802</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>45645</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44743</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45985</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45845</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45784</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45733</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45630</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45988</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45831</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45903</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>45989</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>45992</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45838</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>45762</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45483</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>45992</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>45992</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45817</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45727</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45204</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45994</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>44809</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45880</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45995</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45993</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>44980</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45679</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>46057</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45764</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45224</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45916</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45518</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45742</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>46140</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45510</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45818</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>46140</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45908</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>46006</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>45224</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45679</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>46006</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45811</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>46006</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45646</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>46008</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>46008</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>45475</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45035</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45705</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45005</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44834,7 +44834,7 @@
         <v>44820</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>46006</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>46139</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>45628</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>46006</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>46139</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>46008</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>44712</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45033</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45798</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45567</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45168</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45845</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45714</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45742</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>45012</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>44991</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46075,7 +46075,7 @@
         <v>45824</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45111</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45621</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45267</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45643</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46440,7 +46440,7 @@
         <v>44991</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>44991</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45761</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46659,7 +46659,7 @@
         <v>45818</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>46140</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45476</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>45644</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45055</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45826</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45236</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45735</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45825</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>44565</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44565</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>45169</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44809</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>44810</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45714</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>46059</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45071</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45071</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45733</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>45730</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>44903</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>45842</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45793</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45076</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>45077</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45831</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45068</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>45764</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>46146</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44565</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45036</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>44886</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>45831</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>44585</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>45620</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45831</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45831</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>45831</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>44551</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45594</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45366</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>46146</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49730,7 +49730,7 @@
         <v>45546</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45546</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>45831</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49959,7 +49959,7 @@
         <v>46150</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>46150</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45510</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>45833</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45629</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45202</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>44923</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>44846</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>44896</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>46154</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>46155</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50762,7 +50762,7 @@
         <v>45845</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45874</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>46155</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>46154</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>46059</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45811</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>45835</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>46155</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>46155</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45749</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>46079</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>45099</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>46160</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45092</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51789,7 +51789,7 @@
         <v>45837</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>45835</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45840</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>45103</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>45840</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45595</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>45307</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>45065</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>46161</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>44974</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>44924</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45842</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45775</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>45723</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45035</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>45272</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45848</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45848</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45126</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>45730</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45811</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45852</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45183</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45223</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45223</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45614</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45667</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>45811</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>45109</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45530</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45860</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>46170</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>46104</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>46170</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>46170</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>46171</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>45470</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45097</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45463</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>45775</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54792,7 +54792,7 @@
         <v>46174</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         <v>46174</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>45372</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45306</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>46176</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>46176</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45869</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55308,7 +55308,7 @@
         <v>45869</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>45869</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45567</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45099</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45754</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>45481</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>45783</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>44848</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>45026</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>44847</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>44881</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>44860</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>44917</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45099</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>45831</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45396</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45701</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>45425</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>46182</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46182</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>44515</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56851,7 +56851,7 @@
         <v>44515</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45162</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>44538</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>46182</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>44881</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57216,7 +57216,7 @@
         <v>45617</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>45181</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>45824</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>45390</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57508,7 +57508,7 @@
         <v>45394</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>45701</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45148</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57727,7 +57727,7 @@
         <v>46184</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>46184</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45271</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45301</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>45211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>45301</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>45168</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45188</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58311,7 +58311,7 @@
         <v>44985</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58384,7 +58384,7 @@
         <v>44985</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45847</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58530,7 +58530,7 @@
         <v>45116</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>45116</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58676,7 +58676,7 @@
         <v>45370</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58749,7 +58749,7 @@
         <v>44937</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58822,7 +58822,7 @@
         <v>44621</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>44715</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45273</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>45739</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>45394</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>45533</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59265,7 +59265,7 @@
         <v>45145</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59338,7 +59338,7 @@
         <v>45676</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45750</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59484,7 +59484,7 @@
         <v>45593</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45079</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>45005</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>45274</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59781,7 +59781,7 @@
         <v>45145</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59854,7 +59854,7 @@
         <v>45247</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59927,7 +59927,7 @@
         <v>44995</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60000,7 +60000,7 @@
         <v>45647</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45301</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60146,7 +60146,7 @@
         <v>45211</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
         <v>45754</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60292,7 +60292,7 @@
         <v>45524</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60365,7 +60365,7 @@
         <v>45527</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45349</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60511,7 +60511,7 @@
         <v>46191</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60584,7 +60584,7 @@
         <v>46195</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45131</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>45875</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45875</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>45089</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60949,7 +60949,7 @@
         <v>44999</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61022,7 +61022,7 @@
         <v>45629</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61095,7 +61095,7 @@
         <v>45056</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61168,7 +61168,7 @@
         <v>45188</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>46197</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61314,7 +61314,7 @@
         <v>45610</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45637</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>45880</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61533,7 +61533,7 @@
         <v>45719</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>45084</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>45614</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61757,7 +61757,7 @@
         <v>45216</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61830,7 +61830,7 @@
         <v>46198</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>45908</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61976,7 +61976,7 @@
         <v>44603</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>44603</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62122,7 +62122,7 @@
         <v>44603</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>45345</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62268,7 +62268,7 @@
         <v>46198</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62341,7 +62341,7 @@
         <v>45880</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62414,7 +62414,7 @@
         <v>44582</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62487,7 +62487,7 @@
         <v>45881</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62560,7 +62560,7 @@
         <v>45881</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62633,7 +62633,7 @@
         <v>45275</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>44988</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62784,7 +62784,7 @@
         <v>46204</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62857,7 +62857,7 @@
         <v>46205</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>45427</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>45176</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63081,7 +63081,7 @@
         <v>45183</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45082</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63227,7 +63227,7 @@
         <v>46206</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63300,7 +63300,7 @@
         <v>46206</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63373,7 +63373,7 @@
         <v>46206</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63446,7 +63446,7 @@
         <v>46251</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>45769</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>44642</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>46206</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>45628</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63811,7 +63811,7 @@
         <v>44634</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>46206</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63957,7 +63957,7 @@
         <v>45615</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>46252</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64103,7 +64103,7 @@
         <v>45628</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64176,7 +64176,7 @@
         <v>45614</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64254,7 +64254,7 @@
         <v>46254</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64327,7 +64327,7 @@
         <v>45069</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64400,7 +64400,7 @@
         <v>46211</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64473,7 +64473,7 @@
         <v>46211</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64546,7 +64546,7 @@
         <v>46253</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64619,7 +64619,7 @@
         <v>44617</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>45677</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45240</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64843,7 +64843,7 @@
         <v>45615</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64916,7 +64916,7 @@
         <v>45179</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64989,7 +64989,7 @@
         <v>44721</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65062,7 +65062,7 @@
         <v>44851</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65140,7 +65140,7 @@
         <v>45686</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65213,7 +65213,7 @@
         <v>45701</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65286,7 +65286,7 @@
         <v>45700</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65359,7 +65359,7 @@
         <v>44628</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65432,7 +65432,7 @@
         <v>46184</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65505,7 +65505,7 @@
         <v>46259</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65578,7 +65578,7 @@
         <v>45446</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65651,7 +65651,7 @@
         <v>46216</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>45181</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
         <v>44851</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65875,7 +65875,7 @@
         <v>45195</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65948,7 +65948,7 @@
         <v>46063</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66021,7 +66021,7 @@
         <v>45163</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66094,7 +66094,7 @@
         <v>44706</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66167,7 +66167,7 @@
         <v>45126</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66240,7 +66240,7 @@
         <v>45187</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>44750</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45581</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66459,7 +66459,7 @@
         <v>45225</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66532,7 +66532,7 @@
         <v>45131</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66605,7 +66605,7 @@
         <v>45207</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66678,7 +66678,7 @@
         <v>45756</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66751,7 +66751,7 @@
         <v>45231</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66824,7 +66824,7 @@
         <v>45264</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66897,7 +66897,7 @@
         <v>45748</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66970,7 +66970,7 @@
         <v>44825</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67043,7 +67043,7 @@
         <v>46265</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67116,7 +67116,7 @@
         <v>45315</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67189,7 +67189,7 @@
         <v>46266</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67267,7 +67267,7 @@
         <v>45215</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67340,7 +67340,7 @@
         <v>45328</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67413,7 +67413,7 @@
         <v>46268</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67486,7 +67486,7 @@
         <v>45225</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67559,7 +67559,7 @@
         <v>45257</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67632,7 +67632,7 @@
         <v>45162</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67705,7 +67705,7 @@
         <v>44988</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67778,7 +67778,7 @@
         <v>46009</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>46273</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67924,7 +67924,7 @@
         <v>45356</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>45218</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68070,7 +68070,7 @@
         <v>45195</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68143,7 +68143,7 @@
         <v>44908</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68221,7 +68221,7 @@
         <v>44858</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68294,7 +68294,7 @@
         <v>46273</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68367,7 +68367,7 @@
         <v>46274</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>46274</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68513,7 +68513,7 @@
         <v>44852</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68586,7 +68586,7 @@
         <v>45280</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68659,7 +68659,7 @@
         <v>45279</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68732,7 +68732,7 @@
         <v>45264</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68805,7 +68805,7 @@
         <v>45099</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68878,7 +68878,7 @@
         <v>46277</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68951,7 +68951,7 @@
         <v>46279</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69024,7 +69024,7 @@
         <v>46239</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69097,7 +69097,7 @@
         <v>45225</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69170,7 +69170,7 @@
         <v>46240</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69248,7 +69248,7 @@
         <v>45604</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69321,7 +69321,7 @@
         <v>45734</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69394,7 +69394,7 @@
         <v>44651</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69467,7 +69467,7 @@
         <v>46241</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69545,7 +69545,7 @@
         <v>44620</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69618,7 +69618,7 @@
         <v>46287</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69691,7 +69691,7 @@
         <v>45812</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69764,7 +69764,7 @@
         <v>44887</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69837,7 +69837,7 @@
         <v>44938</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69910,7 +69910,7 @@
         <v>44974</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69983,7 +69983,7 @@
         <v>44959</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70061,7 +70061,7 @@
         <v>44959</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70134,7 +70134,7 @@
         <v>44959</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70207,7 +70207,7 @@
         <v>46244</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70280,7 +70280,7 @@
         <v>44812</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70353,7 +70353,7 @@
         <v>44810</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70426,7 +70426,7 @@
         <v>46287</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70499,7 +70499,7 @@
         <v>46244</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70572,7 +70572,7 @@
         <v>46246</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70645,7 +70645,7 @@
         <v>46224</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70718,7 +70718,7 @@
         <v>46119</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70796,7 +70796,7 @@
         <v>46286</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70869,7 +70869,7 @@
         <v>46286</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70942,7 +70942,7 @@
         <v>45188</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71015,7 +71015,7 @@
         <v>45162</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71093,7 +71093,7 @@
         <v>44924</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71166,7 +71166,7 @@
         <v>46246</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71239,7 +71239,7 @@
         <v>44657</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71312,7 +71312,7 @@
         <v>46289</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71385,7 +71385,7 @@
         <v>45218</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71458,7 +71458,7 @@
         <v>45260</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71531,7 +71531,7 @@
         <v>44806</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71604,7 +71604,7 @@
         <v>44742</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71677,7 +71677,7 @@
         <v>45356</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71750,7 +71750,7 @@
         <v>44487</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71823,7 +71823,7 @@
         <v>45562</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71901,7 +71901,7 @@
         <v>45546</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71979,7 +71979,7 @@
         <v>45604</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72052,7 +72052,7 @@
         <v>45940</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72125,7 +72125,7 @@
         <v>45593</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72203,7 +72203,7 @@
         <v>45226</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72276,7 +72276,7 @@
         <v>45568</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72349,7 +72349,7 @@
         <v>45097</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72422,7 +72422,7 @@
         <v>45097</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72495,7 +72495,7 @@
         <v>45081</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72568,7 +72568,7 @@
         <v>45093</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72641,7 +72641,7 @@
         <v>45305</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72714,7 +72714,7 @@
         <v>45607</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72787,7 +72787,7 @@
         <v>45097</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72860,7 +72860,7 @@
         <v>45121</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72933,7 +72933,7 @@
         <v>44985</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73006,7 +73006,7 @@
         <v>45757</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73079,7 +73079,7 @@
         <v>45349</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73152,7 +73152,7 @@
         <v>44978</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73225,7 +73225,7 @@
         <v>44960</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73298,7 +73298,7 @@
         <v>44712</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73371,7 +73371,7 @@
         <v>44929</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73444,7 +73444,7 @@
         <v>45281</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73517,7 +73517,7 @@
         <v>45253</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73590,7 +73590,7 @@
         <v>45754</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73663,7 +73663,7 @@
         <v>44991</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73736,7 +73736,7 @@
         <v>44971</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73809,7 +73809,7 @@
         <v>45111</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73882,7 +73882,7 @@
         <v>45181</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73955,7 +73955,7 @@
         <v>45119</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74028,7 +74028,7 @@
         <v>44868</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74101,7 +74101,7 @@
         <v>44882</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74174,7 +74174,7 @@
         <v>45188</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74247,7 +74247,7 @@
         <v>45463</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74320,7 +74320,7 @@
         <v>45602</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74393,7 +74393,7 @@
         <v>45672</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74466,7 +74466,7 @@
         <v>45551</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74544,7 +74544,7 @@
         <v>44883</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74617,7 +74617,7 @@
         <v>45614</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74695,7 +74695,7 @@
         <v>45068</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74768,7 +74768,7 @@
         <v>45401</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74841,7 +74841,7 @@
         <v>45103</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74914,7 +74914,7 @@
         <v>45301</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>45700</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75060,7 +75060,7 @@
         <v>45065</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75133,7 +75133,7 @@
         <v>45121</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75206,7 +75206,7 @@
         <v>45146</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75279,7 +75279,7 @@
         <v>45632</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75352,7 +75352,7 @@
         <v>45210</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75425,7 +75425,7 @@
         <v>45603</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75503,7 +75503,7 @@
         <v>45748</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75576,7 +75576,7 @@
         <v>45181</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75649,7 +75649,7 @@
         <v>45412</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75722,7 +75722,7 @@
         <v>45561</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75795,7 +75795,7 @@
         <v>45755</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75868,7 +75868,7 @@
         <v>44993</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75941,7 +75941,7 @@
         <v>45097</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76014,7 +76014,7 @@
         <v>45223</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76087,7 +76087,7 @@
         <v>45250</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76160,7 +76160,7 @@
         <v>44903</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76233,7 +76233,7 @@
         <v>45106</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76306,7 +76306,7 @@
         <v>45546</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76379,7 +76379,7 @@
         <v>45355</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76452,7 +76452,7 @@
         <v>45315</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76525,7 +76525,7 @@
         <v>45339</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76598,7 +76598,7 @@
         <v>44466</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76671,7 +76671,7 @@
         <v>44971</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76744,7 +76744,7 @@
         <v>45726</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76817,7 +76817,7 @@
         <v>45610</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76890,7 +76890,7 @@
         <v>45281</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76963,7 +76963,7 @@
         <v>44587</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77036,7 +77036,7 @@
         <v>45279</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77114,7 +77114,7 @@
         <v>45548</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77187,7 +77187,7 @@
         <v>45610</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77260,7 +77260,7 @@
         <v>45594</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77333,7 +77333,7 @@
         <v>45077</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77406,7 +77406,7 @@
         <v>45714</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77479,7 +77479,7 @@
         <v>45075</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77552,7 +77552,7 @@
         <v>45635</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77625,7 +77625,7 @@
         <v>45722</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77698,7 +77698,7 @@
         <v>45639</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77771,7 +77771,7 @@
         <v>45156</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77844,7 +77844,7 @@
         <v>45164</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77917,7 +77917,7 @@
         <v>44508</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77990,7 +77990,7 @@
         <v>45730</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78063,7 +78063,7 @@
         <v>45441</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78136,7 +78136,7 @@
         <v>45181</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78209,7 +78209,7 @@
         <v>45629</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78282,7 +78282,7 @@
         <v>45534</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78355,7 +78355,7 @@
         <v>45708</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78428,7 +78428,7 @@
         <v>44959</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78506,7 +78506,7 @@
         <v>45783</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78579,7 +78579,7 @@
         <v>45783</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78652,7 +78652,7 @@
         <v>45783</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78725,7 +78725,7 @@
         <v>45783</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78798,7 +78798,7 @@
         <v>45783</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78871,7 +78871,7 @@
         <v>45161</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78944,7 +78944,7 @@
         <v>45021</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79017,7 +79017,7 @@
         <v>45783</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79090,7 +79090,7 @@
         <v>45708</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79163,7 +79163,7 @@
         <v>45681</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79236,7 +79236,7 @@
         <v>45628</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79309,7 +79309,7 @@
         <v>45372</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79382,7 +79382,7 @@
         <v>45734</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79455,7 +79455,7 @@
         <v>45510</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79528,7 +79528,7 @@
         <v>45756</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79601,7 +79601,7 @@
         <v>45166</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79674,7 +79674,7 @@
         <v>45628</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79747,7 +79747,7 @@
         <v>45792</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79820,7 +79820,7 @@
         <v>45510</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79893,7 +79893,7 @@
         <v>44638</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79966,7 +79966,7 @@
         <v>44644</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80039,7 +80039,7 @@
         <v>44643</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80112,7 +80112,7 @@
         <v>44643</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80185,7 +80185,7 @@
         <v>44655</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80258,7 +80258,7 @@
         <v>44642</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80331,7 +80331,7 @@
         <v>45110</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80404,7 +80404,7 @@
         <v>44820</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80477,7 +80477,7 @@
         <v>45537</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80550,7 +80550,7 @@
         <v>45226</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80623,7 +80623,7 @@
         <v>45527</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80696,7 +80696,7 @@
         <v>45593</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80769,7 +80769,7 @@
         <v>45000</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80842,7 +80842,7 @@
         <v>44820</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80915,7 +80915,7 @@
         <v>45412</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80988,7 +80988,7 @@
         <v>45272</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81061,7 +81061,7 @@
         <v>45168</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81134,7 +81134,7 @@
         <v>45378</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81207,7 +81207,7 @@
         <v>45554</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81280,7 +81280,7 @@
         <v>44484</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81353,7 +81353,7 @@
         <v>45574</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81426,7 +81426,7 @@
         <v>45615</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81499,7 +81499,7 @@
         <v>45526</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81572,7 +81572,7 @@
         <v>45597</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81645,7 +81645,7 @@
         <v>45033</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81718,7 +81718,7 @@
         <v>45553</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81791,7 +81791,7 @@
         <v>45357</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81864,7 +81864,7 @@
         <v>45427</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81937,7 +81937,7 @@
         <v>45447</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82010,7 +82010,7 @@
         <v>45294</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82083,7 +82083,7 @@
         <v>44831</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82156,7 +82156,7 @@
         <v>45000</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82229,7 +82229,7 @@
         <v>45168</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82302,7 +82302,7 @@
         <v>45044</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82375,7 +82375,7 @@
         <v>45267</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82448,7 +82448,7 @@
         <v>45442</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82521,7 +82521,7 @@
         <v>44960</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82594,7 +82594,7 @@
         <v>44973</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82667,7 +82667,7 @@
         <v>45560</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82740,7 +82740,7 @@
         <v>45357</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82813,7 +82813,7 @@
         <v>44882</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82886,7 +82886,7 @@
         <v>45110</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82959,7 +82959,7 @@
         <v>45755</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83032,7 +83032,7 @@
         <v>45637</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83105,7 +83105,7 @@
         <v>45645</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83178,7 +83178,7 @@
         <v>45713</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83251,7 +83251,7 @@
         <v>45742</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83324,7 +83324,7 @@
         <v>45720</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83397,7 +83397,7 @@
         <v>45632</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83470,7 +83470,7 @@
         <v>45631</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83543,7 +83543,7 @@
         <v>45713</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83616,7 +83616,7 @@
         <v>45789</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83689,7 +83689,7 @@
         <v>45818</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83762,7 +83762,7 @@
         <v>45831</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83835,7 +83835,7 @@
         <v>45831</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83908,7 +83908,7 @@
         <v>45895</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83981,7 +83981,7 @@
         <v>45895</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84054,7 +84054,7 @@
         <v>45894</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84127,7 +84127,7 @@
         <v>46024</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84200,7 +84200,7 @@
         <v>46024</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84273,7 +84273,7 @@
         <v>46027</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84346,7 +84346,7 @@
         <v>46029</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84424,7 +84424,7 @@
         <v>46062</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84497,7 +84497,7 @@
         <v>46063</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84570,7 +84570,7 @@
         <v>46064</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84643,7 +84643,7 @@
         <v>46150</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84716,7 +84716,7 @@
         <v>46150</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84789,7 +84789,7 @@
         <v>46156</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84862,7 +84862,7 @@
         <v>46161</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84935,7 +84935,7 @@
         <v>46161</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -85008,7 +85008,7 @@
         <v>46209</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -85086,7 +85086,7 @@
         <v>46266</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85159,7 +85159,7 @@
         <v>46279</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -85237,7 +85237,7 @@
         <v>46279</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>46008</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45568</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45224</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45530</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45211</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>46161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45103</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45476</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45194</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45272</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45819</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>46150</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45357</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45733</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45236</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>45181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>46198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45152</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45212</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>46272</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45111</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45042</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45013</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45427</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45054</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>46006</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45483</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45510</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45561</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45978</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45191</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46106</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45012</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45617</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45832</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>45833</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>44985</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45805</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>44894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45274</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45266</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44820</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>45875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45961</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44645</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45672</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44928</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45079</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46204</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45205</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45686</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45012</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45334</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>46280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45005</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45527</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45555</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45061</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45372</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45020</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45749</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45611</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44616</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45335</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44978</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44831</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44672</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44869</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45772</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>46168</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46202</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46206</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44568</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44853</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44622</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44508</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44818</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44848</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44510</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44635</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44510</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44742</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44592</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44714</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44623</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44749</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44474</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44880</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44837</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44861</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44482</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44476</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44502</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44495</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44476</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44576</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44825</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>44760</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44732</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44550</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44810</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44536</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44588</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44810</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44845</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44862</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44764</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44739</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44742</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44515</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44592</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44517</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44595</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>44879</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44831</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44882</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44817</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>44537</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44806</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44810</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44530</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44882</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44806</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44606</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44809</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44610</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44715</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>44497</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44495</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45748</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45187</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>44929</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44764</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45082</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45614</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45065</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45097</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>44850</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44825</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45068</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44928</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45279</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45761</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45103</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45218</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45551</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45684</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44974</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45735</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>44874</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44617</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45714</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45617</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45188</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45111</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45110</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45602</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44985</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45345</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45166</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44883</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45756</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45510</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>44959</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45758</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45643</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44823</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45681</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45275</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46006</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46006</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>46006</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45775</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>44634</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45510</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45628</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>46006</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>46006</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45260</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>46008</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46008</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>46008</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45719</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45593</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44858</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45441</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45715</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45181</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44852</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>46014</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44634</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>46020</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45888</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45888</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45226</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>45672</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45223</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45837</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>44882</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45895</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>45895</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45895</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>46024</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44923</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45730</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45895</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45895</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45895</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45700</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45897</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44851</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>45993</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45993</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45826</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45279</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>46030</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45103</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45461</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45792</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45278</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44706</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45793</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45163</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45902</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45905</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45905</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44817</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45908</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45910</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45596</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45707</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44927</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45796</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45796</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45796</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>46045</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45876</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>46045</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46045</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45911</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45911</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>46045</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>46045</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45596</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45914</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45183</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45272</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45796</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45106</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45916</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45916</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45917</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45917</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45446</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45562</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45156</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45253</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>46050</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45645</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>46050</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46054</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>46054</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46054</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45923</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45923</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45924</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45923</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45216</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45925</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>45925</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45925</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45925</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>45925</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>46059</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>46059</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45686</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>46059</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>46062</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>46063</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>46063</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>46063</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45350</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45350</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>46063</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45546</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45202</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>45126</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46069</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>44928</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44582</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45734</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45215</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45811</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45811</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45811</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45938</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45940</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45305</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46078</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45945</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45945</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>46076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>46077</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44886</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45317</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45946</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45950</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>45950</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45950</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>45371</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>45742</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45735</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45911</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>45950</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44810</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44908</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>45264</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>45412</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>45097</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>45957</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>45957</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45957</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45957</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45888</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>46084</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>46087</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>45735</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45959</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44809</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45148</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45961</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>46091</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45961</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44945</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45964</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>45964</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>46091</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45684</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45757</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45205</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>46094</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>44603</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>44603</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>44603</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>46094</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>45686</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45817</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45646</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>46097</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>46097</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>44942</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>46097</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>46097</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>46097</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>46097</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44993</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>46097</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>46098</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>46097</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45510</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45162</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45973</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45212</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46104</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45629</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45762</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45518</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>46106</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45525</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45977</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45978</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>45818</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45225</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>45225</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>45099</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>46104</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45978</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45301</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45527</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45617</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44810</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45280</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45257</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>46107</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45119</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45981</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45981</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>46107</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         <v>46107</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>45980</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>46107</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>45980</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45645</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>44894</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>45093</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>46111</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45985</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>46111</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>46112</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41148,7 +41148,7 @@
         <v>45646</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>45632</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>46113</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>46113</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>46113</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45339</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>46113</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>46113</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45328</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>45988</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>45197</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>46120</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44923</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>45700</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45825</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>46119</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45989</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>46119</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45824</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>45992</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>44487</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>45112</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>45992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45992</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45604</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45793</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44903</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>45995</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45826</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45243</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45994</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>46128</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45993</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>44670</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43708,7 +43708,7 @@
         <v>45137</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45831</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45831</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>45831</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45831</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45831</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44146,7 +44146,7 @@
         <v>45833</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45567</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>45167</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>44740</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45272</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45440</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>46134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46134</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45207</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45077</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45069</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>46134</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>44656</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45085</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
         <v>45355</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>44809</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>44809</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45835</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45835</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45645</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45880</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45903</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>44991</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45837</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45162</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45908</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45005</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>44896</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45370</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45215</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45546</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>45840</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>45755</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45831</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45742</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45840</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>46139</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>45734</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>44585</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45679</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>44999</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>45842</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>45475</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>45723</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45775</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>45845</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45679</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45635</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45730</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45483</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>44991</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47874,7 +47874,7 @@
         <v>44991</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>45848</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45848</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45366</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45811</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45069</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45748</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45764</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>45733</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45784</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>45195</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>46139</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45852</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>44634</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45727</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>44991</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44991</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45567</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>44959</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>44959</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45187</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45838</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45176</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45181</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45714</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>44523</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45168</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45224</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45667</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45818</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45097</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>44573</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>45742</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45463</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>45798</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45644</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45109</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45530</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>44820</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45811</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>45811</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45476</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45476</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>45111</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>44846</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45860</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>45916</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>44848</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45733</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45842</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>46140</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45845</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45089</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>44565</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>44565</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>45730</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45068</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46140</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46140</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45315</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>45672</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45470</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>45602</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>45339</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>45097</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>45274</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>45396</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45145</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>44881</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>45169</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>45869</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53072,7 +53072,7 @@
         <v>45614</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>45701</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45847</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53296,7 +53296,7 @@
         <v>45739</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>45783</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45005</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>44917</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>45595</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>44867</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45701</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>46057</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>46059</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>45425</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>45099</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45427</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>44621</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>45079</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>44538</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45394</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>45869</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45271</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>44847</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54688,7 +54688,7 @@
         <v>45026</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54761,7 +54761,7 @@
         <v>45301</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54834,7 +54834,7 @@
         <v>46146</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45225</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45116</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>45116</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55126,7 +55126,7 @@
         <v>45610</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55199,7 +55199,7 @@
         <v>46146</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55272,7 +55272,7 @@
         <v>45647</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55345,7 +55345,7 @@
         <v>45156</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55418,7 +55418,7 @@
         <v>45218</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>44971</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45714</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45754</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55710,7 +55710,7 @@
         <v>45349</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55783,7 +55783,7 @@
         <v>44881</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>44937</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45629</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56002,7 +56002,7 @@
         <v>45211</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56075,7 +56075,7 @@
         <v>45610</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56148,7 +56148,7 @@
         <v>44620</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45247</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56294,7 +56294,7 @@
         <v>45145</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56367,7 +56367,7 @@
         <v>45394</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56440,7 +56440,7 @@
         <v>44715</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45301</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45481</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>44515</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>44515</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45831</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45628</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45211</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57024,7 +57024,7 @@
         <v>45750</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57097,7 +57097,7 @@
         <v>45869</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57175,7 +57175,7 @@
         <v>45824</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>45603</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57326,7 +57326,7 @@
         <v>45301</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>44860</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57472,7 +57472,7 @@
         <v>45676</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>46150</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>46150</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57691,7 +57691,7 @@
         <v>45324</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57764,7 +57764,7 @@
         <v>46154</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57837,7 +57837,7 @@
         <v>46155</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57910,7 +57910,7 @@
         <v>45811</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45845</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58056,7 +58056,7 @@
         <v>45533</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58134,7 +58134,7 @@
         <v>45749</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58207,7 +58207,7 @@
         <v>46155</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58280,7 +58280,7 @@
         <v>45875</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>45510</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58426,7 +58426,7 @@
         <v>46155</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>45874</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58572,7 +58572,7 @@
         <v>46155</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>46059</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>46079</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45764</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58869,7 +58869,7 @@
         <v>45181</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>45097</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45356</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>46160</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45875</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>45264</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59307,7 +59307,7 @@
         <v>44895</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>44895</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>44895</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>45630</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59599,7 +59599,7 @@
         <v>45546</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59677,7 +59677,7 @@
         <v>45048</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59750,7 +59750,7 @@
         <v>46161</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59823,7 +59823,7 @@
         <v>45754</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59896,7 +59896,7 @@
         <v>45639</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59969,7 +59969,7 @@
         <v>45281</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>44886</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60115,7 +60115,7 @@
         <v>45265</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60188,7 +60188,7 @@
         <v>45881</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60261,7 +60261,7 @@
         <v>45179</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60334,7 +60334,7 @@
         <v>45756</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>45880</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60480,7 +60480,7 @@
         <v>46104</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>46170</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>46170</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60699,7 +60699,7 @@
         <v>46170</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60772,7 +60772,7 @@
         <v>45561</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60845,7 +60845,7 @@
         <v>45880</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>46174</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60991,7 +60991,7 @@
         <v>46174</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61064,7 +61064,7 @@
         <v>45881</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61137,7 +61137,7 @@
         <v>45401</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>45775</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61283,7 +61283,7 @@
         <v>46171</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61356,7 +61356,7 @@
         <v>45610</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61429,7 +61429,7 @@
         <v>46176</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61502,7 +61502,7 @@
         <v>45748</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61575,7 +61575,7 @@
         <v>46176</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61648,7 +61648,7 @@
         <v>44900</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45275</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>45715</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>44508</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>44946</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>45239</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>46182</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>46182</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>46182</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>44742</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>46184</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>44974</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>46184</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>44587</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>45315</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>44959</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>44959</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>45036</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62967,7 +62967,7 @@
         <v>45593</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>45483</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45628</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>45181</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>45390</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>44551</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>46191</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63483,7 +63483,7 @@
         <v>45267</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63556,7 +63556,7 @@
         <v>45131</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63629,7 +63629,7 @@
         <v>46195</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63702,7 +63702,7 @@
         <v>45204</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>44971</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         <v>44750</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45084</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>46197</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64067,7 +64067,7 @@
         <v>46198</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64140,7 +64140,7 @@
         <v>45121</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64213,7 +64213,7 @@
         <v>45188</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64286,7 +64286,7 @@
         <v>45056</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64359,7 +64359,7 @@
         <v>45621</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>46198</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64505,7 +64505,7 @@
         <v>45908</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64578,7 +64578,7 @@
         <v>45604</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64651,7 +64651,7 @@
         <v>44802</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>46204</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64797,7 +64797,7 @@
         <v>45240</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64870,7 +64870,7 @@
         <v>45441</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64943,7 +64943,7 @@
         <v>46205</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>44825</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65089,7 +65089,7 @@
         <v>46206</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65162,7 +65162,7 @@
         <v>46206</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65235,7 +65235,7 @@
         <v>45769</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65308,7 +65308,7 @@
         <v>45119</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65381,7 +65381,7 @@
         <v>45273</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65454,7 +65454,7 @@
         <v>45081</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65527,7 +65527,7 @@
         <v>45162</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65605,7 +65605,7 @@
         <v>45463</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65683,7 +65683,7 @@
         <v>46206</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65756,7 +65756,7 @@
         <v>46206</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65829,7 +65829,7 @@
         <v>46206</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65902,7 +65902,7 @@
         <v>45614</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65980,7 +65980,7 @@
         <v>45615</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66053,7 +66053,7 @@
         <v>46211</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66126,7 +66126,7 @@
         <v>45055</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66199,7 +66199,7 @@
         <v>45349</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>46211</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66345,7 +66345,7 @@
         <v>44915</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66418,7 +66418,7 @@
         <v>46216</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66491,7 +66491,7 @@
         <v>45610</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66564,7 +66564,7 @@
         <v>45183</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66637,7 +66637,7 @@
         <v>45509</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66715,7 +66715,7 @@
         <v>45726</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66788,7 +66788,7 @@
         <v>46259</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66861,7 +66861,7 @@
         <v>46063</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66934,7 +66934,7 @@
         <v>45168</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67007,7 +67007,7 @@
         <v>46184</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67080,7 +67080,7 @@
         <v>45614</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67158,7 +67158,7 @@
         <v>45614</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67236,7 +67236,7 @@
         <v>45092</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67309,7 +67309,7 @@
         <v>45146</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67382,7 +67382,7 @@
         <v>44551</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45620</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67528,7 +67528,7 @@
         <v>45236</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67601,7 +67601,7 @@
         <v>44960</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>46265</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>45188</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         <v>46266</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67898,7 +67898,7 @@
         <v>44938</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67971,7 +67971,7 @@
         <v>44908</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>44946</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68122,7 +68122,7 @@
         <v>45357</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68195,7 +68195,7 @@
         <v>44712</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68268,7 +68268,7 @@
         <v>45217</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68341,7 +68341,7 @@
         <v>45618</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68414,7 +68414,7 @@
         <v>46268</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68487,7 +68487,7 @@
         <v>46273</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68560,7 +68560,7 @@
         <v>45562</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68638,7 +68638,7 @@
         <v>45509</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68716,7 +68716,7 @@
         <v>44908</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68794,7 +68794,7 @@
         <v>46009</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68867,7 +68867,7 @@
         <v>45677</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68940,7 +68940,7 @@
         <v>46273</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69013,7 +69013,7 @@
         <v>45568</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69086,7 +69086,7 @@
         <v>44978</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69159,7 +69159,7 @@
         <v>46274</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69232,7 +69232,7 @@
         <v>46274</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69305,7 +69305,7 @@
         <v>46277</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69378,7 +69378,7 @@
         <v>46279</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69451,7 +69451,7 @@
         <v>45702</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69524,7 +69524,7 @@
         <v>45126</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69597,7 +69597,7 @@
         <v>45084</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69670,7 +69670,7 @@
         <v>45722</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69743,7 +69743,7 @@
         <v>46239</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69816,7 +69816,7 @@
         <v>46241</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69894,7 +69894,7 @@
         <v>45754</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69967,7 +69967,7 @@
         <v>44806</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70040,7 +70040,7 @@
         <v>46240</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70118,7 +70118,7 @@
         <v>45812</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70191,7 +70191,7 @@
         <v>45372</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70264,7 +70264,7 @@
         <v>45121</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70337,7 +70337,7 @@
         <v>46286</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70410,7 +70410,7 @@
         <v>46286</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70483,7 +70483,7 @@
         <v>44743</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70556,7 +70556,7 @@
         <v>44991</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70629,7 +70629,7 @@
         <v>46287</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70702,7 +70702,7 @@
         <v>45035</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70775,7 +70775,7 @@
         <v>45614</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70848,7 +70848,7 @@
         <v>46244</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70921,7 +70921,7 @@
         <v>46119</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70999,7 +70999,7 @@
         <v>44851</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71077,7 +71077,7 @@
         <v>46287</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71150,7 +71150,7 @@
         <v>46244</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71223,7 +71223,7 @@
         <v>44988</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71296,7 +71296,7 @@
         <v>45705</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71369,7 +71369,7 @@
         <v>45089</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71442,7 +71442,7 @@
         <v>45356</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71515,7 +71515,7 @@
         <v>46246</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71588,7 +71588,7 @@
         <v>46224</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71661,7 +71661,7 @@
         <v>46246</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71734,7 +71734,7 @@
         <v>46289</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71807,7 +71807,7 @@
         <v>45323</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71885,7 +71885,7 @@
         <v>45373</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71958,7 +71958,7 @@
         <v>44924</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72031,7 +72031,7 @@
         <v>45940</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72104,7 +72104,7 @@
         <v>45621</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72177,7 +72177,7 @@
         <v>46292</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72250,7 +72250,7 @@
         <v>45126</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72323,7 +72323,7 @@
         <v>45253</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72396,7 +72396,7 @@
         <v>44810</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72469,7 +72469,7 @@
         <v>44923</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72542,7 +72542,7 @@
         <v>45187</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72615,7 +72615,7 @@
         <v>45076</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72688,7 +72688,7 @@
         <v>45524</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72761,7 +72761,7 @@
         <v>45099</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72834,7 +72834,7 @@
         <v>44628</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72907,7 +72907,7 @@
         <v>45119</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72980,7 +72980,7 @@
         <v>46252</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73053,7 +73053,7 @@
         <v>44988</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73126,7 +73126,7 @@
         <v>44887</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73199,7 +73199,7 @@
         <v>46251</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73272,7 +73272,7 @@
         <v>44868</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73345,7 +73345,7 @@
         <v>46294</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73418,7 +73418,7 @@
         <v>45126</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73491,7 +73491,7 @@
         <v>44565</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73564,7 +73564,7 @@
         <v>45188</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73637,7 +73637,7 @@
         <v>45546</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73710,7 +73710,7 @@
         <v>44651</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73783,7 +73783,7 @@
         <v>45323</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73861,7 +73861,7 @@
         <v>45012</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73934,7 +73934,7 @@
         <v>45181</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -74007,7 +74007,7 @@
         <v>44812</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74080,7 +74080,7 @@
         <v>45205</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74153,7 +74153,7 @@
         <v>46253</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74226,7 +74226,7 @@
         <v>46296</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74299,7 +74299,7 @@
         <v>46296</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74372,7 +74372,7 @@
         <v>46254</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74445,7 +74445,7 @@
         <v>46154</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74518,7 +74518,7 @@
         <v>44980</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74591,7 +74591,7 @@
         <v>44810</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74664,7 +74664,7 @@
         <v>45231</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74737,7 +74737,7 @@
         <v>45035</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74810,7 +74810,7 @@
         <v>45077</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74883,7 +74883,7 @@
         <v>44945</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74956,7 +74956,7 @@
         <v>45594</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -75029,7 +75029,7 @@
         <v>44721</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75102,7 +75102,7 @@
         <v>45300</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75175,7 +75175,7 @@
         <v>45210</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75248,7 +75248,7 @@
         <v>44903</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75321,7 +75321,7 @@
         <v>45065</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75394,7 +75394,7 @@
         <v>45224</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75467,7 +75467,7 @@
         <v>45607</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75540,7 +75540,7 @@
         <v>45075</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75613,7 +75613,7 @@
         <v>45223</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75686,7 +75686,7 @@
         <v>45223</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75759,7 +75759,7 @@
         <v>45071</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75832,7 +75832,7 @@
         <v>45071</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75905,7 +75905,7 @@
         <v>44642</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75978,7 +75978,7 @@
         <v>45301</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76051,7 +76051,7 @@
         <v>44712</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>45195</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76197,7 +76197,7 @@
         <v>45071</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76270,7 +76270,7 @@
         <v>45071</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76343,7 +76343,7 @@
         <v>45705</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76416,7 +76416,7 @@
         <v>45701</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76489,7 +76489,7 @@
         <v>45628</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76562,7 +76562,7 @@
         <v>45581</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76635,7 +76635,7 @@
         <v>45372</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76708,7 +76708,7 @@
         <v>45250</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76781,7 +76781,7 @@
         <v>44819</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76854,7 +76854,7 @@
         <v>45152</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76927,7 +76927,7 @@
         <v>45097</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -77000,7 +77000,7 @@
         <v>45131</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77073,7 +77073,7 @@
         <v>45441</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77146,7 +77146,7 @@
         <v>45131</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77219,7 +77219,7 @@
         <v>45615</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77292,7 +77292,7 @@
         <v>45033</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77365,7 +77365,7 @@
         <v>45307</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77438,7 +77438,7 @@
         <v>45764</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77511,7 +77511,7 @@
         <v>44886</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77584,7 +77584,7 @@
         <v>45226</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77657,7 +77657,7 @@
         <v>45306</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77730,7 +77730,7 @@
         <v>45548</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77803,7 +77803,7 @@
         <v>44985</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77876,7 +77876,7 @@
         <v>44985</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77949,7 +77949,7 @@
         <v>44995</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -78022,7 +78022,7 @@
         <v>45562</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78095,7 +78095,7 @@
         <v>45594</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78168,7 +78168,7 @@
         <v>45272</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78241,7 +78241,7 @@
         <v>45272</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78314,7 +78314,7 @@
         <v>44924</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78387,7 +78387,7 @@
         <v>45628</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78460,7 +78460,7 @@
         <v>44657</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78533,7 +78533,7 @@
         <v>44999</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78606,7 +78606,7 @@
         <v>45637</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78679,7 +78679,7 @@
         <v>45164</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78752,7 +78752,7 @@
         <v>45629</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78825,7 +78825,7 @@
         <v>45534</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78898,7 +78898,7 @@
         <v>45708</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78971,7 +78971,7 @@
         <v>44959</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79049,7 +79049,7 @@
         <v>45783</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79122,7 +79122,7 @@
         <v>45783</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79195,7 +79195,7 @@
         <v>45783</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79268,7 +79268,7 @@
         <v>45021</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79341,7 +79341,7 @@
         <v>45783</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79414,7 +79414,7 @@
         <v>45783</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79487,7 +79487,7 @@
         <v>45783</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79560,7 +79560,7 @@
         <v>45708</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         <v>45628</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79706,7 +79706,7 @@
         <v>45161</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79779,7 +79779,7 @@
         <v>45734</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         <v>45372</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79925,7 +79925,7 @@
         <v>45110</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79998,7 +79998,7 @@
         <v>44820</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80071,7 +80071,7 @@
         <v>45537</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80144,7 +80144,7 @@
         <v>45226</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80217,7 +80217,7 @@
         <v>45527</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80290,7 +80290,7 @@
         <v>45593</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80363,7 +80363,7 @@
         <v>44638</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80436,7 +80436,7 @@
         <v>45000</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80509,7 +80509,7 @@
         <v>44644</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80582,7 +80582,7 @@
         <v>44820</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80655,7 +80655,7 @@
         <v>44643</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80728,7 +80728,7 @@
         <v>45412</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80801,7 +80801,7 @@
         <v>45272</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80874,7 +80874,7 @@
         <v>45168</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80947,7 +80947,7 @@
         <v>45378</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -81020,7 +81020,7 @@
         <v>44643</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81093,7 +81093,7 @@
         <v>44655</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81166,7 +81166,7 @@
         <v>45554</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81239,7 +81239,7 @@
         <v>44484</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81312,7 +81312,7 @@
         <v>45574</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81385,7 +81385,7 @@
         <v>45615</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45526</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45597</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45033</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81677,7 +81677,7 @@
         <v>45553</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45357</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81823,7 +81823,7 @@
         <v>45427</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81896,7 +81896,7 @@
         <v>44642</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81969,7 +81969,7 @@
         <v>45447</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82042,7 +82042,7 @@
         <v>45294</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82115,7 +82115,7 @@
         <v>45000</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82188,7 +82188,7 @@
         <v>45168</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82261,7 +82261,7 @@
         <v>45044</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82334,7 +82334,7 @@
         <v>45267</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82407,7 +82407,7 @@
         <v>45442</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82480,7 +82480,7 @@
         <v>44960</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82553,7 +82553,7 @@
         <v>44973</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82626,7 +82626,7 @@
         <v>45560</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82699,7 +82699,7 @@
         <v>45357</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82772,7 +82772,7 @@
         <v>44882</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82845,7 +82845,7 @@
         <v>45110</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82918,7 +82918,7 @@
         <v>45755</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82991,7 +82991,7 @@
         <v>45637</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83064,7 +83064,7 @@
         <v>45645</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83137,7 +83137,7 @@
         <v>45713</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83210,7 +83210,7 @@
         <v>45742</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83283,7 +83283,7 @@
         <v>45720</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83356,7 +83356,7 @@
         <v>45632</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83429,7 +83429,7 @@
         <v>45631</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83502,7 +83502,7 @@
         <v>45713</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83575,7 +83575,7 @@
         <v>45789</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83648,7 +83648,7 @@
         <v>45818</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83721,7 +83721,7 @@
         <v>45831</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83794,7 +83794,7 @@
         <v>45831</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83867,7 +83867,7 @@
         <v>45895</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83940,7 +83940,7 @@
         <v>45895</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -84013,7 +84013,7 @@
         <v>45894</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84086,7 +84086,7 @@
         <v>46027</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84159,7 +84159,7 @@
         <v>46024</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84232,7 +84232,7 @@
         <v>46024</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84305,7 +84305,7 @@
         <v>46029</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84383,7 +84383,7 @@
         <v>46063</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84456,7 +84456,7 @@
         <v>46062</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84529,7 +84529,7 @@
         <v>46064</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84602,7 +84602,7 @@
         <v>46150</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84675,7 +84675,7 @@
         <v>46150</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84748,7 +84748,7 @@
         <v>46156</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84821,7 +84821,7 @@
         <v>46161</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84894,7 +84894,7 @@
         <v>46161</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84967,7 +84967,7 @@
         <v>46209</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -85045,7 +85045,7 @@
         <v>46266</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -85118,7 +85118,7 @@
         <v>46279</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85196,7 +85196,7 @@
         <v>46279</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>46008</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45568</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45224</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45530</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45211</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>46161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45103</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45476</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45194</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45272</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45819</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>46150</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45357</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45733</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45236</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>45181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>46198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45152</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45212</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>46272</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45111</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45042</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45013</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45427</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45054</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>46006</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45483</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45510</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45561</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45978</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45191</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46106</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45012</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45617</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45832</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>45833</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>44985</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45805</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>44894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45274</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45266</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44820</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>45875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45961</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44645</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45672</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44928</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45079</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46204</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45205</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45686</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45012</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45334</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>46280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45005</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45527</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45555</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45061</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45372</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45020</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45749</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45611</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44616</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45335</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44978</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44831</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44672</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44869</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45772</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>46168</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46202</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46206</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44568</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44853</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44622</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44508</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44818</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44848</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44510</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44635</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44510</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44742</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44592</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44714</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44623</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44749</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44474</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44880</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44837</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44861</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44482</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44476</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44502</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44495</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44476</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44576</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44825</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44565</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>44760</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44732</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44550</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44810</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44536</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44588</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44810</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44845</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44862</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44764</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44739</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44742</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44515</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44592</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44517</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44595</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>44879</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44831</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44882</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44817</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>44537</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44806</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44810</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44530</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44882</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44806</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44606</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44809</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44610</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44715</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>44497</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44495</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45748</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45187</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>44929</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44764</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45082</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45614</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45065</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45097</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>44850</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44825</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45068</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44928</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45279</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45761</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45103</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45218</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45551</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45684</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44974</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45735</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>44874</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44617</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45714</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45617</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45188</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45111</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45110</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45602</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44985</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45345</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45166</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44883</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45756</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45510</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>44959</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45758</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45643</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44823</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45681</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45275</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46006</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46006</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>46006</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45775</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>44634</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45510</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45628</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>46006</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>46006</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45260</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>46008</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46008</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>46008</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45719</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45593</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44858</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45441</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45715</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45181</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44852</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>46014</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44634</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>46020</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45888</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45888</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45226</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>45672</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45223</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45837</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>44882</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45895</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>45895</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45895</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>46024</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44923</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45730</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45895</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45895</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45895</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45700</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45897</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44851</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>45993</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45993</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45826</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45279</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>46030</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45103</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45461</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45792</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45278</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44706</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45793</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45163</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45902</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>45905</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45905</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44817</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45908</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45910</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45596</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45707</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44927</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45796</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45796</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45796</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>46045</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45876</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>46045</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46045</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45911</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45911</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>46045</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>46045</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45596</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45914</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45183</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45272</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45796</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45106</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45916</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45916</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45917</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45917</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45446</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45562</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45156</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45253</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>46050</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45645</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>46050</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46054</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>46054</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46054</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45923</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45923</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45924</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45923</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45216</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45925</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>45925</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45925</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45925</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>45925</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>46059</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>46059</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45686</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>46059</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>46062</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>46063</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>46063</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>46063</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45350</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45350</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>46063</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45546</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45202</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>45126</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46069</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>44928</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44582</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45734</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45215</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45811</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45811</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45811</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45938</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45940</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45305</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46078</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45945</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45945</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>46076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>46077</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44886</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45317</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45946</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45950</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>45950</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45950</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>45371</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>45742</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45735</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45911</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>45950</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44810</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44908</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>45264</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>45412</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>45097</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>45957</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>45957</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45957</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45957</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45888</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>46084</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>46087</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>45735</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45959</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44809</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45148</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45961</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>46091</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45961</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44945</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45964</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>45964</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>46091</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45684</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45757</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45205</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>46094</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>44603</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>44603</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>44603</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>46094</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>45686</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45817</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45646</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>46097</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>46097</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>44942</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>46097</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>46097</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>46097</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>46097</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44993</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>46097</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>46098</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>46097</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45510</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45162</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45973</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45212</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46104</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45629</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45762</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45518</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>46106</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45525</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45977</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45978</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>45818</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45225</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>45225</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>45099</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>46104</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45978</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45301</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45527</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45617</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44810</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>45280</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45257</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>46107</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45119</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45981</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45981</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>46107</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         <v>46107</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>45980</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>46107</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>45980</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45645</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>44894</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>45093</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>46111</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45985</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>46111</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>46112</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41148,7 +41148,7 @@
         <v>45646</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>45632</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>46113</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>46113</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>46113</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45339</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>46113</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>46113</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45328</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>45988</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>45197</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>46120</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44923</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>45700</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45825</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>46119</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45989</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>46119</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45824</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>45992</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>44487</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>45112</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>45992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45992</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45604</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45793</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44903</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>45995</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45826</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45243</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45994</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>46128</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45993</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>44670</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43708,7 +43708,7 @@
         <v>45137</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45831</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45831</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>45831</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45831</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45831</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44146,7 +44146,7 @@
         <v>45833</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45567</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>45167</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>44740</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45272</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45440</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>46134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46134</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45207</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45077</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45069</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>46134</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>44656</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45085</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
         <v>45355</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>44809</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>44809</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45835</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45835</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45645</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45880</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45903</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>44991</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45837</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45162</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45908</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45005</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>44896</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45370</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45215</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45546</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>45840</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>45755</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45831</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45742</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45840</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>46139</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>45734</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>44585</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45679</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>44999</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>45842</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>45475</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>45723</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45775</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>45845</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45679</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45635</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45730</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45483</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>44991</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47874,7 +47874,7 @@
         <v>44991</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>45848</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45848</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45366</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45811</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45069</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45748</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45764</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>45733</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45784</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>45195</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>46139</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45852</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>44634</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45727</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>44991</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44991</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45567</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>44959</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>44959</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45187</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45838</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45176</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45181</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45714</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>44523</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45168</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45224</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45667</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45818</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45097</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>44573</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>45742</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45463</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>45798</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45644</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45109</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45530</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>44820</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45811</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>45811</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45476</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>45476</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>45111</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>44846</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45860</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>45916</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>44848</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45733</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45842</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>46140</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45845</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45089</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>44565</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>44565</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>45730</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45068</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46140</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46140</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45315</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>45672</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45470</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>45602</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>45339</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>45097</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>45274</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>45396</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45145</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>44881</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>45169</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>45869</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53072,7 +53072,7 @@
         <v>45614</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>45701</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45847</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53296,7 +53296,7 @@
         <v>45739</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>45783</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45005</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>44917</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>45595</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>44867</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45701</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>46057</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>46059</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>45425</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>45099</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45427</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>44621</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>45079</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>44538</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45394</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>45869</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45271</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>44847</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54688,7 +54688,7 @@
         <v>45026</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54761,7 +54761,7 @@
         <v>45301</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54834,7 +54834,7 @@
         <v>46146</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45225</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45116</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>45116</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55126,7 +55126,7 @@
         <v>45610</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55199,7 +55199,7 @@
         <v>46146</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55272,7 +55272,7 @@
         <v>45647</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55345,7 +55345,7 @@
         <v>45156</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55418,7 +55418,7 @@
         <v>45218</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>44971</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         <v>45714</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45754</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55710,7 +55710,7 @@
         <v>45349</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55783,7 +55783,7 @@
         <v>44881</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>44937</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45629</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56002,7 +56002,7 @@
         <v>45211</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56075,7 +56075,7 @@
         <v>45610</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56148,7 +56148,7 @@
         <v>44620</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45247</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56294,7 +56294,7 @@
         <v>45145</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56367,7 +56367,7 @@
         <v>45394</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56440,7 +56440,7 @@
         <v>44715</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45301</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45481</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>44515</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>44515</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45831</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45628</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45211</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57024,7 +57024,7 @@
         <v>45750</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57097,7 +57097,7 @@
         <v>45869</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57175,7 +57175,7 @@
         <v>45824</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>45603</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57326,7 +57326,7 @@
         <v>45301</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>44860</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57472,7 +57472,7 @@
         <v>45676</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>46150</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>46150</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57691,7 +57691,7 @@
         <v>45324</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57764,7 +57764,7 @@
         <v>46154</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57837,7 +57837,7 @@
         <v>46155</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57910,7 +57910,7 @@
         <v>45811</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45845</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58056,7 +58056,7 @@
         <v>45533</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58134,7 +58134,7 @@
         <v>45749</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58207,7 +58207,7 @@
         <v>46155</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58280,7 +58280,7 @@
         <v>45875</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>45510</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58426,7 +58426,7 @@
         <v>46155</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>45874</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58572,7 +58572,7 @@
         <v>46155</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>46059</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>46079</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45764</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58869,7 +58869,7 @@
         <v>45181</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>45097</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45356</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>46160</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45875</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>45264</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59307,7 +59307,7 @@
         <v>44895</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>44895</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>44895</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>45630</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59599,7 +59599,7 @@
         <v>45546</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59677,7 +59677,7 @@
         <v>45048</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59750,7 +59750,7 @@
         <v>46161</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59823,7 +59823,7 @@
         <v>45754</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59896,7 +59896,7 @@
         <v>45639</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59969,7 +59969,7 @@
         <v>45281</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>44886</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60115,7 +60115,7 @@
         <v>45265</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60188,7 +60188,7 @@
         <v>45881</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60261,7 +60261,7 @@
         <v>45179</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60334,7 +60334,7 @@
         <v>45756</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>45880</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60480,7 +60480,7 @@
         <v>46104</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>46170</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>46170</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60699,7 +60699,7 @@
         <v>46170</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60772,7 +60772,7 @@
         <v>45561</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60845,7 +60845,7 @@
         <v>45880</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>46174</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60991,7 +60991,7 @@
         <v>46174</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61064,7 +61064,7 @@
         <v>45881</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61137,7 +61137,7 @@
         <v>45401</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>45775</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61283,7 +61283,7 @@
         <v>46171</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61356,7 +61356,7 @@
         <v>45610</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61429,7 +61429,7 @@
         <v>46176</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61502,7 +61502,7 @@
         <v>45748</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61575,7 +61575,7 @@
         <v>46176</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61648,7 +61648,7 @@
         <v>44900</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45275</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>45715</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>44508</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>44946</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>45239</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>46182</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>46182</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>46182</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>44742</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>46184</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>44974</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>46184</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>44587</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>45315</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>44959</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>44959</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>45036</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62967,7 +62967,7 @@
         <v>45593</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>45483</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45628</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>45181</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>45390</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>44551</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>46191</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63483,7 +63483,7 @@
         <v>45267</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63556,7 +63556,7 @@
         <v>45131</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63629,7 +63629,7 @@
         <v>46195</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63702,7 +63702,7 @@
         <v>45204</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>44971</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         <v>44750</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45084</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>46197</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64067,7 +64067,7 @@
         <v>46198</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64140,7 +64140,7 @@
         <v>45121</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64213,7 +64213,7 @@
         <v>45188</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64286,7 +64286,7 @@
         <v>45056</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64359,7 +64359,7 @@
         <v>45621</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>46198</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64505,7 +64505,7 @@
         <v>45908</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64578,7 +64578,7 @@
         <v>45604</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64651,7 +64651,7 @@
         <v>44802</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>46204</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64797,7 +64797,7 @@
         <v>45240</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64870,7 +64870,7 @@
         <v>45441</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64943,7 +64943,7 @@
         <v>46205</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>44825</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65089,7 +65089,7 @@
         <v>46206</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65162,7 +65162,7 @@
         <v>46206</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65235,7 +65235,7 @@
         <v>45769</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65308,7 +65308,7 @@
         <v>45119</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65381,7 +65381,7 @@
         <v>45273</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65454,7 +65454,7 @@
         <v>45081</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65527,7 +65527,7 @@
         <v>45162</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65605,7 +65605,7 @@
         <v>45463</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65683,7 +65683,7 @@
         <v>46206</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65756,7 +65756,7 @@
         <v>46206</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65829,7 +65829,7 @@
         <v>46206</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65902,7 +65902,7 @@
         <v>45614</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65980,7 +65980,7 @@
         <v>45615</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66053,7 +66053,7 @@
         <v>46211</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66126,7 +66126,7 @@
         <v>45055</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66199,7 +66199,7 @@
         <v>45349</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66272,7 +66272,7 @@
         <v>46211</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66345,7 +66345,7 @@
         <v>44915</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66418,7 +66418,7 @@
         <v>46216</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66491,7 +66491,7 @@
         <v>45610</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66564,7 +66564,7 @@
         <v>45183</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66637,7 +66637,7 @@
         <v>45509</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66715,7 +66715,7 @@
         <v>45726</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66788,7 +66788,7 @@
         <v>46259</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66861,7 +66861,7 @@
         <v>46063</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66934,7 +66934,7 @@
         <v>45168</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67007,7 +67007,7 @@
         <v>46184</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67080,7 +67080,7 @@
         <v>45614</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67158,7 +67158,7 @@
         <v>45614</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67236,7 +67236,7 @@
         <v>45092</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67309,7 +67309,7 @@
         <v>45146</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67382,7 +67382,7 @@
         <v>44551</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45620</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67528,7 +67528,7 @@
         <v>45236</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67601,7 +67601,7 @@
         <v>44960</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>46265</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>45188</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         <v>46266</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67898,7 +67898,7 @@
         <v>44938</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67971,7 +67971,7 @@
         <v>44908</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>44946</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68122,7 +68122,7 @@
         <v>45357</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68195,7 +68195,7 @@
         <v>44712</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68268,7 +68268,7 @@
         <v>45217</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68341,7 +68341,7 @@
         <v>45618</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68414,7 +68414,7 @@
         <v>46268</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68487,7 +68487,7 @@
         <v>46273</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68560,7 +68560,7 @@
         <v>45562</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68638,7 +68638,7 @@
         <v>45509</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68716,7 +68716,7 @@
         <v>44908</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68794,7 +68794,7 @@
         <v>46009</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68867,7 +68867,7 @@
         <v>45677</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68940,7 +68940,7 @@
         <v>46273</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69013,7 +69013,7 @@
         <v>45568</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69086,7 +69086,7 @@
         <v>44978</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69159,7 +69159,7 @@
         <v>46274</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69232,7 +69232,7 @@
         <v>46274</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69305,7 +69305,7 @@
         <v>46277</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69378,7 +69378,7 @@
         <v>46279</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69451,7 +69451,7 @@
         <v>45702</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69524,7 +69524,7 @@
         <v>45126</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69597,7 +69597,7 @@
         <v>45084</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69670,7 +69670,7 @@
         <v>45722</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69743,7 +69743,7 @@
         <v>46239</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69816,7 +69816,7 @@
         <v>46241</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69894,7 +69894,7 @@
         <v>45754</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69967,7 +69967,7 @@
         <v>44806</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70040,7 +70040,7 @@
         <v>46240</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70118,7 +70118,7 @@
         <v>45812</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70191,7 +70191,7 @@
         <v>45372</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70264,7 +70264,7 @@
         <v>45121</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70337,7 +70337,7 @@
         <v>46286</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70410,7 +70410,7 @@
         <v>46286</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70483,7 +70483,7 @@
         <v>44743</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70556,7 +70556,7 @@
         <v>44991</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70629,7 +70629,7 @@
         <v>46287</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70702,7 +70702,7 @@
         <v>45035</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70775,7 +70775,7 @@
         <v>45614</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70848,7 +70848,7 @@
         <v>46244</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70921,7 +70921,7 @@
         <v>46119</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70999,7 +70999,7 @@
         <v>44851</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71077,7 +71077,7 @@
         <v>46287</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71150,7 +71150,7 @@
         <v>46244</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71223,7 +71223,7 @@
         <v>44988</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71296,7 +71296,7 @@
         <v>45705</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71369,7 +71369,7 @@
         <v>45089</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71442,7 +71442,7 @@
         <v>45356</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71515,7 +71515,7 @@
         <v>46246</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71588,7 +71588,7 @@
         <v>46224</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71661,7 +71661,7 @@
         <v>46246</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71734,7 +71734,7 @@
         <v>46289</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71807,7 +71807,7 @@
         <v>45323</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71885,7 +71885,7 @@
         <v>45373</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71958,7 +71958,7 @@
         <v>44924</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72031,7 +72031,7 @@
         <v>45940</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72104,7 +72104,7 @@
         <v>45621</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72177,7 +72177,7 @@
         <v>46292</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72250,7 +72250,7 @@
         <v>45126</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72323,7 +72323,7 @@
         <v>45253</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72396,7 +72396,7 @@
         <v>44810</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72469,7 +72469,7 @@
         <v>44923</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72542,7 +72542,7 @@
         <v>45187</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72615,7 +72615,7 @@
         <v>45076</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72688,7 +72688,7 @@
         <v>45524</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72761,7 +72761,7 @@
         <v>45099</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72834,7 +72834,7 @@
         <v>44628</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72907,7 +72907,7 @@
         <v>45119</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72980,7 +72980,7 @@
         <v>46252</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73053,7 +73053,7 @@
         <v>44988</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73126,7 +73126,7 @@
         <v>44887</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73199,7 +73199,7 @@
         <v>46251</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73272,7 +73272,7 @@
         <v>44868</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73345,7 +73345,7 @@
         <v>46294</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73418,7 +73418,7 @@
         <v>45126</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73491,7 +73491,7 @@
         <v>44565</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73564,7 +73564,7 @@
         <v>45188</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73637,7 +73637,7 @@
         <v>45546</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73710,7 +73710,7 @@
         <v>44651</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73783,7 +73783,7 @@
         <v>45323</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73861,7 +73861,7 @@
         <v>45012</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73934,7 +73934,7 @@
         <v>45181</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -74007,7 +74007,7 @@
         <v>44812</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74080,7 +74080,7 @@
         <v>45205</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74153,7 +74153,7 @@
         <v>46253</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74226,7 +74226,7 @@
         <v>46296</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74299,7 +74299,7 @@
         <v>46296</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74372,7 +74372,7 @@
         <v>46254</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74445,7 +74445,7 @@
         <v>46154</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74518,7 +74518,7 @@
         <v>44980</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74591,7 +74591,7 @@
         <v>44810</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74664,7 +74664,7 @@
         <v>45231</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74737,7 +74737,7 @@
         <v>45035</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74810,7 +74810,7 @@
         <v>45077</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74883,7 +74883,7 @@
         <v>44945</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74956,7 +74956,7 @@
         <v>45594</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -75029,7 +75029,7 @@
         <v>44721</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75102,7 +75102,7 @@
         <v>45300</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75175,7 +75175,7 @@
         <v>45210</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75248,7 +75248,7 @@
         <v>44903</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75321,7 +75321,7 @@
         <v>45065</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75394,7 +75394,7 @@
         <v>45224</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75467,7 +75467,7 @@
         <v>45607</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75540,7 +75540,7 @@
         <v>45075</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75613,7 +75613,7 @@
         <v>45223</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75686,7 +75686,7 @@
         <v>45223</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75759,7 +75759,7 @@
         <v>45071</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75832,7 +75832,7 @@
         <v>45071</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75905,7 +75905,7 @@
         <v>44642</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75978,7 +75978,7 @@
         <v>45301</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76051,7 +76051,7 @@
         <v>44712</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76124,7 +76124,7 @@
         <v>45195</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76197,7 +76197,7 @@
         <v>45071</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76270,7 +76270,7 @@
         <v>45071</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76343,7 +76343,7 @@
         <v>45705</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76416,7 +76416,7 @@
         <v>45701</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76489,7 +76489,7 @@
         <v>45628</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76562,7 +76562,7 @@
         <v>45581</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76635,7 +76635,7 @@
         <v>45372</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76708,7 +76708,7 @@
         <v>45250</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76781,7 +76781,7 @@
         <v>44819</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76854,7 +76854,7 @@
         <v>45152</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76927,7 +76927,7 @@
         <v>45097</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -77000,7 +77000,7 @@
         <v>45131</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77073,7 +77073,7 @@
         <v>45441</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77146,7 +77146,7 @@
         <v>45131</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77219,7 +77219,7 @@
         <v>45615</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77292,7 +77292,7 @@
         <v>45033</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77365,7 +77365,7 @@
         <v>45307</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77438,7 +77438,7 @@
         <v>45764</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77511,7 +77511,7 @@
         <v>44886</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77584,7 +77584,7 @@
         <v>45226</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77657,7 +77657,7 @@
         <v>45306</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77730,7 +77730,7 @@
         <v>45548</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77803,7 +77803,7 @@
         <v>44985</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77876,7 +77876,7 @@
         <v>44985</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77949,7 +77949,7 @@
         <v>44995</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -78022,7 +78022,7 @@
         <v>45562</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78095,7 +78095,7 @@
         <v>45594</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78168,7 +78168,7 @@
         <v>45272</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78241,7 +78241,7 @@
         <v>45272</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78314,7 +78314,7 @@
         <v>44924</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78387,7 +78387,7 @@
         <v>45628</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78460,7 +78460,7 @@
         <v>44657</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78533,7 +78533,7 @@
         <v>44999</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78606,7 +78606,7 @@
         <v>45637</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78679,7 +78679,7 @@
         <v>45164</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78752,7 +78752,7 @@
         <v>45629</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78825,7 +78825,7 @@
         <v>45534</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78898,7 +78898,7 @@
         <v>45708</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78971,7 +78971,7 @@
         <v>44959</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79049,7 +79049,7 @@
         <v>45783</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79122,7 +79122,7 @@
         <v>45783</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79195,7 +79195,7 @@
         <v>45783</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79268,7 +79268,7 @@
         <v>45021</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79341,7 +79341,7 @@
         <v>45783</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79414,7 +79414,7 @@
         <v>45783</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79487,7 +79487,7 @@
         <v>45783</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79560,7 +79560,7 @@
         <v>45708</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         <v>45628</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79706,7 +79706,7 @@
         <v>45161</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79779,7 +79779,7 @@
         <v>45734</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         <v>45372</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79925,7 +79925,7 @@
         <v>45110</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79998,7 +79998,7 @@
         <v>44820</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80071,7 +80071,7 @@
         <v>45537</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80144,7 +80144,7 @@
         <v>45226</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80217,7 +80217,7 @@
         <v>45527</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80290,7 +80290,7 @@
         <v>45593</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80363,7 +80363,7 @@
         <v>44638</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80436,7 +80436,7 @@
         <v>45000</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80509,7 +80509,7 @@
         <v>44644</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80582,7 +80582,7 @@
         <v>44820</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80655,7 +80655,7 @@
         <v>44643</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80728,7 +80728,7 @@
         <v>45412</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80801,7 +80801,7 @@
         <v>45272</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80874,7 +80874,7 @@
         <v>45168</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80947,7 +80947,7 @@
         <v>45378</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -81020,7 +81020,7 @@
         <v>44643</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81093,7 +81093,7 @@
         <v>44655</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81166,7 +81166,7 @@
         <v>45554</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81239,7 +81239,7 @@
         <v>44484</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81312,7 +81312,7 @@
         <v>45574</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81385,7 +81385,7 @@
         <v>45615</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45526</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45597</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45033</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81677,7 +81677,7 @@
         <v>45553</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45357</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81823,7 +81823,7 @@
         <v>45427</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81896,7 +81896,7 @@
         <v>44642</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81969,7 +81969,7 @@
         <v>45447</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82042,7 +82042,7 @@
         <v>45294</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82115,7 +82115,7 @@
         <v>45000</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82188,7 +82188,7 @@
         <v>45168</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82261,7 +82261,7 @@
         <v>45044</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82334,7 +82334,7 @@
         <v>45267</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82407,7 +82407,7 @@
         <v>45442</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82480,7 +82480,7 @@
         <v>44960</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82553,7 +82553,7 @@
         <v>44973</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82626,7 +82626,7 @@
         <v>45560</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82699,7 +82699,7 @@
         <v>45357</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82772,7 +82772,7 @@
         <v>44882</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82845,7 +82845,7 @@
         <v>45110</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82918,7 +82918,7 @@
         <v>45755</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82991,7 +82991,7 @@
         <v>45637</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83064,7 +83064,7 @@
         <v>45645</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83137,7 +83137,7 @@
         <v>45713</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83210,7 +83210,7 @@
         <v>45742</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83283,7 +83283,7 @@
         <v>45720</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83356,7 +83356,7 @@
         <v>45632</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83429,7 +83429,7 @@
         <v>45631</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83502,7 +83502,7 @@
         <v>45713</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83575,7 +83575,7 @@
         <v>45789</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83648,7 +83648,7 @@
         <v>45818</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83721,7 +83721,7 @@
         <v>45831</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83794,7 +83794,7 @@
         <v>45831</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83867,7 +83867,7 @@
         <v>45895</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83940,7 +83940,7 @@
         <v>45895</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -84013,7 +84013,7 @@
         <v>45894</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84086,7 +84086,7 @@
         <v>46027</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84159,7 +84159,7 @@
         <v>46024</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84232,7 +84232,7 @@
         <v>46024</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84305,7 +84305,7 @@
         <v>46029</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84383,7 +84383,7 @@
         <v>46063</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84456,7 +84456,7 @@
         <v>46062</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84529,7 +84529,7 @@
         <v>46064</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84602,7 +84602,7 @@
         <v>46150</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84675,7 +84675,7 @@
         <v>46150</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84748,7 +84748,7 @@
         <v>46156</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84821,7 +84821,7 @@
         <v>46161</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84894,7 +84894,7 @@
         <v>46161</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84967,7 +84967,7 @@
         <v>46209</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -85045,7 +85045,7 @@
         <v>46266</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -85118,7 +85118,7 @@
         <v>46279</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85196,7 +85196,7 @@
         <v>46279</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>45224</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>45211</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>46161</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45086</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45126</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>45236</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>45476</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45357</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45512</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>45272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44610</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45078</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45103</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45194</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45152</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45978</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45819</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45733</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45212</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45111</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45996</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>46150</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>46196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45042</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45013</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45054</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45372</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45686</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45061</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45005</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45594</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45266</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44985</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45617</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45561</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>44928</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>45555</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45527</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45079</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45334</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45510</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44645</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45205</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45832</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45020</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45012</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45833</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45978</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>45869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45274</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44894</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45483</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45875</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>46106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>46006</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45282</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45191</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>45012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45937</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45805</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45961</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45672</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>46204</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>46266</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46280</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44616</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44672</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45611</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44869</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45772</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>46168</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46202</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46206</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44568</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44853</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44622</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44508</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44818</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44848</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44635</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44510</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44742</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44592</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44714</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44623</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44749</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44880</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44837</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44861</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44482</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44502</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44760</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44495</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44537</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44806</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44810</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44732</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44742</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44530</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44576</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>44550</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44536</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44515</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44810</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44592</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44810</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44517</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44595</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44588</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>44879</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>44888</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44882</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44845</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44862</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44831</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44825</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>44882</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44806</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44565</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44712</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>44809</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44764</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44606</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44817</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44610</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44739</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44900</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44867</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44497</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44908</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44825</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45181</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45119</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45324</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45366</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45546</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45546</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44495</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45510</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44868</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44882</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45089</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45188</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45085</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44991</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>44991</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44809</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45463</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45440</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45684</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45629</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44923</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45441</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45048</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45602</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45702</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45672</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45764</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>44846</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45187</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44928</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>45187</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45551</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>44896</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>44819</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44883</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44764</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45614</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45068</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45099</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>45401</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45103</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>45092</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>44810</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45300</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>44810</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45103</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45595</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45307</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45239</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45373</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44895</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44895</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44895</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45301</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45065</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45700</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45065</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45272</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>44924</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45121</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45197</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45126</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45119</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44946</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45632</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45272</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45210</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45461</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45069</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45126</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45317</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45275</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45603</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45748</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45183</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45223</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45223</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45181</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45614</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45412</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45112</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45561</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>44823</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45323</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45755</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>44993</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45119</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45280</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45097</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45275</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45272</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45223</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45097</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45250</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>44903</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45106</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45260</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45546</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45278</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45355</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45315</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45265</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>44894</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45339</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44971</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45726</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45715</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45610</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45748</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45749</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44886</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44850</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45888</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45339</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45281</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45758</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45715</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45888</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>44587</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>45483</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45509</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45775</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45279</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45470</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45097</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45837</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45463</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45548</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45610</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45594</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45077</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>44945</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45372</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45476</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45826</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45895</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45895</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45895</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45895</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45895</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45895</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45897</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45714</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45075</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45635</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>44817</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45672</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45722</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45639</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44523</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45902</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45156</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45164</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44508</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45730</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>45441</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45306</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44656</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45908</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>44908</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>45905</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>45905</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>44915</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45910</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45181</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45629</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>45534</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45567</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45707</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45099</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45911</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45357</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45911</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45708</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45754</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45876</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44959</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>44848</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45137</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45916</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44874</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45646</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45783</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45783</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45783</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>45162</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45783</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45783</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45161</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45021</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45914</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45916</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45783</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45617</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45181</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>45390</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>45148</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45708</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45917</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>45168</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45188</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44985</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>44985</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45116</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45116</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45370</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44937</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45215</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>45681</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45917</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45217</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45273</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45628</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45525</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45533</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45372</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45562</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45593</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44886</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45734</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>44995</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45923</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45923</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>45923</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45350</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45350</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45510</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45524</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>45527</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>45349</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45756</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45925</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45925</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45925</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>45924</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45166</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45628</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>45925</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45925</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45089</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44999</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>45629</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>45056</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45792</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45188</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44942</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45510</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45610</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45126</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45637</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45212</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45796</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45796</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45719</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45596</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>45084</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45372</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>44670</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45614</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45246</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45216</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45793</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>45796</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>44603</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44603</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>44603</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>45345</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>45110</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45796</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45596</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45167</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44582</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45614</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>44927</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45156</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45645</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45071</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45071</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44573</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45562</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>44988</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45427</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45176</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>45441</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45734</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45705</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45253</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45183</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45082</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45205</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45205</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44945</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45938</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45769</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44642</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45243</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45628</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44634</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>44740</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45371</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45615</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45226</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45628</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45940</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45811</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45811</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45811</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44946</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45069</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44617</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45945</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45945</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45946</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45677</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45240</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45084</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>45686</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45617</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45950</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44634</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45179</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45762</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45817</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>44959</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>44923</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>44923</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45518</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45818</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>45950</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44721</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45614</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>44959</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45301</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45628</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>44851</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45824</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45621</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45618</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45826</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>45686</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46225,7 +46225,7 @@
         <v>45950</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45950</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45825</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45701</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45700</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45610</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>44628</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45793</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>44634</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>45446</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>44928</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45831</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45181</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45831</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45831</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45831</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45831</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>44851</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45831</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>45195</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45684</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45911</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45957</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45957</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45888</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45957</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45602</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45957</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45959</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>45833</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>45961</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45163</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>45323</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>44706</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45964</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45152</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45964</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45126</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45131</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45835</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45961</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45645</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>45837</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45835</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45840</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45187</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45840</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45509</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44999</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>44750</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45581</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>44802</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>45225</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45645</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>44743</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45131</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50338,7 +50338,7 @@
         <v>45207</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45756</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45842</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45231</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45775</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45264</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45630</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>45748</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45723</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>45848</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45848</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>44825</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45973</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>45730</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45811</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45852</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45315</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45977</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>45978</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45667</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51798,7 +51798,7 @@
         <v>45204</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45215</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>45811</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45328</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>44980</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45109</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45530</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>45860</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45224</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52455,7 +52455,7 @@
         <v>45225</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45510</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45257</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45978</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>45162</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>44988</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45869</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45869</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45869</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45224</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45481</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45783</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45026</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>44847</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>44881</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>44860</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>44917</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         <v>45099</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>45831</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45396</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>45701</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45646</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45425</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54149,7 +54149,7 @@
         <v>45035</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>45980</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>44515</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>44515</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45705</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>44538</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>44881</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45824</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54733,7 +54733,7 @@
         <v>44820</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>45394</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45701</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>45271</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45356</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>45301</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45211</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>45301</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>45847</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55390,7 +55390,7 @@
         <v>45628</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>44621</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>44715</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45739</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45218</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45394</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>45980</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>45145</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45676</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45750</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45195</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>45079</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45005</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>44908</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56417,7 +56417,7 @@
         <v>45274</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45145</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>44858</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56636,7 +56636,7 @@
         <v>45247</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56709,7 +56709,7 @@
         <v>44712</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>45033</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45647</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>45301</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45211</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45875</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>45168</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45875</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45981</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57366,7 +57366,7 @@
         <v>45714</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>45880</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>44852</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>45012</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>44991</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>45280</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45279</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45111</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45880</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45621</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58096,7 +58096,7 @@
         <v>45267</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58169,7 +58169,7 @@
         <v>45881</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58242,7 +58242,7 @@
         <v>45881</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>45643</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58388,7 +58388,7 @@
         <v>45264</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58461,7 +58461,7 @@
         <v>44991</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58534,7 +58534,7 @@
         <v>44991</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>45761</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>46097</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>46097</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>46094</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58899,7 +58899,7 @@
         <v>46097</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>46097</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59045,7 +59045,7 @@
         <v>46097</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59118,7 +59118,7 @@
         <v>45981</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59191,7 +59191,7 @@
         <v>45099</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45055</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59337,7 +59337,7 @@
         <v>45236</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59410,7 +59410,7 @@
         <v>45735</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>44565</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59556,7 +59556,7 @@
         <v>44565</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>45985</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45169</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59775,7 +59775,7 @@
         <v>44810</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>46104</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59921,7 +59921,7 @@
         <v>46104</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59994,7 +59994,7 @@
         <v>45714</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60067,7 +60067,7 @@
         <v>45225</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60140,7 +60140,7 @@
         <v>46107</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60213,7 +60213,7 @@
         <v>46106</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>46107</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>45071</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45071</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>45730</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>46107</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60651,7 +60651,7 @@
         <v>46107</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>44903</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45604</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>45076</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         <v>45077</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61016,7 +61016,7 @@
         <v>45988</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61089,7 +61089,7 @@
         <v>45989</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61162,7 +61162,7 @@
         <v>45992</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61235,7 +61235,7 @@
         <v>46111</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61308,7 +61308,7 @@
         <v>45068</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61386,7 +61386,7 @@
         <v>45764</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>46111</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61532,7 +61532,7 @@
         <v>46113</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61605,7 +61605,7 @@
         <v>46113</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>46113</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61751,7 +61751,7 @@
         <v>45992</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61824,7 +61824,7 @@
         <v>45734</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>46113</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61970,7 +61970,7 @@
         <v>46113</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62043,7 +62043,7 @@
         <v>44565</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62116,7 +62116,7 @@
         <v>45992</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62189,7 +62189,7 @@
         <v>45036</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>46112</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62335,7 +62335,7 @@
         <v>44886</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>44585</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45620</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62554,7 +62554,7 @@
         <v>44651</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>44551</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45594</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>46119</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62851,7 +62851,7 @@
         <v>46119</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>46120</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62997,7 +62997,7 @@
         <v>45994</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>45995</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63143,7 +63143,7 @@
         <v>45993</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63216,7 +63216,7 @@
         <v>44620</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>44887</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>44938</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>44974</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63508,7 +63508,7 @@
         <v>44959</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63586,7 +63586,7 @@
         <v>44959</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>44959</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63732,7 +63732,7 @@
         <v>46128</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>44812</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>44810</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63951,7 +63951,7 @@
         <v>46134</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>46134</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64097,7 +64097,7 @@
         <v>46134</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>46006</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46006</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64316,7 +64316,7 @@
         <v>46006</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64389,7 +64389,7 @@
         <v>46008</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>46008</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64535,7 +64535,7 @@
         <v>45188</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         <v>45162</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64686,7 +64686,7 @@
         <v>45845</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64759,7 +64759,7 @@
         <v>44924</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64832,7 +64832,7 @@
         <v>45784</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64905,7 +64905,7 @@
         <v>45733</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64978,7 +64978,7 @@
         <v>46006</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65051,7 +65051,7 @@
         <v>44657</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65124,7 +65124,7 @@
         <v>45831</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>45903</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>45218</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46008</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65416,7 +65416,7 @@
         <v>45838</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65489,7 +65489,7 @@
         <v>45260</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65562,7 +65562,7 @@
         <v>45483</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65635,7 +65635,7 @@
         <v>44806</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65708,7 +65708,7 @@
         <v>45727</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65781,7 +65781,7 @@
         <v>44742</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         <v>46014</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65927,7 +65927,7 @@
         <v>46020</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66000,7 +66000,7 @@
         <v>44809</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66073,7 +66073,7 @@
         <v>45880</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66146,7 +66146,7 @@
         <v>45356</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66219,7 +66219,7 @@
         <v>44487</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66292,7 +66292,7 @@
         <v>45562</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66370,7 +66370,7 @@
         <v>45546</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
         <v>45604</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66521,7 +66521,7 @@
         <v>45593</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66599,7 +66599,7 @@
         <v>46024</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66672,7 +66672,7 @@
         <v>45679</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66745,7 +66745,7 @@
         <v>46057</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66818,7 +66818,7 @@
         <v>45226</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>45764</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66964,7 +66964,7 @@
         <v>45916</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67037,7 +67037,7 @@
         <v>45742</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67110,7 +67110,7 @@
         <v>46140</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67183,7 +67183,7 @@
         <v>45993</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67256,7 +67256,7 @@
         <v>45568</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67329,7 +67329,7 @@
         <v>45097</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67402,7 +67402,7 @@
         <v>46030</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67475,7 +67475,7 @@
         <v>45097</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67548,7 +67548,7 @@
         <v>46140</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67621,7 +67621,7 @@
         <v>45993</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67694,7 +67694,7 @@
         <v>45081</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67767,7 +67767,7 @@
         <v>45908</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67840,7 +67840,7 @@
         <v>45679</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67913,7 +67913,7 @@
         <v>45093</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67986,7 +67986,7 @@
         <v>45811</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68059,7 +68059,7 @@
         <v>45475</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68132,7 +68132,7 @@
         <v>45005</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68205,7 +68205,7 @@
         <v>45305</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68278,7 +68278,7 @@
         <v>46139</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68351,7 +68351,7 @@
         <v>45607</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68424,7 +68424,7 @@
         <v>45097</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68497,7 +68497,7 @@
         <v>46139</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68570,7 +68570,7 @@
         <v>45798</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68643,7 +68643,7 @@
         <v>45567</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68716,7 +68716,7 @@
         <v>45845</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68789,7 +68789,7 @@
         <v>45742</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68862,7 +68862,7 @@
         <v>45121</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68935,7 +68935,7 @@
         <v>44985</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69008,7 +69008,7 @@
         <v>45757</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69081,7 +69081,7 @@
         <v>45349</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69154,7 +69154,7 @@
         <v>44978</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69227,7 +69227,7 @@
         <v>44960</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69300,7 +69300,7 @@
         <v>44712</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>45818</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69446,7 +69446,7 @@
         <v>46140</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69519,7 +69519,7 @@
         <v>45476</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69592,7 +69592,7 @@
         <v>45644</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69665,7 +69665,7 @@
         <v>44929</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69738,7 +69738,7 @@
         <v>46045</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69811,7 +69811,7 @@
         <v>46045</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69884,7 +69884,7 @@
         <v>45281</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69957,7 +69957,7 @@
         <v>46045</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70030,7 +70030,7 @@
         <v>46045</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>44809</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70176,7 +70176,7 @@
         <v>45253</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70249,7 +70249,7 @@
         <v>45754</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70322,7 +70322,7 @@
         <v>44991</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70395,7 +70395,7 @@
         <v>44971</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70468,7 +70468,7 @@
         <v>46050</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70541,7 +70541,7 @@
         <v>46050</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         <v>46059</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70687,7 +70687,7 @@
         <v>46054</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70760,7 +70760,7 @@
         <v>46054</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70833,7 +70833,7 @@
         <v>46054</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70906,7 +70906,7 @@
         <v>46059</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70984,7 +70984,7 @@
         <v>45733</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71057,7 +71057,7 @@
         <v>45842</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71130,7 +71130,7 @@
         <v>46059</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71203,7 +71203,7 @@
         <v>46062</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71276,7 +71276,7 @@
         <v>46059</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71349,7 +71349,7 @@
         <v>46146</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71422,7 +71422,7 @@
         <v>46063</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71495,7 +71495,7 @@
         <v>46063</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71568,7 +71568,7 @@
         <v>46063</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71641,7 +71641,7 @@
         <v>46063</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71714,7 +71714,7 @@
         <v>46146</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71787,7 +71787,7 @@
         <v>46069</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71865,7 +71865,7 @@
         <v>46150</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71938,7 +71938,7 @@
         <v>46150</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72011,7 +72011,7 @@
         <v>46076</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72084,7 +72084,7 @@
         <v>46077</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72157,7 +72157,7 @@
         <v>46078</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72230,7 +72230,7 @@
         <v>45735</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72303,7 +72303,7 @@
         <v>45742</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72376,7 +72376,7 @@
         <v>46155</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72449,7 +72449,7 @@
         <v>45845</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72522,7 +72522,7 @@
         <v>45874</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72595,7 +72595,7 @@
         <v>46155</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72668,7 +72668,7 @@
         <v>46084</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72741,7 +72741,7 @@
         <v>45735</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72814,7 +72814,7 @@
         <v>46059</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72892,7 +72892,7 @@
         <v>45811</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72965,7 +72965,7 @@
         <v>46087</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73038,7 +73038,7 @@
         <v>46155</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73111,7 +73111,7 @@
         <v>46155</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73184,7 +73184,7 @@
         <v>45749</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73257,7 +73257,7 @@
         <v>46079</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73330,7 +73330,7 @@
         <v>46160</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73403,7 +73403,7 @@
         <v>46094</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73476,7 +73476,7 @@
         <v>46097</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73549,7 +73549,7 @@
         <v>46097</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73622,7 +73622,7 @@
         <v>46097</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73695,7 +73695,7 @@
         <v>46161</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73768,7 +73768,7 @@
         <v>46170</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73841,7 +73841,7 @@
         <v>46104</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73914,7 +73914,7 @@
         <v>46170</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73987,7 +73987,7 @@
         <v>46170</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74060,7 +74060,7 @@
         <v>46171</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74133,7 +74133,7 @@
         <v>45775</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74206,7 +74206,7 @@
         <v>46174</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74279,7 +74279,7 @@
         <v>46174</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74352,7 +74352,7 @@
         <v>46176</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74425,7 +74425,7 @@
         <v>46176</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74498,7 +74498,7 @@
         <v>46182</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74571,7 +74571,7 @@
         <v>46182</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74644,7 +74644,7 @@
         <v>46184</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74717,7 +74717,7 @@
         <v>46184</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74790,7 +74790,7 @@
         <v>46191</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74863,7 +74863,7 @@
         <v>46195</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74936,7 +74936,7 @@
         <v>45131</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -75009,7 +75009,7 @@
         <v>46197</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75082,7 +75082,7 @@
         <v>46198</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75155,7 +75155,7 @@
         <v>45908</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75228,7 +75228,7 @@
         <v>46198</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75301,7 +75301,7 @@
         <v>46204</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75374,7 +75374,7 @@
         <v>46205</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75447,7 +75447,7 @@
         <v>46206</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75520,7 +75520,7 @@
         <v>46206</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75593,7 +75593,7 @@
         <v>46206</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75666,7 +75666,7 @@
         <v>46206</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75739,7 +75739,7 @@
         <v>46206</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75812,7 +75812,7 @@
         <v>45614</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75890,7 +75890,7 @@
         <v>46211</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75963,7 +75963,7 @@
         <v>46211</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76036,7 +76036,7 @@
         <v>45615</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76109,7 +76109,7 @@
         <v>46184</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76182,7 +76182,7 @@
         <v>46216</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76255,7 +76255,7 @@
         <v>46063</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76328,7 +76328,7 @@
         <v>46265</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76401,7 +76401,7 @@
         <v>46266</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76479,7 +76479,7 @@
         <v>46268</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76552,7 +76552,7 @@
         <v>46009</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76625,7 +76625,7 @@
         <v>46273</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76698,7 +76698,7 @@
         <v>46273</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76771,7 +76771,7 @@
         <v>46274</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76844,7 +76844,7 @@
         <v>46274</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76917,7 +76917,7 @@
         <v>46277</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76990,7 +76990,7 @@
         <v>46279</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77063,7 +77063,7 @@
         <v>46239</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77136,7 +77136,7 @@
         <v>46240</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77214,7 +77214,7 @@
         <v>46241</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77292,7 +77292,7 @@
         <v>46287</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77365,7 +77365,7 @@
         <v>45812</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77438,7 +77438,7 @@
         <v>46244</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77511,7 +77511,7 @@
         <v>46287</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77584,7 +77584,7 @@
         <v>46244</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77657,7 +77657,7 @@
         <v>46246</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77730,7 +77730,7 @@
         <v>46224</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77803,7 +77803,7 @@
         <v>46119</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77881,7 +77881,7 @@
         <v>46286</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77954,7 +77954,7 @@
         <v>46286</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -78027,7 +78027,7 @@
         <v>46246</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78100,7 +78100,7 @@
         <v>46289</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78173,7 +78173,7 @@
         <v>45940</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78246,7 +78246,7 @@
         <v>46294</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78319,7 +78319,7 @@
         <v>46292</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78392,7 +78392,7 @@
         <v>46251</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78465,7 +78465,7 @@
         <v>46296</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78538,7 +78538,7 @@
         <v>46296</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78611,7 +78611,7 @@
         <v>46253</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78684,7 +78684,7 @@
         <v>46252</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78757,7 +78757,7 @@
         <v>46154</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78830,7 +78830,7 @@
         <v>46154</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78903,7 +78903,7 @@
         <v>46182</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78976,7 +78976,7 @@
         <v>46254</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79049,7 +79049,7 @@
         <v>46098</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79122,7 +79122,7 @@
         <v>46298</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79195,7 +79195,7 @@
         <v>46290</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79268,7 +79268,7 @@
         <v>46259</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79341,7 +79341,7 @@
         <v>46301</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79414,7 +79414,7 @@
         <v>46302</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79487,7 +79487,7 @@
         <v>44638</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79560,7 +79560,7 @@
         <v>44644</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         <v>44643</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79706,7 +79706,7 @@
         <v>44643</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79779,7 +79779,7 @@
         <v>44655</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         <v>44642</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79925,7 +79925,7 @@
         <v>45110</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79998,7 +79998,7 @@
         <v>44820</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80071,7 +80071,7 @@
         <v>45537</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80144,7 +80144,7 @@
         <v>45226</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80217,7 +80217,7 @@
         <v>45527</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80290,7 +80290,7 @@
         <v>45593</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80363,7 +80363,7 @@
         <v>45000</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80436,7 +80436,7 @@
         <v>44820</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80509,7 +80509,7 @@
         <v>45412</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80582,7 +80582,7 @@
         <v>45272</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80655,7 +80655,7 @@
         <v>45168</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80728,7 +80728,7 @@
         <v>45378</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80801,7 +80801,7 @@
         <v>45554</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80874,7 +80874,7 @@
         <v>44484</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80947,7 +80947,7 @@
         <v>45574</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -81020,7 +81020,7 @@
         <v>45615</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81093,7 +81093,7 @@
         <v>45526</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81166,7 +81166,7 @@
         <v>45597</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81239,7 +81239,7 @@
         <v>45033</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81312,7 +81312,7 @@
         <v>45553</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81385,7 +81385,7 @@
         <v>45357</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45427</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45447</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45294</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81677,7 +81677,7 @@
         <v>45000</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45168</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81823,7 +81823,7 @@
         <v>45044</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81896,7 +81896,7 @@
         <v>45267</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81969,7 +81969,7 @@
         <v>45442</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82042,7 +82042,7 @@
         <v>44960</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82115,7 +82115,7 @@
         <v>44973</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82188,7 +82188,7 @@
         <v>45560</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82261,7 +82261,7 @@
         <v>45357</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82334,7 +82334,7 @@
         <v>44882</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82407,7 +82407,7 @@
         <v>45110</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82480,7 +82480,7 @@
         <v>45755</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82553,7 +82553,7 @@
         <v>45637</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82626,7 +82626,7 @@
         <v>45645</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82699,7 +82699,7 @@
         <v>45713</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82772,7 +82772,7 @@
         <v>45742</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82845,7 +82845,7 @@
         <v>45720</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82918,7 +82918,7 @@
         <v>45632</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82991,7 +82991,7 @@
         <v>45631</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83064,7 +83064,7 @@
         <v>45713</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83137,7 +83137,7 @@
         <v>45789</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83210,7 +83210,7 @@
         <v>45818</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83283,7 +83283,7 @@
         <v>45831</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83356,7 +83356,7 @@
         <v>45831</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83429,7 +83429,7 @@
         <v>45895</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83502,7 +83502,7 @@
         <v>45895</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83575,7 +83575,7 @@
         <v>45894</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83648,7 +83648,7 @@
         <v>46024</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83721,7 +83721,7 @@
         <v>46024</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83794,7 +83794,7 @@
         <v>46027</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83867,7 +83867,7 @@
         <v>46029</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83945,7 +83945,7 @@
         <v>46062</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -84018,7 +84018,7 @@
         <v>46063</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84091,7 +84091,7 @@
         <v>46064</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84164,7 +84164,7 @@
         <v>46150</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84237,7 +84237,7 @@
         <v>46150</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84310,7 +84310,7 @@
         <v>46156</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84383,7 +84383,7 @@
         <v>46161</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84456,7 +84456,7 @@
         <v>46161</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84529,7 +84529,7 @@
         <v>46209</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84607,7 +84607,7 @@
         <v>46266</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84680,7 +84680,7 @@
         <v>46279</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84758,7 +84758,7 @@
         <v>46279</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>45224</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45568</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45701</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>45211</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>46161</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45086</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45126</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>45236</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>45476</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45357</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45512</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>45272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44610</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45078</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45103</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>45194</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45152</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45978</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45819</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45733</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45212</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45111</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45996</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>46150</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>46196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>46272</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45042</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45013</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45054</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45372</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45686</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45061</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45005</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45594</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45266</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44985</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45617</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45561</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>44928</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>45555</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45527</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45079</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45334</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45510</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44645</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45205</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45832</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45020</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45246</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45012</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45833</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45978</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>45869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45274</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44894</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45483</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45875</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>46106</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>46006</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45282</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45191</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>45012</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45937</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45805</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45961</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45672</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>46204</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>46266</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46280</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44616</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44672</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45611</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44869</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45772</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>46168</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46202</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46210</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46206</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44568</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44853</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44622</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44508</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44818</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44848</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44635</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44510</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44742</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44592</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44714</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44623</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44749</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44880</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44837</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44861</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44482</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44502</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44760</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44495</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44537</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44806</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44810</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44732</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44742</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44530</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44576</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>44550</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44536</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44515</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44810</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44592</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44810</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44517</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44595</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44588</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>44879</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>44888</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44882</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44845</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44862</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44831</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44825</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>44882</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44806</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44565</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44712</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>44809</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44764</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44606</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44817</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44610</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44739</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44900</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44867</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44497</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44908</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44825</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45181</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45119</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45324</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45366</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45546</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45546</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44495</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45510</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44868</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44882</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45089</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45188</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45085</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44991</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>44991</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44809</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45463</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45440</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45684</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>45629</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44923</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45441</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45048</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45602</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45702</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45672</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45764</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>44846</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45187</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44928</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>45187</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45551</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>44896</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>44819</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44883</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44764</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45614</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45068</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45099</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>45401</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>45103</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>45092</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>44810</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45300</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>44810</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45103</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45595</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45307</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45239</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45373</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44895</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44895</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44895</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45301</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45065</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45700</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45065</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45272</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>44924</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45121</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45197</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45126</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45119</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44946</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45632</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45272</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45210</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45461</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45069</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45126</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45317</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45275</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45603</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45748</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45183</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45223</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45223</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45181</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45614</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45412</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45112</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45561</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>44823</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45323</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45755</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>44993</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45119</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45280</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45097</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45275</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45272</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45223</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45097</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45250</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>44903</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45106</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45260</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45546</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45278</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45355</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45315</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45265</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>44894</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45339</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44971</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45726</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45715</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45610</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45748</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45749</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44886</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44850</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45888</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45339</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45281</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45758</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45715</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45888</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>44587</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>45483</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45509</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45775</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45279</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45470</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45097</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45837</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45463</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45548</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45610</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45594</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45077</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>44945</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45372</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45476</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45826</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45895</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45895</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45895</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45895</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45895</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45895</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45897</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45714</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45075</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45635</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>44817</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45672</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45722</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45639</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44523</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45902</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45156</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45164</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44508</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45730</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>45441</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45306</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44656</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45908</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>44908</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>45905</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>45905</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>44915</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45910</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45181</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45629</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>45534</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45567</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45707</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45099</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45911</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45357</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45911</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45708</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45754</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45876</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44959</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>44848</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45137</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45916</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44874</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45646</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45783</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45783</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45783</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>45162</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45783</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45783</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45161</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45021</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45914</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45916</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45783</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45617</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45181</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>45390</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>45148</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45708</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45917</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>45168</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45188</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44985</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>44985</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45116</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45116</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45370</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>44937</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45215</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>45681</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45917</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45217</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45273</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45628</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45525</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>45533</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45372</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45562</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45593</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44886</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45734</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>44995</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45923</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45923</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>45923</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45350</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45350</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45510</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45524</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>45527</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>45349</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45756</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45925</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45925</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45925</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>45924</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45166</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45628</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>45925</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45925</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45089</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44999</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>45629</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>45056</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45792</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45188</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44942</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45510</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45610</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45126</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45637</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45212</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45796</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45796</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45719</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45596</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>45084</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45372</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>44670</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45614</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45246</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45216</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45793</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>45796</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>44603</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44603</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>44603</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>45345</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>45110</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45796</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45596</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45167</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44582</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45614</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>44927</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45156</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45645</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45071</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45071</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44573</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45562</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>44988</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45427</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45176</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>45441</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45734</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45705</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45253</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45183</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45082</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45205</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45205</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>44945</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45938</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45769</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44642</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45243</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45628</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44634</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>44740</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45371</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45615</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45226</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45628</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45940</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45811</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45811</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45811</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44946</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45069</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>44617</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45945</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45945</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45946</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45677</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45240</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45084</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>45686</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45617</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45950</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44634</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45179</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45762</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45817</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>44959</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>44923</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>44923</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45518</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45818</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>45950</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44721</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45614</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>44959</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45301</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45628</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>44851</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45824</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45621</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45618</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45826</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>45686</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46225,7 +46225,7 @@
         <v>45950</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45950</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45825</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45701</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45700</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45610</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>44628</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45793</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>44634</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>45446</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>44928</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45831</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45181</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45831</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45831</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45831</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45831</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>44851</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45831</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>45195</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45684</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45911</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45957</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45957</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45888</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45957</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45602</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45957</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45959</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>45833</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>45961</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45163</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>45323</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>44706</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45964</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45152</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45964</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45126</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45131</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45835</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45961</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45645</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>45837</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45835</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45840</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45187</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45840</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45509</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44999</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>44750</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45581</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>44802</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>45225</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45645</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>44743</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45131</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50338,7 +50338,7 @@
         <v>45207</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45756</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45842</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45231</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45775</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45264</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45630</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>45748</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45723</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>45848</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45848</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>44825</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45973</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>45730</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45811</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45852</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45315</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45977</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>45978</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45667</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51798,7 +51798,7 @@
         <v>45204</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45215</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>45811</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45328</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>44980</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45109</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45530</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>45860</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45224</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52455,7 +52455,7 @@
         <v>45225</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45510</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45257</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45978</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>45162</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>44988</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45869</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45869</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45869</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45224</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45481</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45783</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45026</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>44847</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>44881</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>44860</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>44917</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         <v>45099</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>45831</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45396</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>45701</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45646</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45425</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54149,7 +54149,7 @@
         <v>45035</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>45980</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>44515</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>44515</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45705</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>44538</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>44881</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45824</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54733,7 +54733,7 @@
         <v>44820</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>45394</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45701</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>45271</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45356</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>45301</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45211</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>45301</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>45847</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55390,7 +55390,7 @@
         <v>45628</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>44621</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>44715</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45739</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45218</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45394</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>45980</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>45145</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45676</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45750</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>45195</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>45079</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45005</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>44908</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56417,7 +56417,7 @@
         <v>45274</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45145</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>44858</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56636,7 +56636,7 @@
         <v>45247</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56709,7 +56709,7 @@
         <v>44712</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>45033</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45647</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>45301</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45211</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45875</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>45168</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>45875</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45981</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57366,7 +57366,7 @@
         <v>45714</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>45880</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>44852</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>45012</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>44991</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>45280</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45279</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45111</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45880</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>45621</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58096,7 +58096,7 @@
         <v>45267</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58169,7 +58169,7 @@
         <v>45881</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58242,7 +58242,7 @@
         <v>45881</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>45643</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58388,7 +58388,7 @@
         <v>45264</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58461,7 +58461,7 @@
         <v>44991</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58534,7 +58534,7 @@
         <v>44991</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>45761</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>46097</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>46097</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>46094</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58899,7 +58899,7 @@
         <v>46097</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>46097</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59045,7 +59045,7 @@
         <v>46097</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59118,7 +59118,7 @@
         <v>45981</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59191,7 +59191,7 @@
         <v>45099</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45055</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59337,7 +59337,7 @@
         <v>45236</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59410,7 +59410,7 @@
         <v>45735</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>44565</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59556,7 +59556,7 @@
         <v>44565</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>45985</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45169</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59775,7 +59775,7 @@
         <v>44810</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>46104</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59921,7 +59921,7 @@
         <v>46104</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59994,7 +59994,7 @@
         <v>45714</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60067,7 +60067,7 @@
         <v>45225</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60140,7 +60140,7 @@
         <v>46107</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60213,7 +60213,7 @@
         <v>46106</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>46107</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>45071</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45071</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>45730</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>46107</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60651,7 +60651,7 @@
         <v>46107</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>44903</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45604</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>45076</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         <v>45077</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61016,7 +61016,7 @@
         <v>45988</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61089,7 +61089,7 @@
         <v>45989</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61162,7 +61162,7 @@
         <v>45992</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61235,7 +61235,7 @@
         <v>46111</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61308,7 +61308,7 @@
         <v>45068</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61386,7 +61386,7 @@
         <v>45764</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>46111</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61532,7 +61532,7 @@
         <v>46113</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61605,7 +61605,7 @@
         <v>46113</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>46113</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61751,7 +61751,7 @@
         <v>45992</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61824,7 +61824,7 @@
         <v>45734</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>46113</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61970,7 +61970,7 @@
         <v>46113</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62043,7 +62043,7 @@
         <v>44565</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62116,7 +62116,7 @@
         <v>45992</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62189,7 +62189,7 @@
         <v>45036</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>46112</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62335,7 +62335,7 @@
         <v>44886</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>44585</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>45620</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62554,7 +62554,7 @@
         <v>44651</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>44551</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45594</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>46119</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62851,7 +62851,7 @@
         <v>46119</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>46120</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62997,7 +62997,7 @@
         <v>45994</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>45995</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63143,7 +63143,7 @@
         <v>45993</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63216,7 +63216,7 @@
         <v>44620</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>44887</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>44938</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>44974</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63508,7 +63508,7 @@
         <v>44959</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63586,7 +63586,7 @@
         <v>44959</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>44959</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63732,7 +63732,7 @@
         <v>46128</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>44812</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>44810</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63951,7 +63951,7 @@
         <v>46134</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>46134</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64097,7 +64097,7 @@
         <v>46134</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>46006</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46006</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64316,7 +64316,7 @@
         <v>46006</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64389,7 +64389,7 @@
         <v>46008</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>46008</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64535,7 +64535,7 @@
         <v>45188</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         <v>45162</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64686,7 +64686,7 @@
         <v>45845</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64759,7 +64759,7 @@
         <v>44924</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64832,7 +64832,7 @@
         <v>45784</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64905,7 +64905,7 @@
         <v>45733</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64978,7 +64978,7 @@
         <v>46006</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65051,7 +65051,7 @@
         <v>44657</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65124,7 +65124,7 @@
         <v>45831</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>45903</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>45218</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46008</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65416,7 +65416,7 @@
         <v>45838</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65489,7 +65489,7 @@
         <v>45260</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65562,7 +65562,7 @@
         <v>45483</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65635,7 +65635,7 @@
         <v>44806</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65708,7 +65708,7 @@
         <v>45727</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65781,7 +65781,7 @@
         <v>44742</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         <v>46014</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65927,7 +65927,7 @@
         <v>46020</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66000,7 +66000,7 @@
         <v>44809</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66073,7 +66073,7 @@
         <v>45880</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66146,7 +66146,7 @@
         <v>45356</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66219,7 +66219,7 @@
         <v>44487</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66292,7 +66292,7 @@
         <v>45562</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66370,7 +66370,7 @@
         <v>45546</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
         <v>45604</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66521,7 +66521,7 @@
         <v>45593</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66599,7 +66599,7 @@
         <v>46024</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66672,7 +66672,7 @@
         <v>45679</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66745,7 +66745,7 @@
         <v>46057</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66818,7 +66818,7 @@
         <v>45226</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>45764</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66964,7 +66964,7 @@
         <v>45916</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67037,7 +67037,7 @@
         <v>45742</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67110,7 +67110,7 @@
         <v>46140</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67183,7 +67183,7 @@
         <v>45993</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67256,7 +67256,7 @@
         <v>45568</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67329,7 +67329,7 @@
         <v>45097</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67402,7 +67402,7 @@
         <v>46030</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67475,7 +67475,7 @@
         <v>45097</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67548,7 +67548,7 @@
         <v>46140</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67621,7 +67621,7 @@
         <v>45993</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67694,7 +67694,7 @@
         <v>45081</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67767,7 +67767,7 @@
         <v>45908</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67840,7 +67840,7 @@
         <v>45679</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67913,7 +67913,7 @@
         <v>45093</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67986,7 +67986,7 @@
         <v>45811</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68059,7 +68059,7 @@
         <v>45475</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68132,7 +68132,7 @@
         <v>45005</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68205,7 +68205,7 @@
         <v>45305</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68278,7 +68278,7 @@
         <v>46139</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68351,7 +68351,7 @@
         <v>45607</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68424,7 +68424,7 @@
         <v>45097</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68497,7 +68497,7 @@
         <v>46139</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68570,7 +68570,7 @@
         <v>45798</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68643,7 +68643,7 @@
         <v>45567</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68716,7 +68716,7 @@
         <v>45845</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68789,7 +68789,7 @@
         <v>45742</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68862,7 +68862,7 @@
         <v>45121</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68935,7 +68935,7 @@
         <v>44985</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -69008,7 +69008,7 @@
         <v>45757</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69081,7 +69081,7 @@
         <v>45349</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69154,7 +69154,7 @@
         <v>44978</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69227,7 +69227,7 @@
         <v>44960</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69300,7 +69300,7 @@
         <v>44712</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>45818</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69446,7 +69446,7 @@
         <v>46140</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69519,7 +69519,7 @@
         <v>45476</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69592,7 +69592,7 @@
         <v>45644</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69665,7 +69665,7 @@
         <v>44929</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69738,7 +69738,7 @@
         <v>46045</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69811,7 +69811,7 @@
         <v>46045</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69884,7 +69884,7 @@
         <v>45281</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69957,7 +69957,7 @@
         <v>46045</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70030,7 +70030,7 @@
         <v>46045</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70103,7 +70103,7 @@
         <v>44809</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70176,7 +70176,7 @@
         <v>45253</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70249,7 +70249,7 @@
         <v>45754</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70322,7 +70322,7 @@
         <v>44991</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70395,7 +70395,7 @@
         <v>44971</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70468,7 +70468,7 @@
         <v>46050</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70541,7 +70541,7 @@
         <v>46050</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70614,7 +70614,7 @@
         <v>46059</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70687,7 +70687,7 @@
         <v>46054</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70760,7 +70760,7 @@
         <v>46054</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70833,7 +70833,7 @@
         <v>46054</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70906,7 +70906,7 @@
         <v>46059</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70984,7 +70984,7 @@
         <v>45733</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71057,7 +71057,7 @@
         <v>45842</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71130,7 +71130,7 @@
         <v>46059</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71203,7 +71203,7 @@
         <v>46062</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71276,7 +71276,7 @@
         <v>46059</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71349,7 +71349,7 @@
         <v>46146</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71422,7 +71422,7 @@
         <v>46063</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71495,7 +71495,7 @@
         <v>46063</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71568,7 +71568,7 @@
         <v>46063</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71641,7 +71641,7 @@
         <v>46063</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71714,7 +71714,7 @@
         <v>46146</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71787,7 +71787,7 @@
         <v>46069</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71865,7 +71865,7 @@
         <v>46150</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71938,7 +71938,7 @@
         <v>46150</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -72011,7 +72011,7 @@
         <v>46076</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72084,7 +72084,7 @@
         <v>46077</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72157,7 +72157,7 @@
         <v>46078</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72230,7 +72230,7 @@
         <v>45735</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72303,7 +72303,7 @@
         <v>45742</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72376,7 +72376,7 @@
         <v>46155</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72449,7 +72449,7 @@
         <v>45845</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72522,7 +72522,7 @@
         <v>45874</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72595,7 +72595,7 @@
         <v>46155</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72668,7 +72668,7 @@
         <v>46084</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72741,7 +72741,7 @@
         <v>45735</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72814,7 +72814,7 @@
         <v>46059</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72892,7 +72892,7 @@
         <v>45811</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72965,7 +72965,7 @@
         <v>46087</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73038,7 +73038,7 @@
         <v>46155</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73111,7 +73111,7 @@
         <v>46155</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73184,7 +73184,7 @@
         <v>45749</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73257,7 +73257,7 @@
         <v>46079</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73330,7 +73330,7 @@
         <v>46160</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73403,7 +73403,7 @@
         <v>46094</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73476,7 +73476,7 @@
         <v>46097</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73549,7 +73549,7 @@
         <v>46097</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73622,7 +73622,7 @@
         <v>46097</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73695,7 +73695,7 @@
         <v>46161</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73768,7 +73768,7 @@
         <v>46170</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73841,7 +73841,7 @@
         <v>46104</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73914,7 +73914,7 @@
         <v>46170</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73987,7 +73987,7 @@
         <v>46170</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74060,7 +74060,7 @@
         <v>46171</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74133,7 +74133,7 @@
         <v>45775</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74206,7 +74206,7 @@
         <v>46174</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74279,7 +74279,7 @@
         <v>46174</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74352,7 +74352,7 @@
         <v>46176</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74425,7 +74425,7 @@
         <v>46176</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74498,7 +74498,7 @@
         <v>46182</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74571,7 +74571,7 @@
         <v>46182</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74644,7 +74644,7 @@
         <v>46184</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74717,7 +74717,7 @@
         <v>46184</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74790,7 +74790,7 @@
         <v>46191</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74863,7 +74863,7 @@
         <v>46195</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74936,7 +74936,7 @@
         <v>45131</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -75009,7 +75009,7 @@
         <v>46197</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75082,7 +75082,7 @@
         <v>46198</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75155,7 +75155,7 @@
         <v>45908</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75228,7 +75228,7 @@
         <v>46198</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75301,7 +75301,7 @@
         <v>46204</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75374,7 +75374,7 @@
         <v>46205</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75447,7 +75447,7 @@
         <v>46206</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75520,7 +75520,7 @@
         <v>46206</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75593,7 +75593,7 @@
         <v>46206</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75666,7 +75666,7 @@
         <v>46206</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75739,7 +75739,7 @@
         <v>46206</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75812,7 +75812,7 @@
         <v>45614</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75890,7 +75890,7 @@
         <v>46211</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75963,7 +75963,7 @@
         <v>46211</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76036,7 +76036,7 @@
         <v>45615</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76109,7 +76109,7 @@
         <v>46184</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76182,7 +76182,7 @@
         <v>46216</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76255,7 +76255,7 @@
         <v>46063</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76328,7 +76328,7 @@
         <v>46265</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76401,7 +76401,7 @@
         <v>46266</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76479,7 +76479,7 @@
         <v>46268</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76552,7 +76552,7 @@
         <v>46009</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76625,7 +76625,7 @@
         <v>46273</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76698,7 +76698,7 @@
         <v>46273</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76771,7 +76771,7 @@
         <v>46274</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76844,7 +76844,7 @@
         <v>46274</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76917,7 +76917,7 @@
         <v>46277</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76990,7 +76990,7 @@
         <v>46279</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77063,7 +77063,7 @@
         <v>46239</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77136,7 +77136,7 @@
         <v>46240</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77214,7 +77214,7 @@
         <v>46241</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77292,7 +77292,7 @@
         <v>46287</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77365,7 +77365,7 @@
         <v>45812</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77438,7 +77438,7 @@
         <v>46244</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77511,7 +77511,7 @@
         <v>46287</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77584,7 +77584,7 @@
         <v>46244</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77657,7 +77657,7 @@
         <v>46246</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77730,7 +77730,7 @@
         <v>46224</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77803,7 +77803,7 @@
         <v>46119</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77881,7 +77881,7 @@
         <v>46286</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77954,7 +77954,7 @@
         <v>46286</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -78027,7 +78027,7 @@
         <v>46246</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78100,7 +78100,7 @@
         <v>46289</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78173,7 +78173,7 @@
         <v>45940</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78246,7 +78246,7 @@
         <v>46294</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78319,7 +78319,7 @@
         <v>46292</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78392,7 +78392,7 @@
         <v>46251</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78465,7 +78465,7 @@
         <v>46296</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78538,7 +78538,7 @@
         <v>46296</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78611,7 +78611,7 @@
         <v>46253</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78684,7 +78684,7 @@
         <v>46252</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78757,7 +78757,7 @@
         <v>46154</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78830,7 +78830,7 @@
         <v>46154</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78903,7 +78903,7 @@
         <v>46182</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78976,7 +78976,7 @@
         <v>46254</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79049,7 +79049,7 @@
         <v>46098</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79122,7 +79122,7 @@
         <v>46298</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79195,7 +79195,7 @@
         <v>46290</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79268,7 +79268,7 @@
         <v>46259</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79341,7 +79341,7 @@
         <v>46301</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79414,7 +79414,7 @@
         <v>46302</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79487,7 +79487,7 @@
         <v>44638</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79560,7 +79560,7 @@
         <v>44644</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         <v>44643</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79706,7 +79706,7 @@
         <v>44643</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79779,7 +79779,7 @@
         <v>44655</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         <v>44642</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79925,7 +79925,7 @@
         <v>45110</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79998,7 +79998,7 @@
         <v>44820</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80071,7 +80071,7 @@
         <v>45537</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80144,7 +80144,7 @@
         <v>45226</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80217,7 +80217,7 @@
         <v>45527</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80290,7 +80290,7 @@
         <v>45593</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80363,7 +80363,7 @@
         <v>45000</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80436,7 +80436,7 @@
         <v>44820</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80509,7 +80509,7 @@
         <v>45412</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80582,7 +80582,7 @@
         <v>45272</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80655,7 +80655,7 @@
         <v>45168</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80728,7 +80728,7 @@
         <v>45378</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80801,7 +80801,7 @@
         <v>45554</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80874,7 +80874,7 @@
         <v>44484</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80947,7 +80947,7 @@
         <v>45574</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -81020,7 +81020,7 @@
         <v>45615</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81093,7 +81093,7 @@
         <v>45526</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81166,7 +81166,7 @@
         <v>45597</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81239,7 +81239,7 @@
         <v>45033</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81312,7 +81312,7 @@
         <v>45553</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81385,7 +81385,7 @@
         <v>45357</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45427</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45447</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45294</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81677,7 +81677,7 @@
         <v>45000</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45168</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81823,7 +81823,7 @@
         <v>45044</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81896,7 +81896,7 @@
         <v>45267</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81969,7 +81969,7 @@
         <v>45442</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82042,7 +82042,7 @@
         <v>44960</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82115,7 +82115,7 @@
         <v>44973</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82188,7 +82188,7 @@
         <v>45560</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82261,7 +82261,7 @@
         <v>45357</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82334,7 +82334,7 @@
         <v>44882</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82407,7 +82407,7 @@
         <v>45110</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82480,7 +82480,7 @@
         <v>45755</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82553,7 +82553,7 @@
         <v>45637</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82626,7 +82626,7 @@
         <v>45645</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82699,7 +82699,7 @@
         <v>45713</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82772,7 +82772,7 @@
         <v>45742</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82845,7 +82845,7 @@
         <v>45720</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82918,7 +82918,7 @@
         <v>45632</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82991,7 +82991,7 @@
         <v>45631</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83064,7 +83064,7 @@
         <v>45713</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83137,7 +83137,7 @@
         <v>45789</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83210,7 +83210,7 @@
         <v>45818</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83283,7 +83283,7 @@
         <v>45831</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83356,7 +83356,7 @@
         <v>45831</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83429,7 +83429,7 @@
         <v>45895</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83502,7 +83502,7 @@
         <v>45895</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83575,7 +83575,7 @@
         <v>45894</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83648,7 +83648,7 @@
         <v>46024</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83721,7 +83721,7 @@
         <v>46024</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83794,7 +83794,7 @@
         <v>46027</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83867,7 +83867,7 @@
         <v>46029</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83945,7 +83945,7 @@
         <v>46062</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -84018,7 +84018,7 @@
         <v>46063</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84091,7 +84091,7 @@
         <v>46064</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84164,7 +84164,7 @@
         <v>46150</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84237,7 +84237,7 @@
         <v>46150</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84310,7 +84310,7 @@
         <v>46156</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84383,7 +84383,7 @@
         <v>46161</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84456,7 +84456,7 @@
         <v>46161</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84529,7 +84529,7 @@
         <v>46209</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84607,7 +84607,7 @@
         <v>46266</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84680,7 +84680,7 @@
         <v>46279</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84758,7 +84758,7 @@
         <v>46279</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45224</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>45568</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45103</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45476</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45194</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45078</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45086</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45357</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45996</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45236</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>45152</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>46196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>46198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>45212</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45126</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>45111</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>44610</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>45512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>46272</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45078</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45042</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45013</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45427</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45054</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45483</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45561</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45012</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45617</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45805</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45937</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>44908</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>44985</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45978</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>44820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>45961</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45672</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44928</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45079</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45205</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>45686</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>46106</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45012</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45282</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>46204</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45334</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45005</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>45527</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>45246</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45555</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45061</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45372</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45020</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>45749</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>46280</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46266</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>45832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45833</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45869</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44894</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45274</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45875</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45611</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44616</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45335</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44978</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44831</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44672</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44869</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45772</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>46168</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46202</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46206</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44568</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44853</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44508</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>44622</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44818</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44848</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44635</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44510</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44592</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44742</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44623</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44714</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44749</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44880</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44837</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44861</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44502</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44495</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44576</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44888</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44825</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44565</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44760</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44732</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44550</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44810</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44536</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>44810</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44588</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44845</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44862</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44764</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44739</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44742</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44515</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44592</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44517</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44595</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44879</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44831</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44882</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44537</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44817</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>44806</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44530</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44882</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>44806</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44712</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44809</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44606</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44610</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44715</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44497</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44495</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45748</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45097</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44764</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>44929</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45614</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45187</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>44850</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45279</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44825</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45068</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44928</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45082</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45065</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45551</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44974</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45735</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45761</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>44874</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45103</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45714</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44617</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45218</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45602</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>44985</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45617</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45345</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45684</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45111</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45110</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44883</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45643</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44823</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44959</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>44634</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45099</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45719</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>44634</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45593</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>44858</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45181</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45441</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45226</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44852</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45672</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>44923</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45223</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45730</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44882</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45700</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45279</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44851</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44706</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45163</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>45103</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44817</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>45461</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45278</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45183</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45106</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45446</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45246</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45216</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45686</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45260</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45126</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44582</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45215</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44928</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45305</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44886</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45317</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45264</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45412</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44810</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>44908</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45148</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44809</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45684</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45757</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>44603</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>44603</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44603</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>44945</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45205</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45646</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>44993</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45350</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45350</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44942</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45510</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45162</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45629</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45525</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45212</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45301</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>45225</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>45225</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45527</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45099</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44810</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45280</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45257</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45645</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>44894</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45119</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45093</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45646</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45632</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45546</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45748</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46139</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45679</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45749</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45775</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45475</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45845</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45679</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45260</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45280</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45339</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45328</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45483</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45197</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44923</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45700</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45764</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45733</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45784</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>46139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45727</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>44487</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45112</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45715</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45604</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45567</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44903</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45275</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45838</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45715</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45818</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45888</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45888</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45243</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45742</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44670</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45837</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45895</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45895</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45137</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45895</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45798</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45895</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45895</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45895</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45644</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45897</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45567</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45826</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45167</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45758</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>44740</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>45272</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45440</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45811</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45476</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>45275</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45207</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45916</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45733</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45842</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45077</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>46140</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45845</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45069</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>46140</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>46140</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44656</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45085</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45355</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45902</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45905</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45905</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45645</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>44991</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>46057</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45908</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>46059</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45910</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45162</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45707</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>44896</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45876</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45370</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45215</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45911</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45911</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45914</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45546</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45755</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>46146</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45916</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>45916</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45917</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45917</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>46146</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45734</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>44585</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44999</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45635</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>44991</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>44991</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45923</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45923</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45924</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45366</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45923</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45069</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45748</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45195</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45925</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45925</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45925</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45925</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45925</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>44634</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44991</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>44991</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>46150</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46150</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44959</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44959</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45187</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45176</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45181</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45714</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>44523</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45168</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>45224</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45097</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45734</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>44573</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45463</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45938</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45940</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44820</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45945</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45945</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>46155</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45811</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45476</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45111</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44846</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45946</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45845</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44848</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45749</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>45089</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>44565</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44565</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>46155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45950</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45950</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40169,7 +40169,7 @@
         <v>45911</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>45950</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>46155</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45730</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45068</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>45874</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>45957</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45957</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>45957</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>45315</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>46155</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40972,7 +40972,7 @@
         <v>45957</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>45888</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45672</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>46059</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>45959</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>46079</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>45470</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45961</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45602</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45339</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45097</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45961</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45964</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45964</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45169</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>45614</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45595</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44867</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>45427</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>46160</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45225</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45116</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45116</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>45610</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45973</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45156</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45218</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>44971</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>45714</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>45349</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>44937</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45629</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>45977</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45978</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45610</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>44620</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>46161</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45978</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>45628</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>45603</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45981</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45981</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45980</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45980</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45324</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45533</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45510</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45988</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45764</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45989</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45992</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45181</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45097</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45356</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>45992</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>45992</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45264</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>44895</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>44895</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>44895</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45630</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45546</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45995</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45048</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45994</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45993</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45754</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45639</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>46104</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>46170</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>46170</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>46170</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45281</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>44886</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45265</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45179</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>46006</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>46006</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>45756</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>46006</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>46174</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>46174</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>46006</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45561</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>46008</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>46008</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>46008</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45401</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45610</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45775</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>44900</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>46014</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46171</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>44508</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>46020</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44946</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>46024</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45239</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>46176</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45993</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45993</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>44742</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>44974</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>46030</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>44587</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45315</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46176</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>44959</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>44959</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46045</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45036</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>46045</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>46045</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>46045</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45593</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45483</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45628</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45181</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45390</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>44551</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45267</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46182</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>46050</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>46050</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45204</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>46054</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>44971</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>46054</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>46182</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>46054</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>44750</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45084</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>46059</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>46059</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>46059</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>46184</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>46062</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>46184</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45121</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>46063</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>46063</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45188</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45056</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>46063</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>46063</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45621</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>46069</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>45604</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>44802</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>45240</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>46078</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>46076</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>46077</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>45441</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>44825</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45742</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45735</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45769</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>45119</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45273</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>45081</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         <v>45162</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45463</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>46084</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>46087</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53155,7 +53155,7 @@
         <v>45735</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53228,7 +53228,7 @@
         <v>45055</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45349</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>46094</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>46094</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>44915</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>46191</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45131</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>46097</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>46097</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>45610</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53958,7 +53958,7 @@
         <v>46097</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54031,7 +54031,7 @@
         <v>46097</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>46097</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46097</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>45183</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46097</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>46097</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>46195</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45509</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>45726</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45168</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>46104</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45614</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         <v>45614</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>46106</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>46104</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45092</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45146</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45620</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>46107</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>46107</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>46107</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>46107</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>46111</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55725,7 +55725,7 @@
         <v>46197</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>46111</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>46198</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55944,7 +55944,7 @@
         <v>46112</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>45236</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>44960</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>46113</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56236,7 +56236,7 @@
         <v>46113</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>46113</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>45188</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>46113</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>46113</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>46198</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>44938</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>44908</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         <v>44946</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56898,7 +56898,7 @@
         <v>46120</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>45357</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>46119</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>44712</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>46119</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57268,7 +57268,7 @@
         <v>45217</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>45908</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>45618</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45562</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>46128</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45509</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>44908</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46204</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45677</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57940,7 +57940,7 @@
         <v>45568</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>46134</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58086,7 +58086,7 @@
         <v>46134</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>44978</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>46134</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>44809</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58378,7 +58378,7 @@
         <v>44809</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58451,7 +58451,7 @@
         <v>46205</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>45880</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>46206</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58670,7 +58670,7 @@
         <v>45903</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58743,7 +58743,7 @@
         <v>45908</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>46206</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45005</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58962,7 +58962,7 @@
         <v>45702</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59035,7 +59035,7 @@
         <v>45126</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>45831</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59181,7 +59181,7 @@
         <v>45742</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45084</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45722</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>46206</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>46206</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59546,7 +59546,7 @@
         <v>46206</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>45754</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59692,7 +59692,7 @@
         <v>44806</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59765,7 +59765,7 @@
         <v>45614</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59843,7 +59843,7 @@
         <v>45372</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59916,7 +59916,7 @@
         <v>45615</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59989,7 +59989,7 @@
         <v>46211</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>45121</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>46211</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>46216</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>44743</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60354,7 +60354,7 @@
         <v>44991</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60427,7 +60427,7 @@
         <v>45035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60500,7 +60500,7 @@
         <v>45614</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60573,7 +60573,7 @@
         <v>46063</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         <v>46184</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>44851</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>44988</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>45705</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         <v>45089</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61016,7 +61016,7 @@
         <v>45356</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61089,7 +61089,7 @@
         <v>46273</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61162,7 +61162,7 @@
         <v>46009</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61235,7 +61235,7 @@
         <v>45323</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45373</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61386,7 +61386,7 @@
         <v>46273</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>44924</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61532,7 +61532,7 @@
         <v>45621</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61605,7 +61605,7 @@
         <v>46274</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45126</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61751,7 +61751,7 @@
         <v>45253</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61824,7 +61824,7 @@
         <v>44810</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>44923</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61970,7 +61970,7 @@
         <v>46274</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62043,7 +62043,7 @@
         <v>45187</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62116,7 +62116,7 @@
         <v>45076</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62189,7 +62189,7 @@
         <v>46277</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>45524</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62335,7 +62335,7 @@
         <v>46279</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45099</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>44628</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62554,7 +62554,7 @@
         <v>45119</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>44988</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>44887</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>44868</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45126</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62919,7 +62919,7 @@
         <v>44565</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62992,7 +62992,7 @@
         <v>45188</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45546</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63138,7 +63138,7 @@
         <v>44651</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>46239</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>46241</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>45323</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63440,7 +63440,7 @@
         <v>46240</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63518,7 +63518,7 @@
         <v>45012</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>45181</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         <v>44812</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63737,7 +63737,7 @@
         <v>45812</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63810,7 +63810,7 @@
         <v>45205</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63883,7 +63883,7 @@
         <v>44980</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>44810</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>46286</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64102,7 +64102,7 @@
         <v>46286</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64175,7 +64175,7 @@
         <v>45231</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64248,7 +64248,7 @@
         <v>45035</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>45077</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64394,7 +64394,7 @@
         <v>44945</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>45594</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64540,7 +64540,7 @@
         <v>46287</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>46244</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64686,7 +64686,7 @@
         <v>46119</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>44721</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>45300</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64910,7 +64910,7 @@
         <v>45210</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64983,7 +64983,7 @@
         <v>44903</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>46287</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65129,7 +65129,7 @@
         <v>46244</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65202,7 +65202,7 @@
         <v>45065</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65275,7 +65275,7 @@
         <v>45224</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65348,7 +65348,7 @@
         <v>45607</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65421,7 +65421,7 @@
         <v>46246</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65494,7 +65494,7 @@
         <v>45075</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>46224</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65640,7 +65640,7 @@
         <v>46246</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65713,7 +65713,7 @@
         <v>45223</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65786,7 +65786,7 @@
         <v>45223</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65859,7 +65859,7 @@
         <v>46289</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65932,7 +65932,7 @@
         <v>45071</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66005,7 +66005,7 @@
         <v>45071</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66078,7 +66078,7 @@
         <v>44642</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66151,7 +66151,7 @@
         <v>45301</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66224,7 +66224,7 @@
         <v>44712</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66297,7 +66297,7 @@
         <v>45195</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66370,7 +66370,7 @@
         <v>45071</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66443,7 +66443,7 @@
         <v>45071</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66516,7 +66516,7 @@
         <v>45705</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66589,7 +66589,7 @@
         <v>45701</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66662,7 +66662,7 @@
         <v>45940</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66735,7 +66735,7 @@
         <v>45628</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66808,7 +66808,7 @@
         <v>45581</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66881,7 +66881,7 @@
         <v>46292</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66954,7 +66954,7 @@
         <v>45372</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67027,7 +67027,7 @@
         <v>45250</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67100,7 +67100,7 @@
         <v>44819</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67173,7 +67173,7 @@
         <v>45152</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67246,7 +67246,7 @@
         <v>45097</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67319,7 +67319,7 @@
         <v>45131</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67392,7 +67392,7 @@
         <v>45441</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67465,7 +67465,7 @@
         <v>45131</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67538,7 +67538,7 @@
         <v>45615</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67611,7 +67611,7 @@
         <v>45033</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67684,7 +67684,7 @@
         <v>46252</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67757,7 +67757,7 @@
         <v>45307</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67830,7 +67830,7 @@
         <v>45764</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67903,7 +67903,7 @@
         <v>44886</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67976,7 +67976,7 @@
         <v>46251</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>45226</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68122,7 +68122,7 @@
         <v>45306</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68195,7 +68195,7 @@
         <v>45548</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68268,7 +68268,7 @@
         <v>44985</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68341,7 +68341,7 @@
         <v>44985</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68414,7 +68414,7 @@
         <v>46294</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68487,7 +68487,7 @@
         <v>44995</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68560,7 +68560,7 @@
         <v>45562</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68633,7 +68633,7 @@
         <v>45594</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68706,7 +68706,7 @@
         <v>45272</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68779,7 +68779,7 @@
         <v>45272</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68852,7 +68852,7 @@
         <v>44924</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68925,7 +68925,7 @@
         <v>45628</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68998,7 +68998,7 @@
         <v>44657</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69071,7 +69071,7 @@
         <v>46253</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         <v>46296</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69217,7 +69217,7 @@
         <v>46296</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69290,7 +69290,7 @@
         <v>46254</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69363,7 +69363,7 @@
         <v>46154</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69436,7 +69436,7 @@
         <v>46154</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69509,7 +69509,7 @@
         <v>46290</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69582,7 +69582,7 @@
         <v>44999</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69655,7 +69655,7 @@
         <v>45637</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69728,7 +69728,7 @@
         <v>45164</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69801,7 +69801,7 @@
         <v>45629</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69874,7 +69874,7 @@
         <v>45534</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69947,7 +69947,7 @@
         <v>45708</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70020,7 +70020,7 @@
         <v>44959</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70098,7 +70098,7 @@
         <v>45783</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70171,7 +70171,7 @@
         <v>45783</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70244,7 +70244,7 @@
         <v>45783</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70317,7 +70317,7 @@
         <v>45021</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70390,7 +70390,7 @@
         <v>45783</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70463,7 +70463,7 @@
         <v>45783</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70536,7 +70536,7 @@
         <v>45783</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70609,7 +70609,7 @@
         <v>46098</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70682,7 +70682,7 @@
         <v>45708</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70755,7 +70755,7 @@
         <v>46298</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70828,7 +70828,7 @@
         <v>45628</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70901,7 +70901,7 @@
         <v>45161</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70974,7 +70974,7 @@
         <v>45734</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71047,7 +71047,7 @@
         <v>45372</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71120,7 +71120,7 @@
         <v>46182</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>45166</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71266,7 +71266,7 @@
         <v>46301</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71339,7 +71339,7 @@
         <v>45756</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71412,7 +71412,7 @@
         <v>45510</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71485,7 +71485,7 @@
         <v>45681</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71558,7 +71558,7 @@
         <v>45510</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71631,7 +71631,7 @@
         <v>45628</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71704,7 +71704,7 @@
         <v>46302</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71777,7 +71777,7 @@
         <v>46259</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71850,7 +71850,7 @@
         <v>45792</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71923,7 +71923,7 @@
         <v>45793</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71996,7 +71996,7 @@
         <v>46307</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72069,7 +72069,7 @@
         <v>45596</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72142,7 +72142,7 @@
         <v>44927</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72215,7 +72215,7 @@
         <v>45796</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72293,7 +72293,7 @@
         <v>45796</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72371,7 +72371,7 @@
         <v>45796</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72449,7 +72449,7 @@
         <v>45596</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72522,7 +72522,7 @@
         <v>46305</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72595,7 +72595,7 @@
         <v>45796</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72673,7 +72673,7 @@
         <v>46307</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72746,7 +72746,7 @@
         <v>46307</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72819,7 +72819,7 @@
         <v>46307</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72892,7 +72892,7 @@
         <v>45562</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72965,7 +72965,7 @@
         <v>45156</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73038,7 +73038,7 @@
         <v>45253</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73116,7 +73116,7 @@
         <v>45645</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73189,7 +73189,7 @@
         <v>46266</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73267,7 +73267,7 @@
         <v>45811</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73340,7 +73340,7 @@
         <v>45811</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73413,7 +73413,7 @@
         <v>45811</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73486,7 +73486,7 @@
         <v>46301</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73559,7 +73559,7 @@
         <v>46265</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73632,7 +73632,7 @@
         <v>46310</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73705,7 +73705,7 @@
         <v>45371</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73778,7 +73778,7 @@
         <v>46310</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73851,7 +73851,7 @@
         <v>46310</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73924,7 +73924,7 @@
         <v>45686</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73997,7 +73997,7 @@
         <v>45817</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74070,7 +74070,7 @@
         <v>45762</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74143,7 +74143,7 @@
         <v>45518</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74216,7 +74216,7 @@
         <v>45818</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74289,7 +74289,7 @@
         <v>45617</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74362,7 +74362,7 @@
         <v>46310</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74435,7 +74435,7 @@
         <v>45825</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74508,7 +74508,7 @@
         <v>45824</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74581,7 +74581,7 @@
         <v>46268</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74654,7 +74654,7 @@
         <v>45793</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74727,7 +74727,7 @@
         <v>45826</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74800,7 +74800,7 @@
         <v>46310</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74873,7 +74873,7 @@
         <v>45831</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74946,7 +74946,7 @@
         <v>45831</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -75019,7 +75019,7 @@
         <v>45831</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75092,7 +75092,7 @@
         <v>45831</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75165,7 +75165,7 @@
         <v>45831</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75238,7 +75238,7 @@
         <v>45831</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75311,7 +75311,7 @@
         <v>45833</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75384,7 +75384,7 @@
         <v>45835</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75457,7 +75457,7 @@
         <v>45835</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75530,7 +75530,7 @@
         <v>45837</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75603,7 +75603,7 @@
         <v>45840</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75676,7 +75676,7 @@
         <v>45840</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75749,7 +75749,7 @@
         <v>45842</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75822,7 +75822,7 @@
         <v>45723</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75895,7 +75895,7 @@
         <v>45775</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75968,7 +75968,7 @@
         <v>45730</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76041,7 +76041,7 @@
         <v>45848</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76114,7 +76114,7 @@
         <v>45848</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76187,7 +76187,7 @@
         <v>45811</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76260,7 +76260,7 @@
         <v>45852</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76333,7 +76333,7 @@
         <v>45667</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76406,7 +76406,7 @@
         <v>45109</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76479,7 +76479,7 @@
         <v>45530</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76552,7 +76552,7 @@
         <v>45811</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76625,7 +76625,7 @@
         <v>45860</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76698,7 +76698,7 @@
         <v>45274</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76771,7 +76771,7 @@
         <v>45396</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76844,7 +76844,7 @@
         <v>45145</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76917,7 +76917,7 @@
         <v>44881</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76990,7 +76990,7 @@
         <v>45869</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77068,7 +77068,7 @@
         <v>45701</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77141,7 +77141,7 @@
         <v>45847</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77214,7 +77214,7 @@
         <v>45739</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77287,7 +77287,7 @@
         <v>45783</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77360,7 +77360,7 @@
         <v>45005</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77433,7 +77433,7 @@
         <v>44917</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77506,7 +77506,7 @@
         <v>45701</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77579,7 +77579,7 @@
         <v>45425</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77652,7 +77652,7 @@
         <v>45099</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77725,7 +77725,7 @@
         <v>44621</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77798,7 +77798,7 @@
         <v>45079</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77871,7 +77871,7 @@
         <v>44538</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77944,7 +77944,7 @@
         <v>45394</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -78017,7 +78017,7 @@
         <v>45869</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78095,7 +78095,7 @@
         <v>45271</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78168,7 +78168,7 @@
         <v>44847</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78241,7 +78241,7 @@
         <v>45026</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78314,7 +78314,7 @@
         <v>45301</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78387,7 +78387,7 @@
         <v>45647</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78460,7 +78460,7 @@
         <v>44881</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78533,7 +78533,7 @@
         <v>45211</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78606,7 +78606,7 @@
         <v>45247</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78679,7 +78679,7 @@
         <v>45145</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78752,7 +78752,7 @@
         <v>45394</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78825,7 +78825,7 @@
         <v>44715</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78898,7 +78898,7 @@
         <v>45301</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78971,7 +78971,7 @@
         <v>45481</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79044,7 +79044,7 @@
         <v>44515</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79117,7 +79117,7 @@
         <v>44515</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79190,7 +79190,7 @@
         <v>45831</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79263,7 +79263,7 @@
         <v>45211</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79336,7 +79336,7 @@
         <v>45750</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79409,7 +79409,7 @@
         <v>45869</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79487,7 +79487,7 @@
         <v>45824</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79560,7 +79560,7 @@
         <v>45301</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         <v>44860</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79706,7 +79706,7 @@
         <v>45676</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79779,7 +79779,7 @@
         <v>45875</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         <v>45875</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79925,7 +79925,7 @@
         <v>45881</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79998,7 +79998,7 @@
         <v>45880</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80071,7 +80071,7 @@
         <v>45880</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80144,7 +80144,7 @@
         <v>45881</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80217,7 +80217,7 @@
         <v>45110</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80290,7 +80290,7 @@
         <v>44820</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80363,7 +80363,7 @@
         <v>45537</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80436,7 +80436,7 @@
         <v>45226</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80509,7 +80509,7 @@
         <v>45527</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80582,7 +80582,7 @@
         <v>45593</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80655,7 +80655,7 @@
         <v>44638</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80728,7 +80728,7 @@
         <v>45000</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80801,7 +80801,7 @@
         <v>44644</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80874,7 +80874,7 @@
         <v>44820</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80947,7 +80947,7 @@
         <v>44643</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -81020,7 +81020,7 @@
         <v>45412</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81093,7 +81093,7 @@
         <v>45272</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81166,7 +81166,7 @@
         <v>45168</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81239,7 +81239,7 @@
         <v>45378</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81312,7 +81312,7 @@
         <v>44643</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81385,7 +81385,7 @@
         <v>44655</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45554</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45574</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45615</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81677,7 +81677,7 @@
         <v>45526</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45597</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81823,7 +81823,7 @@
         <v>45033</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81896,7 +81896,7 @@
         <v>45553</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81969,7 +81969,7 @@
         <v>45357</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82042,7 +82042,7 @@
         <v>45427</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82115,7 +82115,7 @@
         <v>44642</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82188,7 +82188,7 @@
         <v>45447</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82261,7 +82261,7 @@
         <v>45294</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82334,7 +82334,7 @@
         <v>45000</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82407,7 +82407,7 @@
         <v>45168</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82480,7 +82480,7 @@
         <v>45044</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82553,7 +82553,7 @@
         <v>45267</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82626,7 +82626,7 @@
         <v>45442</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82699,7 +82699,7 @@
         <v>44960</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82772,7 +82772,7 @@
         <v>44973</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82845,7 +82845,7 @@
         <v>45560</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82918,7 +82918,7 @@
         <v>45357</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82991,7 +82991,7 @@
         <v>44882</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83064,7 +83064,7 @@
         <v>45110</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83137,7 +83137,7 @@
         <v>45755</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83210,7 +83210,7 @@
         <v>45637</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83283,7 +83283,7 @@
         <v>45645</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83356,7 +83356,7 @@
         <v>45713</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83429,7 +83429,7 @@
         <v>45742</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83502,7 +83502,7 @@
         <v>45720</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83575,7 +83575,7 @@
         <v>45632</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83648,7 +83648,7 @@
         <v>45631</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83721,7 +83721,7 @@
         <v>45713</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83794,7 +83794,7 @@
         <v>45789</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83867,7 +83867,7 @@
         <v>45818</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83940,7 +83940,7 @@
         <v>45831</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -84013,7 +84013,7 @@
         <v>45831</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84086,7 +84086,7 @@
         <v>45895</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84159,7 +84159,7 @@
         <v>45895</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84232,7 +84232,7 @@
         <v>45894</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84305,7 +84305,7 @@
         <v>46027</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84378,7 +84378,7 @@
         <v>46024</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84451,7 +84451,7 @@
         <v>46024</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84524,7 +84524,7 @@
         <v>46029</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84602,7 +84602,7 @@
         <v>46063</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84675,7 +84675,7 @@
         <v>46062</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84748,7 +84748,7 @@
         <v>46064</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84821,7 +84821,7 @@
         <v>46150</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84894,7 +84894,7 @@
         <v>46150</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84967,7 +84967,7 @@
         <v>46156</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -85040,7 +85040,7 @@
         <v>46161</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -85113,7 +85113,7 @@
         <v>46161</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85186,7 +85186,7 @@
         <v>46209</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -85264,7 +85264,7 @@
         <v>46279</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -85342,7 +85342,7 @@
         <v>46279</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -85420,7 +85420,7 @@
         <v>46266</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45533</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45224</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>46161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>45568</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44978</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44524</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45103</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45476</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45194</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45078</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45086</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45357</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45996</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45236</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>45152</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>46196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>46198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>45212</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45126</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>45111</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>44610</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>45512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>46272</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45078</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44644</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45042</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45013</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45427</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44585</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45054</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45483</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45561</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45012</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45617</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45805</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45937</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>44908</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>44985</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45978</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>44820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>45961</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45672</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44928</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45079</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45205</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>45686</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>46106</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45012</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45282</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>46204</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45334</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45005</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>45527</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>45246</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45555</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45061</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45372</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45020</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>45749</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>46280</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46266</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>45832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45833</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45869</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44894</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45274</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45875</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45611</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44616</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45335</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44978</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44831</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44672</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44869</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45772</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>46168</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46202</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46206</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44568</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44853</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44508</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>44622</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44809</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44818</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44848</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44635</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44510</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44592</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44742</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44623</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44714</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44749</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44880</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44837</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44861</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44502</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44495</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44576</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44888</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44825</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44565</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44760</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44732</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44550</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44810</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44536</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>44810</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44588</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44845</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44862</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44764</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44739</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44742</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44515</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>44592</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44517</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44595</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44879</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44831</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44882</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44537</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44817</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>44806</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44530</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44882</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>44806</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44712</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44809</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44606</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44610</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44715</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44497</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44495</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45748</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45097</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44764</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>44929</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45614</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45187</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>44850</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45279</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44825</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45068</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44928</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45082</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45065</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45551</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44974</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45735</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45761</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>44874</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45103</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45714</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44617</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45218</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45602</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>44985</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45617</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45345</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45684</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45111</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45110</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44883</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45643</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44823</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44959</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>44634</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45099</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45719</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>44634</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45593</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>44858</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45181</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45441</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45226</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44852</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45672</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>44923</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45223</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45730</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44882</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45700</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45279</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44851</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44706</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45163</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>45103</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44817</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>45461</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45278</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45183</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45106</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45446</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45246</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45216</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45686</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45260</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45126</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44582</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45215</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44928</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45305</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44886</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45317</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45264</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45412</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>44810</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>44908</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45148</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44809</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45684</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45757</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>44603</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>44603</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44603</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>44945</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45205</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45646</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>44993</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45350</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45350</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44942</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45510</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45162</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45629</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45525</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45212</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45301</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>45225</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>45225</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45527</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45099</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>44810</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45280</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45257</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45645</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>44894</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45119</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45093</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45646</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45632</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45546</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45748</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46139</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45679</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45749</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45775</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45475</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45845</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45679</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45260</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45280</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45339</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45328</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45483</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45197</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44923</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45700</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45764</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45733</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45784</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>46139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45727</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>44487</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45112</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45715</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45604</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45567</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44903</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>45275</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45838</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45715</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45818</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45888</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45888</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45243</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45742</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44670</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45837</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45895</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45895</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45137</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45895</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45798</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45895</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45895</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45895</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45644</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45897</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45567</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45826</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45167</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45758</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>44740</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>45272</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45440</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45811</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45476</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>45275</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45207</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45916</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45733</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45842</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45077</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>46140</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45845</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45069</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>46140</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>46140</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44656</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45085</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45355</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45902</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45905</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45905</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45645</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>44991</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>46057</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45908</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>46059</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45910</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45162</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45707</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>44896</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45876</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45370</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45215</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45911</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45911</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45914</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45546</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45755</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>46146</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45916</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>45916</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45917</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45917</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>46146</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45734</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>44585</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44999</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45635</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>44991</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>44991</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45923</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45923</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45924</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45366</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45923</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45069</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45748</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45195</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45925</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45925</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45925</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45925</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45925</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>44634</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44991</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>44991</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>46150</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46150</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44959</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>44959</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45187</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45176</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45181</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45714</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>44523</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45168</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>45224</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45097</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45734</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>44573</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45463</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45938</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45940</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44820</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45945</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45945</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>46155</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45811</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45476</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>45111</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44846</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45946</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45845</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44848</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45749</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>45089</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>44565</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44565</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>46155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45950</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45950</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40169,7 +40169,7 @@
         <v>45911</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>45950</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>46155</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45730</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45068</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>45874</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>45957</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45957</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>45957</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>45315</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>46155</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40972,7 +40972,7 @@
         <v>45957</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>45888</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45672</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>46059</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>45959</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>46079</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>45470</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45961</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45602</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45339</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45097</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45961</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45964</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45964</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45169</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>45614</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45595</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44867</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>45427</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>46160</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45225</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45116</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45116</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>45610</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45973</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45156</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45218</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>44971</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>45714</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>45349</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>44937</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45629</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>45977</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45978</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45610</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>44620</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>46161</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45978</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>45628</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>45603</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45981</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45981</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45980</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45980</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45324</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45533</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45510</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45988</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45764</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45989</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45992</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45181</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45097</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45356</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>45992</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>45992</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>45264</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>44895</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>44895</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>44895</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45630</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45546</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45995</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45048</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45994</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45993</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45754</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45639</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>46104</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>46170</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>46170</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>46170</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45281</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>44886</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45265</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45179</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>46006</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>46006</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>45756</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>46006</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>46174</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>46174</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>46006</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45561</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>46008</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>46008</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>46008</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45401</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45610</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>45775</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>44900</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>46014</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46171</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>44508</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>46020</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44946</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>46024</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45239</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>46176</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45993</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45993</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>44742</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>44974</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>46030</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>44587</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45315</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46176</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>44959</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>44959</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46045</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45036</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>46045</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>46045</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>46045</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45593</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45483</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45628</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45181</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45390</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>44551</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45267</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46182</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>46050</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>46050</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45204</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>46054</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>44971</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>46054</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>46182</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>46054</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>44750</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45084</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>46059</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>46059</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>46059</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>46184</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>46062</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>46184</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45121</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>46063</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>46063</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45188</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45056</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>46063</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>46063</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45621</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>46069</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>45604</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>44802</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>45240</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>46078</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>46076</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>46077</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>45441</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>44825</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>45742</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45735</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45769</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>45119</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45273</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>45081</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         <v>45162</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45463</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>46084</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>46087</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53155,7 +53155,7 @@
         <v>45735</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53228,7 +53228,7 @@
         <v>45055</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45349</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>46094</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>46094</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>44915</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>46191</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45131</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>46097</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>46097</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>45610</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53958,7 +53958,7 @@
         <v>46097</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54031,7 +54031,7 @@
         <v>46097</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>46097</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46097</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>45183</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46097</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>46097</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>46195</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45509</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>45726</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45168</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>46104</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45614</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         <v>45614</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>46106</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>46104</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45092</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45146</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45620</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>46107</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>46107</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>46107</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>46107</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>46111</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55725,7 +55725,7 @@
         <v>46197</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>46111</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>46198</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55944,7 +55944,7 @@
         <v>46112</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>45236</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>44960</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>46113</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56236,7 +56236,7 @@
         <v>46113</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>46113</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>45188</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>46113</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>46113</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>46198</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>44938</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>44908</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         <v>44946</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56898,7 +56898,7 @@
         <v>46120</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>45357</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>46119</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>44712</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>46119</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57268,7 +57268,7 @@
         <v>45217</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>45908</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>45618</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45562</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>46128</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45509</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>44908</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46204</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45677</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57940,7 +57940,7 @@
         <v>45568</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>46134</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58086,7 +58086,7 @@
         <v>46134</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>44978</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>46134</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>44809</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58378,7 +58378,7 @@
         <v>44809</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58451,7 +58451,7 @@
         <v>46205</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>45880</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>46206</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58670,7 +58670,7 @@
         <v>45903</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58743,7 +58743,7 @@
         <v>45908</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>46206</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45005</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58962,7 +58962,7 @@
         <v>45702</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59035,7 +59035,7 @@
         <v>45126</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>45831</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59181,7 +59181,7 @@
         <v>45742</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45084</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>45722</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>46206</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>46206</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59546,7 +59546,7 @@
         <v>46206</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>45754</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59692,7 +59692,7 @@
         <v>44806</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59765,7 +59765,7 @@
         <v>45614</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59843,7 +59843,7 @@
         <v>45372</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59916,7 +59916,7 @@
         <v>45615</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59989,7 +59989,7 @@
         <v>46211</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>45121</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>46211</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>46216</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>44743</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60354,7 +60354,7 @@
         <v>44991</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60427,7 +60427,7 @@
         <v>45035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60500,7 +60500,7 @@
         <v>45614</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60573,7 +60573,7 @@
         <v>46063</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         <v>46184</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>44851</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>44988</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>45705</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         <v>45089</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61016,7 +61016,7 @@
         <v>45356</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61089,7 +61089,7 @@
         <v>46273</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61162,7 +61162,7 @@
         <v>46009</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61235,7 +61235,7 @@
         <v>45323</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61313,7 +61313,7 @@
         <v>45373</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61386,7 +61386,7 @@
         <v>46273</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61459,7 +61459,7 @@
         <v>44924</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61532,7 +61532,7 @@
         <v>45621</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61605,7 +61605,7 @@
         <v>46274</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45126</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61751,7 +61751,7 @@
         <v>45253</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61824,7 +61824,7 @@
         <v>44810</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>44923</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61970,7 +61970,7 @@
         <v>46274</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62043,7 +62043,7 @@
         <v>45187</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62116,7 +62116,7 @@
         <v>45076</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62189,7 +62189,7 @@
         <v>46277</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62262,7 +62262,7 @@
         <v>45524</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62335,7 +62335,7 @@
         <v>46279</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45099</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62481,7 +62481,7 @@
         <v>44628</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62554,7 +62554,7 @@
         <v>45119</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>44988</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>44887</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>44868</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45126</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62919,7 +62919,7 @@
         <v>44565</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62992,7 +62992,7 @@
         <v>45188</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45546</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63138,7 +63138,7 @@
         <v>44651</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>46239</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>46241</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>45323</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63440,7 +63440,7 @@
         <v>46240</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63518,7 +63518,7 @@
         <v>45012</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>45181</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         <v>44812</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63737,7 +63737,7 @@
         <v>45812</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63810,7 +63810,7 @@
         <v>45205</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63883,7 +63883,7 @@
         <v>44980</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>44810</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>46286</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64102,7 +64102,7 @@
         <v>46286</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64175,7 +64175,7 @@
         <v>45231</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64248,7 +64248,7 @@
         <v>45035</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>45077</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64394,7 +64394,7 @@
         <v>44945</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>45594</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64540,7 +64540,7 @@
         <v>46287</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>46244</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64686,7 +64686,7 @@
         <v>46119</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>44721</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>45300</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64910,7 +64910,7 @@
         <v>45210</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64983,7 +64983,7 @@
         <v>44903</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>46287</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65129,7 +65129,7 @@
         <v>46244</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65202,7 +65202,7 @@
         <v>45065</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65275,7 +65275,7 @@
         <v>45224</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65348,7 +65348,7 @@
         <v>45607</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65421,7 +65421,7 @@
         <v>46246</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65494,7 +65494,7 @@
         <v>45075</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>46224</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65640,7 +65640,7 @@
         <v>46246</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65713,7 +65713,7 @@
         <v>45223</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65786,7 +65786,7 @@
         <v>45223</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65859,7 +65859,7 @@
         <v>46289</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65932,7 +65932,7 @@
         <v>45071</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66005,7 +66005,7 @@
         <v>45071</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66078,7 +66078,7 @@
         <v>44642</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66151,7 +66151,7 @@
         <v>45301</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66224,7 +66224,7 @@
         <v>44712</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66297,7 +66297,7 @@
         <v>45195</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66370,7 +66370,7 @@
         <v>45071</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66443,7 +66443,7 @@
         <v>45071</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66516,7 +66516,7 @@
         <v>45705</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66589,7 +66589,7 @@
         <v>45701</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66662,7 +66662,7 @@
         <v>45940</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66735,7 +66735,7 @@
         <v>45628</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66808,7 +66808,7 @@
         <v>45581</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66881,7 +66881,7 @@
         <v>46292</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66954,7 +66954,7 @@
         <v>45372</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67027,7 +67027,7 @@
         <v>45250</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67100,7 +67100,7 @@
         <v>44819</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67173,7 +67173,7 @@
         <v>45152</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67246,7 +67246,7 @@
         <v>45097</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67319,7 +67319,7 @@
         <v>45131</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67392,7 +67392,7 @@
         <v>45441</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67465,7 +67465,7 @@
         <v>45131</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67538,7 +67538,7 @@
         <v>45615</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67611,7 +67611,7 @@
         <v>45033</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67684,7 +67684,7 @@
         <v>46252</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67757,7 +67757,7 @@
         <v>45307</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67830,7 +67830,7 @@
         <v>45764</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67903,7 +67903,7 @@
         <v>44886</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67976,7 +67976,7 @@
         <v>46251</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>45226</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -68122,7 +68122,7 @@
         <v>45306</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -68195,7 +68195,7 @@
         <v>45548</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -68268,7 +68268,7 @@
         <v>44985</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -68341,7 +68341,7 @@
         <v>44985</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -68414,7 +68414,7 @@
         <v>46294</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -68487,7 +68487,7 @@
         <v>44995</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68560,7 +68560,7 @@
         <v>45562</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68633,7 +68633,7 @@
         <v>45594</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68706,7 +68706,7 @@
         <v>45272</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68779,7 +68779,7 @@
         <v>45272</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68852,7 +68852,7 @@
         <v>44924</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68925,7 +68925,7 @@
         <v>45628</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68998,7 +68998,7 @@
         <v>44657</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -69071,7 +69071,7 @@
         <v>46253</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         <v>46296</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -69217,7 +69217,7 @@
         <v>46296</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -69290,7 +69290,7 @@
         <v>46254</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -69363,7 +69363,7 @@
         <v>46154</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -69436,7 +69436,7 @@
         <v>46154</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -69509,7 +69509,7 @@
         <v>46290</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69582,7 +69582,7 @@
         <v>44999</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69655,7 +69655,7 @@
         <v>45637</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69728,7 +69728,7 @@
         <v>45164</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69801,7 +69801,7 @@
         <v>45629</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69874,7 +69874,7 @@
         <v>45534</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69947,7 +69947,7 @@
         <v>45708</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -70020,7 +70020,7 @@
         <v>44959</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -70098,7 +70098,7 @@
         <v>45783</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -70171,7 +70171,7 @@
         <v>45783</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -70244,7 +70244,7 @@
         <v>45783</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -70317,7 +70317,7 @@
         <v>45021</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -70390,7 +70390,7 @@
         <v>45783</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -70463,7 +70463,7 @@
         <v>45783</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70536,7 +70536,7 @@
         <v>45783</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70609,7 +70609,7 @@
         <v>46098</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70682,7 +70682,7 @@
         <v>45708</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70755,7 +70755,7 @@
         <v>46298</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70828,7 +70828,7 @@
         <v>45628</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70901,7 +70901,7 @@
         <v>45161</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70974,7 +70974,7 @@
         <v>45734</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -71047,7 +71047,7 @@
         <v>45372</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -71120,7 +71120,7 @@
         <v>46182</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>45166</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -71266,7 +71266,7 @@
         <v>46301</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -71339,7 +71339,7 @@
         <v>45756</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -71412,7 +71412,7 @@
         <v>45510</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -71485,7 +71485,7 @@
         <v>45681</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71558,7 +71558,7 @@
         <v>45510</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71631,7 +71631,7 @@
         <v>45628</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71704,7 +71704,7 @@
         <v>46302</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71777,7 +71777,7 @@
         <v>46259</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71850,7 +71850,7 @@
         <v>45792</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71923,7 +71923,7 @@
         <v>45793</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71996,7 +71996,7 @@
         <v>46307</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -72069,7 +72069,7 @@
         <v>45596</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -72142,7 +72142,7 @@
         <v>44927</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -72215,7 +72215,7 @@
         <v>45796</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -72293,7 +72293,7 @@
         <v>45796</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -72371,7 +72371,7 @@
         <v>45796</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -72449,7 +72449,7 @@
         <v>45596</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72522,7 +72522,7 @@
         <v>46305</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72595,7 +72595,7 @@
         <v>45796</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72673,7 +72673,7 @@
         <v>46307</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72746,7 +72746,7 @@
         <v>46307</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72819,7 +72819,7 @@
         <v>46307</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72892,7 +72892,7 @@
         <v>45562</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72965,7 +72965,7 @@
         <v>45156</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -73038,7 +73038,7 @@
         <v>45253</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -73116,7 +73116,7 @@
         <v>45645</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -73189,7 +73189,7 @@
         <v>46266</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -73267,7 +73267,7 @@
         <v>45811</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -73340,7 +73340,7 @@
         <v>45811</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -73413,7 +73413,7 @@
         <v>45811</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -73486,7 +73486,7 @@
         <v>46301</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73559,7 +73559,7 @@
         <v>46265</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73632,7 +73632,7 @@
         <v>46310</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73705,7 +73705,7 @@
         <v>45371</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73778,7 +73778,7 @@
         <v>46310</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73851,7 +73851,7 @@
         <v>46310</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73924,7 +73924,7 @@
         <v>45686</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73997,7 +73997,7 @@
         <v>45817</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -74070,7 +74070,7 @@
         <v>45762</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -74143,7 +74143,7 @@
         <v>45518</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -74216,7 +74216,7 @@
         <v>45818</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -74289,7 +74289,7 @@
         <v>45617</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -74362,7 +74362,7 @@
         <v>46310</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -74435,7 +74435,7 @@
         <v>45825</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74508,7 +74508,7 @@
         <v>45824</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74581,7 +74581,7 @@
         <v>46268</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74654,7 +74654,7 @@
         <v>45793</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74727,7 +74727,7 @@
         <v>45826</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74800,7 +74800,7 @@
         <v>46310</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74873,7 +74873,7 @@
         <v>45831</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74946,7 +74946,7 @@
         <v>45831</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -75019,7 +75019,7 @@
         <v>45831</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -75092,7 +75092,7 @@
         <v>45831</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -75165,7 +75165,7 @@
         <v>45831</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -75238,7 +75238,7 @@
         <v>45831</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -75311,7 +75311,7 @@
         <v>45833</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -75384,7 +75384,7 @@
         <v>45835</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -75457,7 +75457,7 @@
         <v>45835</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75530,7 +75530,7 @@
         <v>45837</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75603,7 +75603,7 @@
         <v>45840</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75676,7 +75676,7 @@
         <v>45840</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75749,7 +75749,7 @@
         <v>45842</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75822,7 +75822,7 @@
         <v>45723</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75895,7 +75895,7 @@
         <v>45775</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75968,7 +75968,7 @@
         <v>45730</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -76041,7 +76041,7 @@
         <v>45848</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -76114,7 +76114,7 @@
         <v>45848</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -76187,7 +76187,7 @@
         <v>45811</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -76260,7 +76260,7 @@
         <v>45852</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -76333,7 +76333,7 @@
         <v>45667</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -76406,7 +76406,7 @@
         <v>45109</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76479,7 +76479,7 @@
         <v>45530</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76552,7 +76552,7 @@
         <v>45811</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76625,7 +76625,7 @@
         <v>45860</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76698,7 +76698,7 @@
         <v>45274</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76771,7 +76771,7 @@
         <v>45396</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76844,7 +76844,7 @@
         <v>45145</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76917,7 +76917,7 @@
         <v>44881</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76990,7 +76990,7 @@
         <v>45869</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -77068,7 +77068,7 @@
         <v>45701</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -77141,7 +77141,7 @@
         <v>45847</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -77214,7 +77214,7 @@
         <v>45739</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -77287,7 +77287,7 @@
         <v>45783</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -77360,7 +77360,7 @@
         <v>45005</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77433,7 +77433,7 @@
         <v>44917</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77506,7 +77506,7 @@
         <v>45701</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77579,7 +77579,7 @@
         <v>45425</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77652,7 +77652,7 @@
         <v>45099</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77725,7 +77725,7 @@
         <v>44621</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77798,7 +77798,7 @@
         <v>45079</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77871,7 +77871,7 @@
         <v>44538</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77944,7 +77944,7 @@
         <v>45394</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -78017,7 +78017,7 @@
         <v>45869</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -78095,7 +78095,7 @@
         <v>45271</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -78168,7 +78168,7 @@
         <v>44847</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -78241,7 +78241,7 @@
         <v>45026</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -78314,7 +78314,7 @@
         <v>45301</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -78387,7 +78387,7 @@
         <v>45647</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78460,7 +78460,7 @@
         <v>44881</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78533,7 +78533,7 @@
         <v>45211</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78606,7 +78606,7 @@
         <v>45247</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78679,7 +78679,7 @@
         <v>45145</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78752,7 +78752,7 @@
         <v>45394</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78825,7 +78825,7 @@
         <v>44715</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78898,7 +78898,7 @@
         <v>45301</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78971,7 +78971,7 @@
         <v>45481</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -79044,7 +79044,7 @@
         <v>44515</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -79117,7 +79117,7 @@
         <v>44515</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -79190,7 +79190,7 @@
         <v>45831</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -79263,7 +79263,7 @@
         <v>45211</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -79336,7 +79336,7 @@
         <v>45750</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79409,7 +79409,7 @@
         <v>45869</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79487,7 +79487,7 @@
         <v>45824</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79560,7 +79560,7 @@
         <v>45301</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         <v>44860</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79706,7 +79706,7 @@
         <v>45676</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79779,7 +79779,7 @@
         <v>45875</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         <v>45875</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79925,7 +79925,7 @@
         <v>45881</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79998,7 +79998,7 @@
         <v>45880</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -80071,7 +80071,7 @@
         <v>45880</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -80144,7 +80144,7 @@
         <v>45881</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -80217,7 +80217,7 @@
         <v>45110</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -80290,7 +80290,7 @@
         <v>44820</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -80363,7 +80363,7 @@
         <v>45537</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80436,7 +80436,7 @@
         <v>45226</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80509,7 +80509,7 @@
         <v>45527</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80582,7 +80582,7 @@
         <v>45593</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80655,7 +80655,7 @@
         <v>44638</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80728,7 +80728,7 @@
         <v>45000</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80801,7 +80801,7 @@
         <v>44644</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80874,7 +80874,7 @@
         <v>44820</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80947,7 +80947,7 @@
         <v>44643</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -81020,7 +81020,7 @@
         <v>45412</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -81093,7 +81093,7 @@
         <v>45272</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -81166,7 +81166,7 @@
         <v>45168</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -81239,7 +81239,7 @@
         <v>45378</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -81312,7 +81312,7 @@
         <v>44643</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81385,7 +81385,7 @@
         <v>44655</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45554</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45574</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45615</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81677,7 +81677,7 @@
         <v>45526</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45597</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81823,7 +81823,7 @@
         <v>45033</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81896,7 +81896,7 @@
         <v>45553</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81969,7 +81969,7 @@
         <v>45357</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -82042,7 +82042,7 @@
         <v>45427</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -82115,7 +82115,7 @@
         <v>44642</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -82188,7 +82188,7 @@
         <v>45447</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -82261,7 +82261,7 @@
         <v>45294</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82334,7 +82334,7 @@
         <v>45000</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82407,7 +82407,7 @@
         <v>45168</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82480,7 +82480,7 @@
         <v>45044</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82553,7 +82553,7 @@
         <v>45267</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82626,7 +82626,7 @@
         <v>45442</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82699,7 +82699,7 @@
         <v>44960</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82772,7 +82772,7 @@
         <v>44973</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82845,7 +82845,7 @@
         <v>45560</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82918,7 +82918,7 @@
         <v>45357</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82991,7 +82991,7 @@
         <v>44882</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -83064,7 +83064,7 @@
         <v>45110</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -83137,7 +83137,7 @@
         <v>45755</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -83210,7 +83210,7 @@
         <v>45637</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -83283,7 +83283,7 @@
         <v>45645</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83356,7 +83356,7 @@
         <v>45713</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83429,7 +83429,7 @@
         <v>45742</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83502,7 +83502,7 @@
         <v>45720</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83575,7 +83575,7 @@
         <v>45632</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83648,7 +83648,7 @@
         <v>45631</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83721,7 +83721,7 @@
         <v>45713</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83794,7 +83794,7 @@
         <v>45789</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83867,7 +83867,7 @@
         <v>45818</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83940,7 +83940,7 @@
         <v>45831</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -84013,7 +84013,7 @@
         <v>45831</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -84086,7 +84086,7 @@
         <v>45895</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -84159,7 +84159,7 @@
         <v>45895</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -84232,7 +84232,7 @@
         <v>45894</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84305,7 +84305,7 @@
         <v>46027</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84378,7 +84378,7 @@
         <v>46024</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84451,7 +84451,7 @@
         <v>46024</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84524,7 +84524,7 @@
         <v>46029</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84602,7 +84602,7 @@
         <v>46063</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84675,7 +84675,7 @@
         <v>46062</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84748,7 +84748,7 @@
         <v>46064</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84821,7 +84821,7 @@
         <v>46150</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84894,7 +84894,7 @@
         <v>46150</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84967,7 +84967,7 @@
         <v>46156</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -85040,7 +85040,7 @@
         <v>46161</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -85113,7 +85113,7 @@
         <v>46161</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85186,7 +85186,7 @@
         <v>46209</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -85264,7 +85264,7 @@
         <v>46279</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -85342,7 +85342,7 @@
         <v>46279</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -85420,7 +85420,7 @@
         <v>46266</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>

--- a/Översikt LJUNGBY.xlsx
+++ b/Översikt LJUNGBY.xlsx
@@ -601,7 +601,7 @@
         <v>46007</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45105</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44978</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45881</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45020</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45754</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>45867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46139</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46161</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>46203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45999</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>46155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44735</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46161</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45533</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>46008</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45568</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>45530</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>45211</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45224</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>45205</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45013</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>44978</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>46279</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>45181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>46196</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45978</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45236</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45996</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45512</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45819</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45733</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45476</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45357</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>46198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>46272</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>46150</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>45078</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45152</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>45212</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45111</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>45086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>45126</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45642</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>45103</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>45194</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44644</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44585</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45042</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>45427</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45378</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44496</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>46024</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>46146</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>46161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44495</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44806</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45594</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45282</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45191</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45012</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>44908</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>45961</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45672</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>45372</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45061</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>44820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>45162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45005</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45749</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>46204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>46006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45832</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45833</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>46106</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45869</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>45274</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>44894</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44985</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>46266</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45617</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44928</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>45937</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>45555</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45805</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45510</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46280</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>46317</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44645</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>45020</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>45012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>45483</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44852</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45054</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45686</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45561</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45527</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45079</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45334</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45205</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>45246</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44616</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44672</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45611</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45335</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>44831</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44869</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45772</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>46146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>46168</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>46202</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>46210</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>46206</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>46211</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46279</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44571</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>44715</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44568</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>44853</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>44622</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44508</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44510</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>44607</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>44809</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>44721</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44510</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44818</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>44848</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>44635</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44503</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44510</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44587</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>44592</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>44650</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>44714</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>44623</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44847</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>44847</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>44749</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>44880</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>44837</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>44861</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>44502</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44495</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44576</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>44888</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>44825</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44565</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>44760</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>44732</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>44550</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44536</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>44810</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44810</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44588</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>44845</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>44862</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44764</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44739</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44742</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44515</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44592</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>44517</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44595</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44879</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>44831</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44882</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>44817</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44537</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44806</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44810</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>44530</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44882</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>44806</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44712</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44809</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>44606</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44610</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>44497</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45715</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45748</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45888</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44495</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45758</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>44991</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44991</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>44809</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45188</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45684</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45048</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45162</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>44924</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45187</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45715</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45187</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45888</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45775</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44819</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44764</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45837</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45280</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45826</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45895</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44657</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45275</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45895</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45895</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45895</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45895</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45272</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45218</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45260</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45897</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44806</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45069</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44742</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44900</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44867</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>44908</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44825</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45356</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45562</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45908</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45546</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45604</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>45593</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45905</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45905</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45324</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>46160</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45226</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45910</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45568</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45707</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45911</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45097</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45911</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45097</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>46161</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>45876</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45081</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45916</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45093</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45914</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45916</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45917</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45305</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45917</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45097</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45923</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>45923</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45923</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45121</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45925</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45925</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45925</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45924</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45925</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45925</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44985</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45757</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45349</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44978</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>44960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45089</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45085</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>46170</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44712</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46104</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>46170</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>46170</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>44929</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>46171</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45281</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45440</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45253</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45754</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45734</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45441</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45938</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45702</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45764</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>44928</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>44991</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45775</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44971</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>46174</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>46174</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45111</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45940</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45119</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45945</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>46176</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>45945</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44868</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>44882</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46176</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44810</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45188</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45300</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44810</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
         <v>45239</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>45373</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44895</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44895</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44895</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45946</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45463</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45197</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45126</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45119</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45602</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45672</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>45950</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45950</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>45551</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45950</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45950</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44883</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45614</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45461</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45911</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45068</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>46182</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45401</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45103</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>46182</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45957</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45888</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45957</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>46184</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>46184</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>45301</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45700</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45959</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45065</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45961</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>45964</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>45121</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>45961</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45146</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45632</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45210</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45317</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>46191</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45603</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>46195</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45131</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45748</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>45181</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33752,7 +33752,7 @@
         <v>45412</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>46197</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45561</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45755</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45973</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>44993</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>45097</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45223</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>45977</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45978</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>46198</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45908</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>45250</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>44903</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45106</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45978</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>45546</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>45355</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45315</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45112</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>46198</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45980</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>45339</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>45980</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>44971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>45726</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>45981</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45610</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>44823</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45281</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>44587</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>46204</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45279</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45323</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45981</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>46205</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45985</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45548</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45610</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45594</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45077</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45714</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>46206</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>46206</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>46206</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45075</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>46206</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>46206</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45635</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45614</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45988</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45722</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>46211</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>45639</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>46211</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45989</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>45156</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45992</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>45164</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45992</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45615</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>44508</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45992</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45119</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>45730</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45441</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>45097</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>46184</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38731,7 +38731,7 @@
         <v>45994</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45995</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>46216</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45993</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>46063</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45181</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45629</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45534</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45278</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45708</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44959</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>46006</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>46006</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46009</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>46006</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>46008</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>46008</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>45783</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>45783</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45783</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>45783</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45161</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45021</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45783</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>46006</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>45708</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45265</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>46008</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>46277</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45681</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45628</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>46279</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>46014</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45372</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45734</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>46020</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>46239</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>45510</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>46024</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45756</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>45993</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45166</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45628</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>44894</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>46240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>46030</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45993</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45792</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>45510</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>46241</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45796</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45796</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45596</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46287</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45812</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
   